--- a/Morosos/informe_reporte_morosos_50.xlsx
+++ b/Morosos/informe_reporte_morosos_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="581">
   <si>
     <t>identificacion</t>
   </si>
@@ -43,40 +43,310 @@
     <t>deuda total</t>
   </si>
   <si>
-    <t>1025904113</t>
-  </si>
-  <si>
-    <t>1023535252</t>
-  </si>
-  <si>
-    <t>1025897533</t>
-  </si>
-  <si>
-    <t>1033198814</t>
+    <t>1192469248</t>
+  </si>
+  <si>
+    <t>1192466240</t>
+  </si>
+  <si>
+    <t>1036521142</t>
+  </si>
+  <si>
+    <t>1020322501</t>
+  </si>
+  <si>
+    <t>1020327607</t>
+  </si>
+  <si>
+    <t>1020317655</t>
+  </si>
+  <si>
+    <t>1011410509</t>
+  </si>
+  <si>
+    <t>1020235465</t>
+  </si>
+  <si>
+    <t>1192467267</t>
+  </si>
+  <si>
+    <t>1035006417</t>
+  </si>
+  <si>
+    <t>1011412659</t>
+  </si>
+  <si>
+    <t>1037130310</t>
+  </si>
+  <si>
+    <t>1013464926</t>
+  </si>
+  <si>
+    <t>1013466654</t>
+  </si>
+  <si>
+    <t>1023540172</t>
+  </si>
+  <si>
+    <t>1023165980</t>
+  </si>
+  <si>
+    <t>1011514095</t>
   </si>
   <si>
     <t>1013358746</t>
   </si>
   <si>
+    <t>1020323596</t>
+  </si>
+  <si>
+    <t>1021935485</t>
+  </si>
+  <si>
+    <t>1033192943</t>
+  </si>
+  <si>
+    <t>1025898446</t>
+  </si>
+  <si>
+    <t>1025895387</t>
+  </si>
+  <si>
     <t>1035003747</t>
   </si>
   <si>
-    <t>1141352259</t>
-  </si>
-  <si>
-    <t>1018254177</t>
-  </si>
-  <si>
-    <t>1054882046</t>
+    <t>1202213225</t>
+  </si>
+  <si>
+    <t>1021930204</t>
+  </si>
+  <si>
+    <t>1025906631</t>
+  </si>
+  <si>
+    <t>1011515086</t>
+  </si>
+  <si>
+    <t>1038872200</t>
+  </si>
+  <si>
+    <t>1038873057</t>
+  </si>
+  <si>
+    <t>1020230331</t>
+  </si>
+  <si>
+    <t>1039311523</t>
+  </si>
+  <si>
+    <t>1018252964</t>
+  </si>
+  <si>
+    <t>1013353521</t>
+  </si>
+  <si>
+    <t>1013362371</t>
+  </si>
+  <si>
+    <t>1011410413</t>
+  </si>
+  <si>
+    <t>1013349020</t>
+  </si>
+  <si>
+    <t>1013366022</t>
+  </si>
+  <si>
+    <t>1011517901</t>
+  </si>
+  <si>
+    <t>1011517846</t>
+  </si>
+  <si>
+    <t>1021931737</t>
+  </si>
+  <si>
+    <t>1018248214</t>
+  </si>
+  <si>
+    <t>1020228417</t>
+  </si>
+  <si>
+    <t>1020226198</t>
+  </si>
+  <si>
+    <t>1020321633</t>
+  </si>
+  <si>
+    <t>1018261295</t>
+  </si>
+  <si>
+    <t>1042587012</t>
+  </si>
+  <si>
+    <t>1018269052</t>
+  </si>
+  <si>
+    <t>1013364053</t>
+  </si>
+  <si>
+    <t>1013357048</t>
+  </si>
+  <si>
+    <t>1025902964</t>
+  </si>
+  <si>
+    <t>1041634370</t>
+  </si>
+  <si>
+    <t>1018258929</t>
+  </si>
+  <si>
+    <t>1018248468</t>
+  </si>
+  <si>
+    <t>1023538982</t>
+  </si>
+  <si>
+    <t>1013369943</t>
+  </si>
+  <si>
+    <t>1018254830</t>
+  </si>
+  <si>
+    <t>1013350043</t>
+  </si>
+  <si>
+    <t>1021931357</t>
+  </si>
+  <si>
+    <t>1020308169</t>
+  </si>
+  <si>
+    <t>1020232494</t>
+  </si>
+  <si>
+    <t>1020228828</t>
+  </si>
+  <si>
+    <t>1017938288</t>
+  </si>
+  <si>
+    <t>1018253746</t>
+  </si>
+  <si>
+    <t>1018271477</t>
   </si>
   <si>
     <t>1192469448</t>
   </si>
   <si>
-    <t>1011518603</t>
-  </si>
-  <si>
-    <t>1155716876</t>
+    <t>1025899613</t>
+  </si>
+  <si>
+    <t>1035005666</t>
+  </si>
+  <si>
+    <t>1020225476</t>
+  </si>
+  <si>
+    <t>1018253841</t>
+  </si>
+  <si>
+    <t>1032020916</t>
+  </si>
+  <si>
+    <t>1025770324</t>
+  </si>
+  <si>
+    <t>1025896359</t>
+  </si>
+  <si>
+    <t>1022007379</t>
+  </si>
+  <si>
+    <t>1020307672</t>
+  </si>
+  <si>
+    <t>1020321755</t>
+  </si>
+  <si>
+    <t>1011519079</t>
+  </si>
+  <si>
+    <t>1011516886</t>
+  </si>
+  <si>
+    <t>1093600920</t>
+  </si>
+  <si>
+    <t>1025898909</t>
+  </si>
+  <si>
+    <t>1020323103</t>
+  </si>
+  <si>
+    <t>1034993527</t>
+  </si>
+  <si>
+    <t>1034304812</t>
+  </si>
+  <si>
+    <t>1018261585</t>
+  </si>
+  <si>
+    <t>1011405972</t>
+  </si>
+  <si>
+    <t>1025897300</t>
+  </si>
+  <si>
+    <t>1020321827</t>
+  </si>
+  <si>
+    <t>1027664379</t>
+  </si>
+  <si>
+    <t>1027663704</t>
+  </si>
+  <si>
+    <t>1020312315</t>
+  </si>
+  <si>
+    <t>1036457627</t>
+  </si>
+  <si>
+    <t>1195213635</t>
+  </si>
+  <si>
+    <t>1015079466</t>
+  </si>
+  <si>
+    <t>1015077703</t>
+  </si>
+  <si>
+    <t>1011517041</t>
+  </si>
+  <si>
+    <t>1020311102</t>
+  </si>
+  <si>
+    <t>1096705038</t>
+  </si>
+  <si>
+    <t>1018273200</t>
+  </si>
+  <si>
+    <t>1021941636</t>
+  </si>
+  <si>
+    <t>1035011673</t>
+  </si>
+  <si>
+    <t>1035001646</t>
+  </si>
+  <si>
+    <t>1025895823</t>
   </si>
   <si>
     <t>1013368945</t>
@@ -85,25 +355,61 @@
     <t>1015075125</t>
   </si>
   <si>
+    <t>1025663772</t>
+  </si>
+  <si>
+    <t>1031943917</t>
+  </si>
+  <si>
+    <t>1021929020</t>
+  </si>
+  <si>
     <t>1035008500</t>
   </si>
   <si>
+    <t>1011404208</t>
+  </si>
+  <si>
+    <t>1011410559</t>
+  </si>
+  <si>
     <t>1025904957</t>
   </si>
   <si>
-    <t>1037676515</t>
-  </si>
-  <si>
-    <t>1037676716</t>
-  </si>
-  <si>
     <t>1018271176</t>
   </si>
   <si>
     <t>1018254757</t>
   </si>
   <si>
-    <t>1035978921</t>
+    <t>1141722491</t>
+  </si>
+  <si>
+    <t>1141719278</t>
+  </si>
+  <si>
+    <t>1011415143</t>
+  </si>
+  <si>
+    <t>1092540648</t>
+  </si>
+  <si>
+    <t>1069762747</t>
+  </si>
+  <si>
+    <t>1069756765</t>
+  </si>
+  <si>
+    <t>1011106856</t>
+  </si>
+  <si>
+    <t>1020228682</t>
+  </si>
+  <si>
+    <t>1023638076</t>
+  </si>
+  <si>
+    <t>1023595113</t>
   </si>
   <si>
     <t>1084474489</t>
@@ -115,46 +421,331 @@
     <t>1033200952</t>
   </si>
   <si>
-    <t>1023654563</t>
+    <t>1033190800</t>
+  </si>
+  <si>
+    <t>1025901666</t>
+  </si>
+  <si>
+    <t>1034925183</t>
+  </si>
+  <si>
+    <t>1025900606</t>
+  </si>
+  <si>
+    <t>1021929216</t>
+  </si>
+  <si>
+    <t>1205964537</t>
   </si>
   <si>
     <t>1023655274</t>
   </si>
   <si>
-    <t>Agudelo Luciana</t>
-  </si>
-  <si>
-    <t>Arango Plata Julieta</t>
-  </si>
-  <si>
-    <t>Bohorquez Vera Juan Esteban</t>
-  </si>
-  <si>
-    <t>Carmona Taborda Luciana</t>
+    <t>Aguirre Gomez Ariana</t>
+  </si>
+  <si>
+    <t>Aguirre Gomez Susana</t>
+  </si>
+  <si>
+    <t>Alzate Monsalve David</t>
+  </si>
+  <si>
+    <t>Artunduaga Burgos Emmanuel</t>
+  </si>
+  <si>
+    <t>Artunduaga Burgos Isaac</t>
+  </si>
+  <si>
+    <t>Artunduaga Burgos Sarahy</t>
+  </si>
+  <si>
+    <t>Atehortua Quintero Miguel Angel</t>
+  </si>
+  <si>
+    <t>Atehortua Quintero Simon</t>
+  </si>
+  <si>
+    <t>Betancur Cardona Samuel</t>
+  </si>
+  <si>
+    <t>Betancur Ortiz Isabella</t>
+  </si>
+  <si>
+    <t>Buitrago Caicedo Juan Sebastian</t>
+  </si>
+  <si>
+    <t>Cardenas Martinez Cristian Mathias</t>
+  </si>
+  <si>
+    <t>Cardona Mosquera Isaac</t>
+  </si>
+  <si>
+    <t>Cardona Mosquera Roxana</t>
+  </si>
+  <si>
+    <t>Caro Soto Samuel</t>
+  </si>
+  <si>
+    <t>Castaño Patiño Juan Jose</t>
+  </si>
+  <si>
+    <t>Castaño Viloria Sara</t>
   </si>
   <si>
     <t>Chavarria Osorio Luna Celeste</t>
   </si>
   <si>
+    <t>Chaverra Gomez Rebeca</t>
+  </si>
+  <si>
+    <t>Clavijo Quiceno Sara</t>
+  </si>
+  <si>
+    <t>Correa Castaño Christopher</t>
+  </si>
+  <si>
+    <t>Cortes Correa Rebeca</t>
+  </si>
+  <si>
+    <t>Cortes Correa Salome</t>
+  </si>
+  <si>
     <t>Cuervo Consuegra Tamara</t>
   </si>
   <si>
-    <t>Fonseca Rivera Emily Sofia</t>
-  </si>
-  <si>
-    <t>Garcia Correa Andres Esteban</t>
-  </si>
-  <si>
-    <t>Gomez Leon Mateo</t>
+    <t>De Luquez Bernal Mabel Sarai</t>
+  </si>
+  <si>
+    <t>Diaz Gonzalez Matias</t>
+  </si>
+  <si>
+    <t>Durango Vasco Mara</t>
+  </si>
+  <si>
+    <t>Echeverri Agudelo Samuel</t>
+  </si>
+  <si>
+    <t>Escalante Martinez Samuel</t>
+  </si>
+  <si>
+    <t>Escalante Martinez Sara</t>
+  </si>
+  <si>
+    <t>Ferraro Gallego Santiago</t>
+  </si>
+  <si>
+    <t>Garcia Arias Jheremy David</t>
+  </si>
+  <si>
+    <t>Garcia Gonzalez Juan Manuel</t>
+  </si>
+  <si>
+    <t>Garcia Ramirez Nicolas</t>
+  </si>
+  <si>
+    <t>Garcia Ramirez Thomás</t>
+  </si>
+  <si>
+    <t>Garzon Herrera Joel</t>
+  </si>
+  <si>
+    <t>Gaviria Cespedes Brenda</t>
+  </si>
+  <si>
+    <t>Gaviria Cespedes Evelyn</t>
+  </si>
+  <si>
+    <t>Gil Arroyo David</t>
+  </si>
+  <si>
+    <t>Giraldo Lozano Emma</t>
+  </si>
+  <si>
+    <t>Giraldo Perez Ana Isabel</t>
+  </si>
+  <si>
+    <t>Gomez Buitrago Mariangel</t>
+  </si>
+  <si>
+    <t>Gonzalez Bedoya Gracia</t>
+  </si>
+  <si>
+    <t>Gonzalez Bedoya Juanita</t>
+  </si>
+  <si>
+    <t>Gonzalez Gamboa Julieta</t>
+  </si>
+  <si>
+    <t>Gonzalez Mora Emily</t>
+  </si>
+  <si>
+    <t>Guette Ortiz Ashley Carolina</t>
+  </si>
+  <si>
+    <t>Guette Ortiz Norah Isabella</t>
+  </si>
+  <si>
+    <t>Henao Pinilla Simon</t>
+  </si>
+  <si>
+    <t>Herrera Higuita Antonia</t>
+  </si>
+  <si>
+    <t>Hurtado Hurtado Sara</t>
+  </si>
+  <si>
+    <t>Jaramillo Agudelo Ana Sofia</t>
+  </si>
+  <si>
+    <t>Jaramillo Carranza Camila</t>
+  </si>
+  <si>
+    <t>Jaramillo Carranza Santiago</t>
+  </si>
+  <si>
+    <t>Londoño Jaramillo Ezequiel</t>
+  </si>
+  <si>
+    <t>Londoño Jaramillo Samuel</t>
+  </si>
+  <si>
+    <t>Londoño Sanchez Antonia</t>
+  </si>
+  <si>
+    <t>Luna Rincon Juan Sebastian</t>
+  </si>
+  <si>
+    <t>Machado Taborda Mateo</t>
+  </si>
+  <si>
+    <t>Manco Fonnegra Samuel</t>
+  </si>
+  <si>
+    <t>Mariaca Montagut Alejandra</t>
+  </si>
+  <si>
+    <t>Mariaca Montagut Maria Clara</t>
+  </si>
+  <si>
+    <t>Marin Correa Matias</t>
+  </si>
+  <si>
+    <t>Marin Jaramillo Nicolas</t>
+  </si>
+  <si>
+    <t>Marin Vergara Nicolas</t>
   </si>
   <si>
     <t>Marquez Mora Emilia</t>
   </si>
   <si>
-    <t>Ospina Cifuentes Antonella</t>
-  </si>
-  <si>
-    <t>Quintero Suarez Andres David</t>
+    <t>Martinez Alvarez Thiago</t>
+  </si>
+  <si>
+    <t>Martinez Ciro Josue</t>
+  </si>
+  <si>
+    <t>Martinez Correa Tomas</t>
+  </si>
+  <si>
+    <t>Mendoza Alvarez Abigail</t>
+  </si>
+  <si>
+    <t>Meneses Jimenez Mariangel</t>
+  </si>
+  <si>
+    <t>Mesa Cardona Mariangel</t>
+  </si>
+  <si>
+    <t>Mina Andrade Sara Lucia</t>
+  </si>
+  <si>
+    <t>Montagut Ibañez Sara</t>
+  </si>
+  <si>
+    <t>Muñoz Vellojin Mateo</t>
+  </si>
+  <si>
+    <t>Orozco Velez Emiliano</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Analucia</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Benjamin</t>
+  </si>
+  <si>
+    <t>Ortega Zabala Heri Thomas</t>
+  </si>
+  <si>
+    <t>Perez Coronado David</t>
+  </si>
+  <si>
+    <t>Perez Pino Susana</t>
+  </si>
+  <si>
+    <t>Perez Polo Sofia</t>
+  </si>
+  <si>
+    <t>Perilla Chica Isabella</t>
+  </si>
+  <si>
+    <t>Peña González Sophia</t>
+  </si>
+  <si>
+    <t>Piedrahita Betancur Ana Sofia</t>
+  </si>
+  <si>
+    <t>Piedrahita Restrepo Mariana</t>
+  </si>
+  <si>
+    <t>Posada Alzate Abraham</t>
+  </si>
+  <si>
+    <t>Prieto Albán Isaac</t>
+  </si>
+  <si>
+    <t>Prieto Albán Mathías</t>
+  </si>
+  <si>
+    <t>Pérez Hernández Salomé</t>
+  </si>
+  <si>
+    <t>Ramirez Ramirez Luciana</t>
+  </si>
+  <si>
+    <t>Restrepo Cadavid Emanuel</t>
+  </si>
+  <si>
+    <t>Restrepo Cortes Isabella</t>
+  </si>
+  <si>
+    <t>Restrepo Cortes Juan Manuel</t>
+  </si>
+  <si>
+    <t>Rios Hurtado Miguel Angel</t>
+  </si>
+  <si>
+    <t>Rios Salazar Santiago</t>
+  </si>
+  <si>
+    <t>Rizo Paez David Armando</t>
+  </si>
+  <si>
+    <t>Rizo Paez Elisa Victoria</t>
+  </si>
+  <si>
+    <t>Rojas Jimenez Sofia</t>
+  </si>
+  <si>
+    <t>Rueda Alvarez Josue</t>
+  </si>
+  <si>
+    <t>Rueda Alvarez Julieta</t>
+  </si>
+  <si>
+    <t>Ruiz Aristizabal Nicolas</t>
   </si>
   <si>
     <t>Ruiz Estrada Sofia Camila</t>
@@ -163,25 +754,61 @@
     <t>Ruiz Rodas Jacobo</t>
   </si>
   <si>
+    <t>Ruiz Urquijo Martin</t>
+  </si>
+  <si>
+    <t>Ruiz Urquijo Violeta</t>
+  </si>
+  <si>
+    <t>Saldarriaga Aguirre Hannah</t>
+  </si>
+  <si>
     <t>Sanabria Cardona Santiago</t>
   </si>
   <si>
+    <t>Sanchez Bustamante Genesis</t>
+  </si>
+  <si>
+    <t>Sanchez Bustamante Sarah Joann</t>
+  </si>
+  <si>
     <t>Sanchez Justiniano Jose David</t>
   </si>
   <si>
-    <t>Santos Paz Ezra Wolf</t>
-  </si>
-  <si>
-    <t>Santos Paz Mateo Maximo</t>
-  </si>
-  <si>
     <t>Sayago Acevedo Isabella</t>
   </si>
   <si>
     <t>Sayago Acevedo Samuel</t>
   </si>
   <si>
-    <t>Serna Ramirez Luciana</t>
+    <t>Segura Rios Emmanuel David</t>
+  </si>
+  <si>
+    <t>Segura Rios Samuel Felipe</t>
+  </si>
+  <si>
+    <t>Serna Longa Sahilyn</t>
+  </si>
+  <si>
+    <t>Sierra Peñaranda Miguel Angel</t>
+  </si>
+  <si>
+    <t>Sorza Hernandez Juan Martin</t>
+  </si>
+  <si>
+    <t>Sorza Hernandez Maria Juliana</t>
+  </si>
+  <si>
+    <t>Suarez Bayona Martina</t>
+  </si>
+  <si>
+    <t>Suescun Yepes Juan Manuel</t>
+  </si>
+  <si>
+    <t>Suescun Yepes Luciana</t>
+  </si>
+  <si>
+    <t>Tabares Martinez Martina</t>
   </si>
   <si>
     <t>Tenorio Maya Liam</t>
@@ -193,7 +820,22 @@
     <t>Usma Jaramillo Maria Celeste</t>
   </si>
   <si>
-    <t>Yepes Murillo Mariangel</t>
+    <t>Usuga Hidalgo Juan Sebastian</t>
+  </si>
+  <si>
+    <t>Vanegas Olaya Simon</t>
+  </si>
+  <si>
+    <t>Vanegas Pulgarin Sheray</t>
+  </si>
+  <si>
+    <t>Velez Ortiz Simon</t>
+  </si>
+  <si>
+    <t>Villegas Vargas Mariangel</t>
+  </si>
+  <si>
+    <t>Zambrano Blanco Luis Felipe</t>
   </si>
   <si>
     <t>Zambrano Mejia Mariangel</t>
@@ -202,64 +844,286 @@
     <t>SEGUNDO</t>
   </si>
   <si>
+    <t>NOVENO</t>
+  </si>
+  <si>
     <t>CUARTO</t>
   </si>
   <si>
+    <t>QUINTO</t>
+  </si>
+  <si>
+    <t>TRANSICIÓN</t>
+  </si>
+  <si>
     <t>SEPTIMO</t>
   </si>
   <si>
+    <t>SEXTO</t>
+  </si>
+  <si>
     <t>TERCERO</t>
   </si>
   <si>
-    <t>SEXTO</t>
+    <t>DÉCIMO</t>
+  </si>
+  <si>
+    <t>ONCE</t>
+  </si>
+  <si>
+    <t>OCTAVO</t>
   </si>
   <si>
     <t>PRIMERO</t>
   </si>
   <si>
-    <t>DÉCIMO</t>
-  </si>
-  <si>
-    <t>QUINTO</t>
-  </si>
-  <si>
-    <t>NOVENO</t>
-  </si>
-  <si>
-    <t>Agudelo Juliet Cristina</t>
-  </si>
-  <si>
-    <t>Arango Parra Juan Carlos</t>
-  </si>
-  <si>
-    <t>Bohorquez Almeida Cristian</t>
-  </si>
-  <si>
-    <t>Correa Claudia Patricia</t>
+    <t>Aguirre Naranjo Bryan Stiven</t>
+  </si>
+  <si>
+    <t>Alzate Villa William</t>
+  </si>
+  <si>
+    <t>Artunduaga Cabrera Anderson</t>
+  </si>
+  <si>
+    <t>Atehortua Morales Didier</t>
+  </si>
+  <si>
+    <t>Cardona Gómez Marcela</t>
+  </si>
+  <si>
+    <t>Ortiz Monsalve Natalia</t>
+  </si>
+  <si>
+    <t>Buitrago Gonzalez Edison Alexander</t>
+  </si>
+  <si>
+    <t>Cardenas Cordero Christian Enrique</t>
+  </si>
+  <si>
+    <t>Mosquera Rodriguez Tania Karina</t>
+  </si>
+  <si>
+    <t>Caro Rivas Grovis Yinois</t>
+  </si>
+  <si>
+    <t>Castaño Zapata Jose Fernando</t>
+  </si>
+  <si>
+    <t>Viloria Montoya Isabel Cristina</t>
   </si>
   <si>
     <t>Chavarria Ramirez Roman Alberto</t>
   </si>
   <si>
+    <t>Chaverra Chaverra Juan David</t>
+  </si>
+  <si>
+    <t>Carreño Bohorquez Nora Maria</t>
+  </si>
+  <si>
+    <t>Correa Santana Edwin Andres</t>
+  </si>
+  <si>
+    <t>Cortes Velasquez Juan Pablo</t>
+  </si>
+  <si>
     <t>Cuervo Paternina Eder Andres</t>
   </si>
   <si>
-    <t>David Mercado Andres Felipe</t>
-  </si>
-  <si>
-    <t>Correa Osorio Luisa Fernanda</t>
-  </si>
-  <si>
-    <t>Gomez Serna Daniel</t>
+    <t>De Luquez Diaz Ezequiel</t>
+  </si>
+  <si>
+    <t>Diaz Rico John Edwin</t>
+  </si>
+  <si>
+    <t>Vasco Ortiz Yeimy Natalia</t>
+  </si>
+  <si>
+    <t>Echeverry Agudelo Sara Catalina</t>
+  </si>
+  <si>
+    <t>Forero Reyes Janeth</t>
+  </si>
+  <si>
+    <t>Ferraro Trejos Diego Gian Franco</t>
+  </si>
+  <si>
+    <t>Garcia Gomez Reinaldo David</t>
+  </si>
+  <si>
+    <t>Gonzalez Mora Julieth Marcela</t>
+  </si>
+  <si>
+    <t>Ramirez Suarez Leidy Tatiana</t>
+  </si>
+  <si>
+    <t>Garcia Valencia Cesar Augusto</t>
+  </si>
+  <si>
+    <t>Garzon Garcia Milton Arley</t>
+  </si>
+  <si>
+    <t>Cespedes Restrepo Maria Alejandra</t>
+  </si>
+  <si>
+    <t>Gil Clavijo Luber Mario</t>
+  </si>
+  <si>
+    <t>Lozano Mosquera Mariam</t>
+  </si>
+  <si>
+    <t>Giraldo Hoyos David</t>
+  </si>
+  <si>
+    <t>Gomez Rios Geovanny Arley</t>
+  </si>
+  <si>
+    <t>Gonzalez Diaz Mauricio De Jesus</t>
+  </si>
+  <si>
+    <t>Gamboa Melendrez Jeniffer</t>
+  </si>
+  <si>
+    <t>Ortiz Julio Sirly Dayana</t>
+  </si>
+  <si>
+    <t>Henao Betancur Jorge Humberto</t>
+  </si>
+  <si>
+    <t>Herrera Serna Oscar Alejandro</t>
+  </si>
+  <si>
+    <t>Hurtado Orozco Yudi Andrea</t>
+  </si>
+  <si>
+    <t>Agudelo Torres Sumilde Elena</t>
+  </si>
+  <si>
+    <t>Carranza Ricardo Diana Marcela</t>
+  </si>
+  <si>
+    <t>Londoño Moreno Andres Felipe</t>
+  </si>
+  <si>
+    <t>Sanchez Isaura Pilar</t>
+  </si>
+  <si>
+    <t>Rincon Lopera Liliana Maria</t>
+  </si>
+  <si>
+    <t>Sas Inversiones Myt</t>
+  </si>
+  <si>
+    <t>Manco Echavarria Reynel De Jesus</t>
+  </si>
+  <si>
+    <t>Montagut Ortiz Clariveth</t>
+  </si>
+  <si>
+    <t>Correa Arboleda Ana Maria</t>
+  </si>
+  <si>
+    <t>Marin Jaramillo Juan Camilo</t>
+  </si>
+  <si>
+    <t>Vergara Mejia Sara Valentina</t>
   </si>
   <si>
     <t>Mora Cardona Katherine</t>
   </si>
   <si>
-    <t>Ospina Escobar Nilson James</t>
-  </si>
-  <si>
-    <t>Quintero Gerardino Jairo Andres</t>
+    <t>Hernandez Morelo Liliana</t>
+  </si>
+  <si>
+    <t>Martinez Moreno Devinson</t>
+  </si>
+  <si>
+    <t>Correa Mejia Catalina</t>
+  </si>
+  <si>
+    <t>Alvarez Martinez Glenys Yanet</t>
+  </si>
+  <si>
+    <t>Meneses Schroeder Henry Harold</t>
+  </si>
+  <si>
+    <t>Cardona Gaviria Maribel</t>
+  </si>
+  <si>
+    <t>Mina Zapata James Dayner</t>
+  </si>
+  <si>
+    <t>Montagut Ortiz Adiel</t>
+  </si>
+  <si>
+    <t>Vellojin Cavadia Tania Marjolia</t>
+  </si>
+  <si>
+    <t>Velez Ortiz Jeniffer</t>
+  </si>
+  <si>
+    <t>Orrego Zuluaga Juan Esteban</t>
+  </si>
+  <si>
+    <t>Zabala Cuervo Diana Rocio</t>
+  </si>
+  <si>
+    <t>Perez Bohorquez Jhon Robert</t>
+  </si>
+  <si>
+    <t>Perez Toro Juan Pablo</t>
+  </si>
+  <si>
+    <t>Polo Aly Angela Maria</t>
+  </si>
+  <si>
+    <t>Perilla Alarcon Elisio</t>
+  </si>
+  <si>
+    <t>Peña Solórzano Francisco Javier</t>
+  </si>
+  <si>
+    <t>Betancur Ramirez Gina Marcela</t>
+  </si>
+  <si>
+    <t>Piedrahita Bracamonte Alan Yesith</t>
+  </si>
+  <si>
+    <t>Posada Suarez Gabriel Fernando</t>
+  </si>
+  <si>
+    <t>Prieto Oyaga Cristhian Camilo</t>
+  </si>
+  <si>
+    <t>Hernandez Cardona Mauricio</t>
+  </si>
+  <si>
+    <t>Ramirez Puerta Johnnatan</t>
+  </si>
+  <si>
+    <t>Restrepo Duque Jorge Mauricio</t>
+  </si>
+  <si>
+    <t>Restrepo Silva Jeison</t>
+  </si>
+  <si>
+    <t>Hurtado Garzon Rosalba</t>
+  </si>
+  <si>
+    <t>Rios Echeverri John Walter</t>
+  </si>
+  <si>
+    <t>Rizo Ibanez Jorge Armando</t>
+  </si>
+  <si>
+    <t>Marino Millan Yelitza Rossana</t>
+  </si>
+  <si>
+    <t>Rueda Piedrahita Carlos Ariel</t>
+  </si>
+  <si>
+    <t>Agudelo Ruiz Sergio Mario</t>
   </si>
   <si>
     <t>Estrada Colon Yerica Del Carmen</t>
@@ -268,22 +1132,46 @@
     <t>Rodas Marin Monica Janeth</t>
   </si>
   <si>
+    <t>Ruiz Cardona Pablo Andres</t>
+  </si>
+  <si>
+    <t>Claudina Estela Aguirre Diaz</t>
+  </si>
+  <si>
     <t>Sanabria Ballen Andres Leonardo</t>
   </si>
   <si>
+    <t>Zuleta Castrillon Monica Marcela</t>
+  </si>
+  <si>
     <t>Sanchez Justiniano Martha Catherine</t>
   </si>
   <si>
-    <t>Santos Lopez Sebastian</t>
-  </si>
-  <si>
     <t>Sayago Montes Juan Esteban</t>
   </si>
   <si>
     <t>Acevedo Galeano Viviana</t>
   </si>
   <si>
-    <t>Arboleda Ramirez Daniel Andres</t>
+    <t>Segura Camacho Oscar Dario</t>
+  </si>
+  <si>
+    <t>Longa Ramirez Baldoina</t>
+  </si>
+  <si>
+    <t>Hernandez Ospina Juan Camilo</t>
+  </si>
+  <si>
+    <t>Hernandez Baron Lina Paola</t>
+  </si>
+  <si>
+    <t>Bayona Buitrago Sandra Milena</t>
+  </si>
+  <si>
+    <t>Suescun Gomez Jhony Alexander</t>
+  </si>
+  <si>
+    <t>Tabares Vergara Sergio Adrian</t>
   </si>
   <si>
     <t>Marin Osorio Johny Alexander</t>
@@ -295,7 +1183,22 @@
     <t>Usma Acevedo Elkin Humberto</t>
   </si>
   <si>
-    <t>Yepes Arias Angela Maria</t>
+    <t>Usuga Sepulveda Henrry</t>
+  </si>
+  <si>
+    <t>Olaya Rojas Liliana Maria</t>
+  </si>
+  <si>
+    <t>Vanegas Zuñiga Ray Andres</t>
+  </si>
+  <si>
+    <t>Ortiz Velez Laura Catalina</t>
+  </si>
+  <si>
+    <t>Villegas Gonzalez Wbeimar Alexander</t>
+  </si>
+  <si>
+    <t>Blanco Rincon Diana Margarita</t>
   </si>
   <si>
     <t>Santana Marulanda Stuart</t>
@@ -307,52 +1210,223 @@
     <t>Padre</t>
   </si>
   <si>
+    <t>Abuela</t>
+  </si>
+  <si>
     <t>Tía</t>
   </si>
   <si>
+    <t>Tío</t>
+  </si>
+  <si>
+    <t>Otro</t>
+  </si>
+  <si>
     <t>Padrastro</t>
   </si>
   <si>
-    <t>3102032602</t>
-  </si>
-  <si>
-    <t>5586629</t>
-  </si>
-  <si>
-    <t>5076630</t>
-  </si>
-  <si>
-    <t>3148691862</t>
+    <t>5083522</t>
+  </si>
+  <si>
+    <t>3008486499</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>4794235</t>
+  </si>
+  <si>
+    <t>4210191</t>
+  </si>
+  <si>
+    <t>3005565956</t>
+  </si>
+  <si>
+    <t>5780406</t>
+  </si>
+  <si>
+    <t>5671163</t>
+  </si>
+  <si>
+    <t>5095498</t>
+  </si>
+  <si>
+    <t>6044444614</t>
+  </si>
+  <si>
+    <t>5075518</t>
+  </si>
+  <si>
+    <t>5467166</t>
   </si>
   <si>
     <t>3104067600</t>
   </si>
   <si>
+    <t>4579679</t>
+  </si>
+  <si>
+    <t>4432431</t>
+  </si>
+  <si>
+    <t>2973675</t>
+  </si>
+  <si>
     <t>2068714</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>3013564721</t>
-  </si>
-  <si>
-    <t>3013620164</t>
-  </si>
-  <si>
-    <t>3233605163</t>
+    <t>5823889</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>3015686911</t>
+  </si>
+  <si>
+    <t>2612413</t>
+  </si>
+  <si>
+    <t>4076883</t>
+  </si>
+  <si>
+    <t>4337791</t>
+  </si>
+  <si>
+    <t>3204743</t>
+  </si>
+  <si>
+    <t>3204103173</t>
+  </si>
+  <si>
+    <t>4889842</t>
+  </si>
+  <si>
+    <t>5802808</t>
+  </si>
+  <si>
+    <t>5O9 80 21</t>
+  </si>
+  <si>
+    <t>5038065</t>
+  </si>
+  <si>
+    <t>4811500</t>
+  </si>
+  <si>
+    <t>2678435</t>
+  </si>
+  <si>
+    <t>5060713</t>
+  </si>
+  <si>
+    <t>4195996</t>
+  </si>
+  <si>
+    <t>3136549427</t>
+  </si>
+  <si>
+    <t>4224748</t>
+  </si>
+  <si>
+    <t>3113353894</t>
+  </si>
+  <si>
+    <t>4986408</t>
+  </si>
+  <si>
+    <t>4773589</t>
+  </si>
+  <si>
+    <t>2050489</t>
+  </si>
+  <si>
+    <t>4778965</t>
+  </si>
+  <si>
+    <t>5892695</t>
+  </si>
+  <si>
+    <t>5700932</t>
+  </si>
+  <si>
+    <t>4172927</t>
+  </si>
+  <si>
+    <t>3006234263</t>
+  </si>
+  <si>
+    <t>5848983</t>
+  </si>
+  <si>
+    <t>6045061121</t>
+  </si>
+  <si>
+    <t>3135826927</t>
+  </si>
+  <si>
+    <t>6125258</t>
+  </si>
+  <si>
+    <t>6045823601</t>
+  </si>
+  <si>
+    <t>5839111</t>
+  </si>
+  <si>
+    <t>3178333446</t>
+  </si>
+  <si>
+    <t>3323915</t>
+  </si>
+  <si>
+    <t>3112860092</t>
+  </si>
+  <si>
+    <t>5042146</t>
+  </si>
+  <si>
+    <t>5030235</t>
+  </si>
+  <si>
+    <t>3022703240</t>
+  </si>
+  <si>
+    <t>5044236</t>
   </si>
   <si>
     <t>2840252</t>
   </si>
   <si>
+    <t>4802180</t>
+  </si>
+  <si>
+    <t>2941876</t>
+  </si>
+  <si>
     <t>2347767</t>
   </si>
   <si>
-    <t>3117634856</t>
-  </si>
-  <si>
-    <t>5771821</t>
+    <t>4330808</t>
+  </si>
+  <si>
+    <t>5863905</t>
+  </si>
+  <si>
+    <t>6008276</t>
+  </si>
+  <si>
+    <t>4886484</t>
+  </si>
+  <si>
+    <t>6045901145</t>
+  </si>
+  <si>
+    <t>5797398</t>
   </si>
   <si>
     <t>3205617348</t>
@@ -361,43 +1435,259 @@
     <t>4381023</t>
   </si>
   <si>
-    <t>3104440838</t>
-  </si>
-  <si>
-    <t>agudeloluciana90@gmail.com</t>
-  </si>
-  <si>
-    <t>jcarangoparra@gmail.com</t>
-  </si>
-  <si>
-    <t>KRISTIANBOHOR25@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>geraldinetabordacardona@gmail.com</t>
+    <t>4882576</t>
+  </si>
+  <si>
+    <t>3113582464</t>
+  </si>
+  <si>
+    <t>bryansan87@gmail.com</t>
+  </si>
+  <si>
+    <t>kellyj2914@hotmail.com</t>
+  </si>
+  <si>
+    <t>macartin01@hotmail.es</t>
+  </si>
+  <si>
+    <t>vanequin09@gmail.com</t>
+  </si>
+  <si>
+    <t>FUEGOVITAL760@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MASMECANICA1@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>EDISONBUITRAGO_1@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>christian.cardenas@correo.policia.gov.co</t>
+  </si>
+  <si>
+    <t>ANDRESCARDONA70@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>alejandrasotoh@gmail.com</t>
+  </si>
+  <si>
+    <t>CTATIANAP@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>CLAUDIAYAVIMO@GMAIL.COM</t>
   </si>
   <si>
     <t>veronicaosoriocarvajal@gmail.com</t>
   </si>
   <si>
+    <t>PAO1825@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>marybella2905@gmail.com</t>
+  </si>
+  <si>
+    <t>linacastano065@gmail.com</t>
+  </si>
+  <si>
+    <t>ALEJANDRA210187@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>mercadeo@vertigologistica.com</t>
+  </si>
+  <si>
     <t>marlencj@hotmail.com</t>
   </si>
   <si>
-    <t>leidypaorivera@gmail.com</t>
-  </si>
-  <si>
-    <t>fercorreaosorio25@gmail.com</t>
-  </si>
-  <si>
-    <t>yeimyleon8904@gmail.com</t>
+    <t>EZDEDI7@YAHOO.ES</t>
+  </si>
+  <si>
+    <t>jhondiazrico@gmail.com</t>
+  </si>
+  <si>
+    <t>nataliav.o@outlook.com</t>
+  </si>
+  <si>
+    <t>SARITA-ECHEVERRI@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>jafore0809@hotmail.comsan</t>
+  </si>
+  <si>
+    <t>GIANFRANCO1077@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>REYDAVIDGJ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>marcegonzalez353@gmail.com</t>
+  </si>
+  <si>
+    <t>Ramirezsuarezt@gmail.com</t>
+  </si>
+  <si>
+    <t>nancymj7481@gmail.com</t>
+  </si>
+  <si>
+    <t>alejandra.cespedes.r@hotmail.com</t>
+  </si>
+  <si>
+    <t>kellymargaritaarroyogonzalez@gmail.com</t>
+  </si>
+  <si>
+    <t>esteban.g0104@hotmail.com</t>
+  </si>
+  <si>
+    <t>davidgi2427@gmail.com</t>
+  </si>
+  <si>
+    <t>GIOVA.GO8124@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>nataliabedoya@hotmail.com</t>
+  </si>
+  <si>
+    <t>jennifermelendrez87@gmail.com</t>
+  </si>
+  <si>
+    <t>Sirlydayana@hotmail.com</t>
+  </si>
+  <si>
+    <t>zuleimapv4@hotmail.com</t>
+  </si>
+  <si>
+    <t>chiguita08@gmail.com</t>
+  </si>
+  <si>
+    <t>SEAGUDELOT@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>carranza.dm21@hotmail.es</t>
+  </si>
+  <si>
+    <t>ledisjaramillo0@gmail.com</t>
+  </si>
+  <si>
+    <t>ISAPISAN@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>jclunapublicidad@gmail.com</t>
+  </si>
+  <si>
+    <t>SELVAAZUL_07@YAHOO.ES</t>
+  </si>
+  <si>
+    <t>REYNELM1980@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>klariveth@gmail.com</t>
+  </si>
+  <si>
+    <t>alejomtoro1@gmail.com</t>
+  </si>
+  <si>
+    <t>amariac22@hotmail.com</t>
+  </si>
+  <si>
+    <t>o.mairaj.opjh39@gmail.com</t>
+  </si>
+  <si>
+    <t>saravergara775@gmail.com</t>
   </si>
   <si>
     <t>ktmc-10@hotmail.com</t>
   </si>
   <si>
-    <t>y-ulivale@hotmail.com</t>
-  </si>
-  <si>
-    <t>yohelissuarez@gmail.com</t>
+    <t>EZEQUIELMARTINEZ-5@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>alexandraa200906@gmail.com</t>
+  </si>
+  <si>
+    <t>CATALINACORREA1327@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>glenysyanett@hotmail.com</t>
+  </si>
+  <si>
+    <t>henryme1966@gmail.com</t>
+  </si>
+  <si>
+    <t>TONERYPCS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>EMMA_ANDRADE@YAHOO.ES</t>
+  </si>
+  <si>
+    <t>adielmontagut@gmail.com</t>
+  </si>
+  <si>
+    <t>TANIAVELCAV@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>JENIFER1129@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>NATALIAJIMENEZCOMUNICACIONES@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DIANITAZABALA@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>robertpb2713@gmail.com</t>
+  </si>
+  <si>
+    <t>khathik18@gmail.com</t>
+  </si>
+  <si>
+    <t>poloangela87@gmail.com</t>
+  </si>
+  <si>
+    <t>mariat169@yahoo.com</t>
+  </si>
+  <si>
+    <t>vanekiu1979@hotmail.com</t>
+  </si>
+  <si>
+    <t>ginmarcela@gmail.com</t>
+  </si>
+  <si>
+    <t>vivianarestrepo@gmail.com</t>
+  </si>
+  <si>
+    <t>posadagabriel@hotmail.com</t>
+  </si>
+  <si>
+    <t>luiza1415@hotmail.es</t>
+  </si>
+  <si>
+    <t>PAOLAHC0312@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>jramirez1483@gmail.com</t>
+  </si>
+  <si>
+    <t>JMRESTREPODUQUE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>jeison.restrepo5280@correopolicia.gov.co</t>
+  </si>
+  <si>
+    <t>auxcontable.arcilaloaizasas@gmail.com</t>
+  </si>
+  <si>
+    <t>RIOSWALTER7@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>wendyyuranypaez2016@gmail.com</t>
+  </si>
+  <si>
+    <t>pablopoderoso@gmail.com</t>
+  </si>
+  <si>
+    <t>litosrueda@gmail.com</t>
+  </si>
+  <si>
+    <t>sergio02marzo@gmail.com</t>
   </si>
   <si>
     <t>estradayerica2430@gmail.com</t>
@@ -406,19 +1696,43 @@
     <t>MONICA.RODASM@GMAIL.COM</t>
   </si>
   <si>
+    <t>RUIZ_CARDONA@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>JUANMARCOS.SAL@GMAIL.COM</t>
+  </si>
+  <si>
     <t>sanabriaandres501@Gmail.com</t>
   </si>
   <si>
+    <t>gerente.magesa@gmail.com</t>
+  </si>
+  <si>
     <t>marthacsanchezj@gmail.com</t>
   </si>
   <si>
-    <t>ss7canada@gmail.com</t>
-  </si>
-  <si>
     <t>VIACEGA@GMAIL.COM</t>
   </si>
   <si>
-    <t>lucianaserna32@gmail.com</t>
+    <t>lilios12@hotmail.com</t>
+  </si>
+  <si>
+    <t>sernalonga@gmail.com</t>
+  </si>
+  <si>
+    <t>JUANCAMILOHERNANDEZHO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>juliocesar@sorza.com</t>
+  </si>
+  <si>
+    <t>samy587@hotmail.com</t>
+  </si>
+  <si>
+    <t>deisyferr@hotmail.com</t>
+  </si>
+  <si>
+    <t>lalamartinezg@hotmail.com</t>
   </si>
   <si>
     <t>sunandbeach88@hotmail.com</t>
@@ -430,7 +1744,16 @@
     <t>HECHIS83@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>admisiones@colombosueco.com</t>
+    <t>USUGA2310@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>sherayvp@gmail.com</t>
+  </si>
+  <si>
+    <t>LAURAORTIZ.PSICOLOGIA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>lauramarcelav@yahoo.es</t>
   </si>
   <si>
     <t>zantana07@gmail.com</t>
@@ -791,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -828,28 +2151,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>275</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>287</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>403</v>
       </c>
       <c r="G2">
-        <v>3137650642</v>
+        <v>3117739445</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>475</v>
       </c>
       <c r="I2">
-        <v>5470470</v>
+        <v>750823</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -857,28 +2180,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>276</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>287</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>403</v>
       </c>
       <c r="G3">
-        <v>3054580820</v>
+        <v>3117739445</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>475</v>
       </c>
       <c r="I3">
-        <v>541564</v>
+        <v>601842</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -886,28 +2209,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>277</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>288</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>404</v>
       </c>
       <c r="G4">
-        <v>3187766267</v>
+        <v>3006800473</v>
       </c>
       <c r="H4" t="s">
-        <v>118</v>
+        <v>476</v>
       </c>
       <c r="I4">
-        <v>560487</v>
+        <v>577752</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -915,28 +2238,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>278</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>289</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>405</v>
       </c>
       <c r="G5">
-        <v>3006153207</v>
+        <v>3105262606</v>
       </c>
       <c r="H5" t="s">
-        <v>119</v>
+        <v>477</v>
       </c>
       <c r="I5">
-        <v>3562726</v>
+        <v>628360</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -944,28 +2267,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>405</v>
       </c>
       <c r="G6">
-        <v>3104067600</v>
+        <v>3105262606</v>
       </c>
       <c r="H6" t="s">
-        <v>120</v>
+        <v>477</v>
       </c>
       <c r="I6">
-        <v>530829</v>
+        <v>613673</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -973,28 +2296,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>289</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="G7">
-        <v>3233179080</v>
+        <v>3105262606</v>
       </c>
       <c r="H7" t="s">
-        <v>121</v>
+        <v>477</v>
       </c>
       <c r="I7">
-        <v>581235</v>
+        <v>598074</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1002,28 +2325,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>278</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>290</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F8" t="s">
-        <v>105</v>
+        <v>406</v>
       </c>
       <c r="G8">
-        <v>3002731587</v>
+        <v>3008146051</v>
       </c>
       <c r="H8" t="s">
-        <v>122</v>
+        <v>478</v>
       </c>
       <c r="I8">
-        <v>804948</v>
+        <v>557982</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1031,28 +2354,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>277</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>406</v>
       </c>
       <c r="G9">
-        <v>3013564721</v>
+        <v>3008146051</v>
       </c>
       <c r="H9" t="s">
-        <v>123</v>
+        <v>478</v>
       </c>
       <c r="I9">
-        <v>2512680</v>
+        <v>577876</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1060,28 +2383,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>276</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="G10">
-        <v>3160524609</v>
+        <v>3226255509</v>
       </c>
       <c r="H10" t="s">
-        <v>124</v>
+        <v>479</v>
       </c>
       <c r="I10">
-        <v>2262772</v>
+        <v>538030</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1089,28 +2412,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>278</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>408</v>
       </c>
       <c r="G11">
-        <v>3116823407</v>
+        <v>3005565956</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>480</v>
       </c>
       <c r="I11">
-        <v>1472088</v>
+        <v>628360</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1118,28 +2441,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>278</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="F12" t="s">
-        <v>107</v>
+        <v>409</v>
       </c>
       <c r="G12">
-        <v>3013620164</v>
+        <v>3187949466</v>
       </c>
       <c r="H12" t="s">
-        <v>126</v>
+        <v>481</v>
       </c>
       <c r="I12">
-        <v>3024840</v>
+        <v>162396</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1147,28 +2470,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>278</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>410</v>
       </c>
       <c r="G13">
-        <v>3233605163</v>
+        <v>3108914534</v>
       </c>
       <c r="H13" t="s">
-        <v>127</v>
+        <v>482</v>
       </c>
       <c r="I13">
-        <v>2709144</v>
+        <v>592342</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1176,28 +2499,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>281</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="G14">
-        <v>3106368274</v>
+        <v>3185029620</v>
       </c>
       <c r="H14" t="s">
-        <v>128</v>
+        <v>483</v>
       </c>
       <c r="I14">
-        <v>2078650</v>
+        <v>1242434</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1205,28 +2528,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>275</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>397</v>
       </c>
       <c r="F15" t="s">
-        <v>109</v>
+        <v>411</v>
       </c>
       <c r="G15">
-        <v>3008674834</v>
+        <v>3185029620</v>
       </c>
       <c r="H15" t="s">
-        <v>129</v>
+        <v>483</v>
       </c>
       <c r="I15">
-        <v>1515860</v>
+        <v>1423984</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1234,28 +2557,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>282</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="F16" t="s">
-        <v>110</v>
+        <v>412</v>
       </c>
       <c r="G16">
-        <v>3022424243</v>
+        <v>3117996256</v>
       </c>
       <c r="H16" t="s">
-        <v>130</v>
+        <v>484</v>
       </c>
       <c r="I16">
-        <v>100000</v>
+        <v>605299</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1263,28 +2586,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>283</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>297</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>413</v>
       </c>
       <c r="G17">
-        <v>3168660548</v>
+        <v>3212776005</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>485</v>
       </c>
       <c r="I17">
-        <v>1771470</v>
+        <v>442660</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1292,28 +2615,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>284</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>298</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>397</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>414</v>
       </c>
       <c r="G18">
-        <v>3028133419</v>
+        <v>3148494120</v>
       </c>
       <c r="H18" t="s">
-        <v>132</v>
+        <v>486</v>
       </c>
       <c r="I18">
-        <v>1196214</v>
+        <v>970720</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1321,28 +2644,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>277</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>299</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
+        <v>415</v>
       </c>
       <c r="G19">
-        <v>3028133419</v>
+        <v>3104067600</v>
       </c>
       <c r="H19" t="s">
-        <v>132</v>
+        <v>487</v>
       </c>
       <c r="I19">
-        <v>635834</v>
+        <v>539856</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1350,28 +2673,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>277</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>300</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F20" t="s">
-        <v>105</v>
+        <v>416</v>
       </c>
       <c r="G20">
-        <v>3207608861</v>
+        <v>3003767391</v>
       </c>
       <c r="H20" t="s">
-        <v>133</v>
+        <v>488</v>
       </c>
       <c r="I20">
-        <v>3542736</v>
+        <v>614324</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1379,28 +2702,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>281</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>301</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F21" t="s">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="G21">
-        <v>3207608861</v>
+        <v>3016959292</v>
       </c>
       <c r="H21" t="s">
-        <v>133</v>
+        <v>489</v>
       </c>
       <c r="I21">
-        <v>5708870</v>
+        <v>1242434</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1408,28 +2731,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>302</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>405</v>
       </c>
       <c r="G22">
-        <v>3207611691</v>
+        <v>3046838460</v>
       </c>
       <c r="H22" t="s">
-        <v>134</v>
+        <v>490</v>
       </c>
       <c r="I22">
-        <v>474335</v>
+        <v>502720</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1437,28 +2760,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>285</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>303</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="F23" t="s">
-        <v>113</v>
+        <v>418</v>
       </c>
       <c r="G23">
-        <v>3205617348</v>
+        <v>3012457263</v>
       </c>
       <c r="H23" t="s">
-        <v>135</v>
+        <v>491</v>
       </c>
       <c r="I23">
-        <v>1314565</v>
+        <v>1007440</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1466,28 +2789,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>284</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>303</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
+        <v>397</v>
       </c>
       <c r="F24" t="s">
-        <v>105</v>
+        <v>418</v>
       </c>
       <c r="G24">
-        <v>3206798318</v>
+        <v>3012457266</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>492</v>
       </c>
       <c r="I24">
-        <v>1405060</v>
+        <v>913296</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1495,28 +2818,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>304</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>397</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>419</v>
       </c>
       <c r="G25">
-        <v>3175795524</v>
+        <v>3233179080</v>
       </c>
       <c r="H25" t="s">
-        <v>137</v>
+        <v>493</v>
       </c>
       <c r="I25">
-        <v>567257</v>
+        <v>1265122</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1524,28 +2847,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>283</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>305</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>397</v>
       </c>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>420</v>
       </c>
       <c r="G26">
-        <v>3104440838</v>
+        <v>3156803375</v>
       </c>
       <c r="H26" t="s">
-        <v>138</v>
+        <v>494</v>
       </c>
       <c r="I26">
-        <v>266341</v>
+        <v>1136976</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1553,28 +2876,3095 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" t="s">
+        <v>283</v>
+      </c>
+      <c r="D27" t="s">
+        <v>306</v>
+      </c>
+      <c r="E27" t="s">
+        <v>397</v>
+      </c>
+      <c r="F27" t="s">
+        <v>421</v>
+      </c>
+      <c r="G27">
+        <v>3045957277</v>
+      </c>
+      <c r="H27" t="s">
+        <v>495</v>
+      </c>
+      <c r="I27">
+        <v>477251</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C28" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" t="s">
+        <v>307</v>
+      </c>
+      <c r="E28" t="s">
+        <v>396</v>
+      </c>
+      <c r="F28" t="s">
+        <v>405</v>
+      </c>
+      <c r="G28">
+        <v>3212412336</v>
+      </c>
+      <c r="H28" t="s">
+        <v>496</v>
+      </c>
+      <c r="I28">
+        <v>612660</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" t="s">
+        <v>308</v>
+      </c>
+      <c r="E29" t="s">
+        <v>397</v>
+      </c>
+      <c r="F29" t="s">
+        <v>422</v>
+      </c>
+      <c r="G29">
+        <v>3143828183</v>
+      </c>
+      <c r="H29" t="s">
+        <v>497</v>
+      </c>
+      <c r="I29">
+        <v>567488</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" t="s">
+        <v>309</v>
+      </c>
+      <c r="E30" t="s">
+        <v>398</v>
+      </c>
+      <c r="F30" t="s">
+        <v>423</v>
+      </c>
+      <c r="G30">
+        <v>3015686911</v>
+      </c>
+      <c r="H30" t="s">
+        <v>498</v>
+      </c>
+      <c r="I30">
+        <v>480060</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31" t="s">
+        <v>309</v>
+      </c>
+      <c r="E31" t="s">
+        <v>398</v>
+      </c>
+      <c r="F31" t="s">
+        <v>423</v>
+      </c>
+      <c r="G31">
+        <v>3015686911</v>
+      </c>
+      <c r="H31" t="s">
+        <v>498</v>
+      </c>
+      <c r="I31">
+        <v>567172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" t="s">
+        <v>310</v>
+      </c>
+      <c r="E32" t="s">
+        <v>397</v>
+      </c>
+      <c r="F32" t="s">
+        <v>405</v>
+      </c>
+      <c r="G32">
+        <v>3116347838</v>
+      </c>
+      <c r="H32" t="s">
+        <v>499</v>
+      </c>
+      <c r="I32">
+        <v>564172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" t="s">
+        <v>281</v>
+      </c>
+      <c r="D33" t="s">
+        <v>311</v>
+      </c>
+      <c r="E33" t="s">
+        <v>397</v>
+      </c>
+      <c r="F33" t="s">
+        <v>424</v>
+      </c>
+      <c r="G33">
+        <v>3103911258</v>
+      </c>
+      <c r="H33" t="s">
+        <v>500</v>
+      </c>
+      <c r="I33">
+        <v>502754</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D34" t="s">
+        <v>312</v>
+      </c>
+      <c r="E34" t="s">
+        <v>399</v>
+      </c>
+      <c r="F34" t="s">
+        <v>405</v>
+      </c>
+      <c r="G34">
+        <v>3219014852</v>
+      </c>
+      <c r="H34" t="s">
+        <v>501</v>
+      </c>
+      <c r="I34">
+        <v>138030</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" t="s">
+        <v>281</v>
+      </c>
+      <c r="D35" t="s">
+        <v>313</v>
+      </c>
+      <c r="E35" t="s">
+        <v>396</v>
+      </c>
+      <c r="F35" t="s">
+        <v>425</v>
+      </c>
+      <c r="G35">
+        <v>3146320382</v>
+      </c>
+      <c r="H35" t="s">
+        <v>502</v>
+      </c>
+      <c r="I35">
+        <v>803508</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D36" t="s">
+        <v>314</v>
+      </c>
+      <c r="E36" t="s">
+        <v>396</v>
+      </c>
+      <c r="F36" t="s">
+        <v>425</v>
+      </c>
+      <c r="G36">
+        <v>3146320382</v>
+      </c>
+      <c r="H36" t="s">
+        <v>502</v>
+      </c>
+      <c r="I36">
+        <v>862598</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D37" t="s">
+        <v>315</v>
+      </c>
+      <c r="E37" t="s">
+        <v>396</v>
+      </c>
+      <c r="F37" t="s">
+        <v>405</v>
+      </c>
+      <c r="G37">
+        <v>3226071559</v>
+      </c>
+      <c r="H37" t="s">
+        <v>503</v>
+      </c>
+      <c r="I37">
+        <v>583472</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" t="s">
+        <v>276</v>
+      </c>
+      <c r="D38" t="s">
+        <v>316</v>
+      </c>
+      <c r="E38" t="s">
+        <v>396</v>
+      </c>
+      <c r="F38" t="s">
+        <v>426</v>
+      </c>
+      <c r="G38">
+        <v>3108384796</v>
+      </c>
+      <c r="H38" t="s">
+        <v>504</v>
+      </c>
+      <c r="I38">
+        <v>506123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C39" t="s">
+        <v>275</v>
+      </c>
+      <c r="D39" t="s">
+        <v>316</v>
+      </c>
+      <c r="E39" t="s">
+        <v>396</v>
+      </c>
+      <c r="F39" t="s">
+        <v>426</v>
+      </c>
+      <c r="G39">
+        <v>3108384796</v>
+      </c>
+      <c r="H39" t="s">
+        <v>504</v>
+      </c>
+      <c r="I39">
+        <v>631330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s">
+        <v>180</v>
+      </c>
+      <c r="C40" t="s">
+        <v>278</v>
+      </c>
+      <c r="D40" t="s">
+        <v>317</v>
+      </c>
+      <c r="E40" t="s">
+        <v>396</v>
+      </c>
+      <c r="F40" t="s">
+        <v>427</v>
+      </c>
+      <c r="G40">
+        <v>3145242166</v>
+      </c>
+      <c r="H40" t="s">
+        <v>505</v>
+      </c>
+      <c r="I40">
+        <v>592342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" t="s">
+        <v>278</v>
+      </c>
+      <c r="D41" t="s">
+        <v>318</v>
+      </c>
+      <c r="E41" t="s">
+        <v>397</v>
+      </c>
+      <c r="F41" t="s">
+        <v>428</v>
+      </c>
+      <c r="G41">
+        <v>3147398657</v>
+      </c>
+      <c r="H41" t="s">
+        <v>506</v>
+      </c>
+      <c r="I41">
+        <v>628360</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" t="s">
+        <v>276</v>
+      </c>
+      <c r="D42" t="s">
+        <v>319</v>
+      </c>
+      <c r="E42" t="s">
+        <v>397</v>
+      </c>
+      <c r="F42" t="s">
+        <v>405</v>
+      </c>
+      <c r="G42">
+        <v>3127328669</v>
+      </c>
+      <c r="H42" t="s">
+        <v>507</v>
+      </c>
+      <c r="I42">
+        <v>573936</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>183</v>
+      </c>
+      <c r="C43" t="s">
+        <v>284</v>
+      </c>
+      <c r="D43" t="s">
+        <v>320</v>
+      </c>
+      <c r="E43" t="s">
+        <v>397</v>
+      </c>
+      <c r="F43" t="s">
+        <v>405</v>
+      </c>
+      <c r="G43">
+        <v>3004353149</v>
+      </c>
+      <c r="H43" t="s">
+        <v>508</v>
+      </c>
+      <c r="I43">
+        <v>484360</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" t="s">
+        <v>184</v>
+      </c>
+      <c r="C44" t="s">
+        <v>285</v>
+      </c>
+      <c r="D44" t="s">
+        <v>321</v>
+      </c>
+      <c r="E44" t="s">
+        <v>396</v>
+      </c>
+      <c r="F44" t="s">
+        <v>429</v>
+      </c>
+      <c r="G44">
+        <v>3046270488</v>
+      </c>
+      <c r="H44" t="s">
+        <v>509</v>
+      </c>
+      <c r="I44">
+        <v>396871</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C45" t="s">
+        <v>283</v>
+      </c>
+      <c r="D45" t="s">
+        <v>321</v>
+      </c>
+      <c r="E45" t="s">
+        <v>396</v>
+      </c>
+      <c r="F45" t="s">
+        <v>429</v>
+      </c>
+      <c r="G45">
+        <v>3046270488</v>
+      </c>
+      <c r="H45" t="s">
+        <v>509</v>
+      </c>
+      <c r="I45">
+        <v>376786</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" t="s">
+        <v>278</v>
+      </c>
+      <c r="D46" t="s">
+        <v>322</v>
+      </c>
+      <c r="E46" t="s">
+        <v>396</v>
+      </c>
+      <c r="F46" t="s">
+        <v>430</v>
+      </c>
+      <c r="G46">
+        <v>3005281616</v>
+      </c>
+      <c r="H46" t="s">
+        <v>510</v>
+      </c>
+      <c r="I46">
+        <v>557982</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D47" t="s">
+        <v>312</v>
+      </c>
+      <c r="E47" t="s">
+        <v>396</v>
+      </c>
+      <c r="F47" t="s">
+        <v>405</v>
+      </c>
+      <c r="G47">
+        <v>3219014852</v>
+      </c>
+      <c r="H47" t="s">
+        <v>501</v>
+      </c>
+      <c r="I47">
+        <v>585486</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" t="s">
+        <v>323</v>
+      </c>
+      <c r="E48" t="s">
+        <v>396</v>
+      </c>
+      <c r="F48" t="s">
+        <v>431</v>
+      </c>
+      <c r="G48">
+        <v>3013531871</v>
+      </c>
+      <c r="H48" t="s">
+        <v>511</v>
+      </c>
+      <c r="I48">
+        <v>484360</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" t="s">
+        <v>282</v>
+      </c>
+      <c r="D49" t="s">
+        <v>323</v>
+      </c>
+      <c r="E49" t="s">
+        <v>396</v>
+      </c>
+      <c r="F49" t="s">
+        <v>431</v>
+      </c>
+      <c r="G49">
+        <v>3013531871</v>
+      </c>
+      <c r="H49" t="s">
+        <v>511</v>
+      </c>
+      <c r="I49">
+        <v>643482</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" t="s">
+        <v>282</v>
+      </c>
+      <c r="D50" t="s">
+        <v>324</v>
+      </c>
+      <c r="E50" t="s">
+        <v>396</v>
+      </c>
+      <c r="F50" t="s">
+        <v>405</v>
+      </c>
+      <c r="G50">
+        <v>3008092108</v>
+      </c>
+      <c r="H50" t="s">
+        <v>512</v>
+      </c>
+      <c r="I50">
+        <v>604598</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C51" t="s">
+        <v>278</v>
+      </c>
+      <c r="D51" t="s">
+        <v>325</v>
+      </c>
+      <c r="E51" t="s">
+        <v>396</v>
+      </c>
+      <c r="F51" t="s">
+        <v>405</v>
+      </c>
+      <c r="G51">
+        <v>3043539006</v>
+      </c>
+      <c r="H51" t="s">
+        <v>513</v>
+      </c>
+      <c r="I51">
+        <v>557982</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" t="s">
+        <v>278</v>
+      </c>
+      <c r="D52" t="s">
+        <v>326</v>
+      </c>
+      <c r="I52">
+        <v>1047586</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
         <v>60</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C53" t="s">
+        <v>283</v>
+      </c>
+      <c r="D53" t="s">
+        <v>327</v>
+      </c>
+      <c r="E53" t="s">
+        <v>396</v>
+      </c>
+      <c r="F53" t="s">
+        <v>432</v>
+      </c>
+      <c r="G53">
+        <v>3102013484</v>
+      </c>
+      <c r="H53" t="s">
+        <v>514</v>
+      </c>
+      <c r="I53">
+        <v>956502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
         <v>61</v>
       </c>
-      <c r="D27" t="s">
+      <c r="B54" t="s">
+        <v>194</v>
+      </c>
+      <c r="C54" t="s">
+        <v>281</v>
+      </c>
+      <c r="D54" t="s">
+        <v>328</v>
+      </c>
+      <c r="E54" t="s">
+        <v>396</v>
+      </c>
+      <c r="F54" t="s">
+        <v>433</v>
+      </c>
+      <c r="G54">
+        <v>3206768830</v>
+      </c>
+      <c r="H54" t="s">
+        <v>515</v>
+      </c>
+      <c r="I54">
+        <v>550754</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" t="s">
+        <v>284</v>
+      </c>
+      <c r="D55" t="s">
+        <v>328</v>
+      </c>
+      <c r="E55" t="s">
+        <v>396</v>
+      </c>
+      <c r="F55" t="s">
+        <v>433</v>
+      </c>
+      <c r="G55">
+        <v>3206768830</v>
+      </c>
+      <c r="H55" t="s">
+        <v>515</v>
+      </c>
+      <c r="I55">
+        <v>455648</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" t="s">
+        <v>282</v>
+      </c>
+      <c r="D56" t="s">
+        <v>329</v>
+      </c>
+      <c r="E56" t="s">
+        <v>396</v>
+      </c>
+      <c r="F56" t="s">
+        <v>405</v>
+      </c>
+      <c r="G56">
+        <v>3177519337</v>
+      </c>
+      <c r="H56" t="s">
+        <v>516</v>
+      </c>
+      <c r="I56">
+        <v>362979</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C57" t="s">
+        <v>286</v>
+      </c>
+      <c r="D57" t="s">
+        <v>329</v>
+      </c>
+      <c r="E57" t="s">
+        <v>396</v>
+      </c>
+      <c r="F57" t="s">
+        <v>405</v>
+      </c>
+      <c r="G57">
+        <v>3177519337</v>
+      </c>
+      <c r="H57" t="s">
+        <v>516</v>
+      </c>
+      <c r="I57">
+        <v>368671</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" t="s">
+        <v>285</v>
+      </c>
+      <c r="D58" t="s">
+        <v>330</v>
+      </c>
+      <c r="E58" t="s">
+        <v>396</v>
+      </c>
+      <c r="F58" t="s">
+        <v>434</v>
+      </c>
+      <c r="G58">
+        <v>3122327344</v>
+      </c>
+      <c r="H58" t="s">
+        <v>517</v>
+      </c>
+      <c r="I58">
+        <v>534411</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" t="s">
+        <v>199</v>
+      </c>
+      <c r="C59" t="s">
+        <v>276</v>
+      </c>
+      <c r="D59" t="s">
+        <v>331</v>
+      </c>
+      <c r="E59" t="s">
+        <v>396</v>
+      </c>
+      <c r="F59" t="s">
+        <v>435</v>
+      </c>
+      <c r="G59">
+        <v>3113200460</v>
+      </c>
+      <c r="H59" t="s">
+        <v>518</v>
+      </c>
+      <c r="I59">
+        <v>778060</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" t="s">
+        <v>200</v>
+      </c>
+      <c r="C60" t="s">
+        <v>276</v>
+      </c>
+      <c r="D60" t="s">
+        <v>332</v>
+      </c>
+      <c r="E60" t="s">
+        <v>397</v>
+      </c>
+      <c r="F60" t="s">
+        <v>436</v>
+      </c>
+      <c r="G60">
+        <v>3136146481</v>
+      </c>
+      <c r="H60" t="s">
+        <v>519</v>
+      </c>
+      <c r="I60">
+        <v>1141872</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C61" t="s">
+        <v>283</v>
+      </c>
+      <c r="D61" t="s">
+        <v>333</v>
+      </c>
+      <c r="E61" t="s">
+        <v>397</v>
+      </c>
+      <c r="F61" t="s">
+        <v>437</v>
+      </c>
+      <c r="G61">
+        <v>3017206508</v>
+      </c>
+      <c r="H61" t="s">
+        <v>520</v>
+      </c>
+      <c r="I61">
+        <v>956502</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
+        <v>202</v>
+      </c>
+      <c r="C62" t="s">
+        <v>281</v>
+      </c>
+      <c r="D62" t="s">
+        <v>334</v>
+      </c>
+      <c r="E62" t="s">
+        <v>396</v>
+      </c>
+      <c r="F62" t="s">
+        <v>438</v>
+      </c>
+      <c r="G62">
+        <v>3113815076</v>
+      </c>
+      <c r="H62" t="s">
+        <v>521</v>
+      </c>
+      <c r="I62">
+        <v>585486</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" t="s">
+        <v>285</v>
+      </c>
+      <c r="D63" t="s">
+        <v>334</v>
+      </c>
+      <c r="E63" t="s">
+        <v>397</v>
+      </c>
+      <c r="F63" t="s">
+        <v>438</v>
+      </c>
+      <c r="G63">
+        <v>3113448104</v>
+      </c>
+      <c r="H63" t="s">
+        <v>522</v>
+      </c>
+      <c r="I63">
+        <v>1070822</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" t="s">
+        <v>204</v>
+      </c>
+      <c r="C64" t="s">
+        <v>280</v>
+      </c>
+      <c r="D64" t="s">
+        <v>335</v>
+      </c>
+      <c r="E64" t="s">
+        <v>396</v>
+      </c>
+      <c r="F64" t="s">
+        <v>439</v>
+      </c>
+      <c r="G64">
+        <v>3113353894</v>
+      </c>
+      <c r="H64" t="s">
+        <v>523</v>
+      </c>
+      <c r="I64">
+        <v>559172</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65" t="s">
+        <v>276</v>
+      </c>
+      <c r="D65" t="s">
+        <v>336</v>
+      </c>
+      <c r="E65" t="s">
+        <v>397</v>
+      </c>
+      <c r="F65" t="s">
+        <v>440</v>
+      </c>
+      <c r="G65">
+        <v>3135319641</v>
+      </c>
+      <c r="H65" t="s">
+        <v>524</v>
+      </c>
+      <c r="I65">
+        <v>538030</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" t="s">
+        <v>206</v>
+      </c>
+      <c r="C66" t="s">
+        <v>286</v>
+      </c>
+      <c r="D66" t="s">
+        <v>337</v>
+      </c>
+      <c r="E66" t="s">
+        <v>396</v>
+      </c>
+      <c r="F66" t="s">
+        <v>405</v>
+      </c>
+      <c r="G66">
+        <v>3022977529</v>
+      </c>
+      <c r="H66" t="s">
+        <v>525</v>
+      </c>
+      <c r="I66">
+        <v>521451</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" t="s">
+        <v>207</v>
+      </c>
+      <c r="C67" t="s">
+        <v>275</v>
+      </c>
+      <c r="D67" t="s">
+        <v>338</v>
+      </c>
+      <c r="E67" t="s">
+        <v>396</v>
+      </c>
+      <c r="F67" t="s">
+        <v>405</v>
+      </c>
+      <c r="G67">
+        <v>3116823407</v>
+      </c>
+      <c r="H67" t="s">
+        <v>526</v>
+      </c>
+      <c r="I67">
+        <v>331330</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" t="s">
+        <v>208</v>
+      </c>
+      <c r="C68" t="s">
+        <v>280</v>
+      </c>
+      <c r="D68" t="s">
+        <v>339</v>
+      </c>
+      <c r="E68" t="s">
+        <v>396</v>
+      </c>
+      <c r="F68" t="s">
+        <v>405</v>
+      </c>
+      <c r="G68">
+        <v>3013807813</v>
+      </c>
+      <c r="H68" t="s">
+        <v>527</v>
+      </c>
+      <c r="I68">
+        <v>1198148</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" t="s">
+        <v>281</v>
+      </c>
+      <c r="D69" t="s">
+        <v>340</v>
+      </c>
+      <c r="E69" t="s">
+        <v>396</v>
+      </c>
+      <c r="F69" t="s">
+        <v>405</v>
+      </c>
+      <c r="G69">
+        <v>3186656220</v>
+      </c>
+      <c r="H69" t="s">
+        <v>528</v>
+      </c>
+      <c r="I69">
+        <v>1172972</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" t="s">
+        <v>210</v>
+      </c>
+      <c r="C70" t="s">
+        <v>284</v>
+      </c>
+      <c r="D70" t="s">
+        <v>341</v>
+      </c>
+      <c r="E70" t="s">
+        <v>396</v>
+      </c>
+      <c r="F70" t="s">
+        <v>441</v>
+      </c>
+      <c r="G70">
+        <v>3003934941</v>
+      </c>
+      <c r="H70" t="s">
+        <v>529</v>
+      </c>
+      <c r="I70">
+        <v>483720</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" t="s">
+        <v>211</v>
+      </c>
+      <c r="C71" t="s">
+        <v>276</v>
+      </c>
+      <c r="D71" t="s">
+        <v>342</v>
+      </c>
+      <c r="E71" t="s">
+        <v>396</v>
+      </c>
+      <c r="F71" t="s">
+        <v>442</v>
+      </c>
+      <c r="G71">
+        <v>3012100135</v>
+      </c>
+      <c r="H71" t="s">
+        <v>530</v>
+      </c>
+      <c r="I71">
+        <v>1141872</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" t="s">
+        <v>212</v>
+      </c>
+      <c r="C72" t="s">
+        <v>283</v>
+      </c>
+      <c r="D72" t="s">
+        <v>343</v>
+      </c>
+      <c r="E72" t="s">
+        <v>397</v>
+      </c>
+      <c r="F72" t="s">
+        <v>443</v>
+      </c>
+      <c r="G72">
+        <v>3135826724</v>
+      </c>
+      <c r="H72" t="s">
+        <v>531</v>
+      </c>
+      <c r="I72">
+        <v>476502</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" t="s">
+        <v>213</v>
+      </c>
+      <c r="C73" t="s">
+        <v>281</v>
+      </c>
+      <c r="D73" t="s">
+        <v>344</v>
+      </c>
+      <c r="E73" t="s">
+        <v>397</v>
+      </c>
+      <c r="F73" t="s">
+        <v>405</v>
+      </c>
+      <c r="G73">
+        <v>3015656941</v>
+      </c>
+      <c r="H73" t="s">
+        <v>532</v>
+      </c>
+      <c r="I73">
+        <v>543508</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" t="s">
+        <v>214</v>
+      </c>
+      <c r="C74" t="s">
+        <v>276</v>
+      </c>
+      <c r="D74" t="s">
+        <v>345</v>
+      </c>
+      <c r="E74" t="s">
+        <v>396</v>
+      </c>
+      <c r="F74" t="s">
+        <v>444</v>
+      </c>
+      <c r="G74">
+        <v>3012195447</v>
+      </c>
+      <c r="H74" t="s">
+        <v>533</v>
+      </c>
+      <c r="I74">
+        <v>506123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" t="s">
+        <v>215</v>
+      </c>
+      <c r="C75" t="s">
+        <v>281</v>
+      </c>
+      <c r="D75" t="s">
+        <v>346</v>
+      </c>
+      <c r="E75" t="s">
+        <v>397</v>
+      </c>
+      <c r="F75" t="s">
+        <v>405</v>
+      </c>
+      <c r="G75">
+        <v>3108364195</v>
+      </c>
+      <c r="H75" t="s">
+        <v>534</v>
+      </c>
+      <c r="I75">
+        <v>527137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" t="s">
+        <v>216</v>
+      </c>
+      <c r="C76" t="s">
+        <v>283</v>
+      </c>
+      <c r="D76" t="s">
+        <v>347</v>
+      </c>
+      <c r="E76" t="s">
+        <v>396</v>
+      </c>
+      <c r="F76" t="s">
+        <v>445</v>
+      </c>
+      <c r="G76">
+        <v>3015954319</v>
+      </c>
+      <c r="H76" t="s">
+        <v>535</v>
+      </c>
+      <c r="I76">
+        <v>1016660</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" t="s">
+        <v>217</v>
+      </c>
+      <c r="C77" t="s">
+        <v>278</v>
+      </c>
+      <c r="D77" t="s">
+        <v>348</v>
+      </c>
+      <c r="E77" t="s">
+        <v>396</v>
+      </c>
+      <c r="F77" t="s">
+        <v>446</v>
+      </c>
+      <c r="G77">
+        <v>3104076628</v>
+      </c>
+      <c r="H77" t="s">
+        <v>536</v>
+      </c>
+      <c r="I77">
+        <v>593171</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" t="s">
+        <v>218</v>
+      </c>
+      <c r="C78" t="s">
+        <v>282</v>
+      </c>
+      <c r="D78" t="s">
+        <v>349</v>
+      </c>
+      <c r="E78" t="s">
+        <v>396</v>
+      </c>
+      <c r="F78" t="s">
+        <v>447</v>
+      </c>
+      <c r="G78">
+        <v>3006234263</v>
+      </c>
+      <c r="H78" t="s">
+        <v>537</v>
+      </c>
+      <c r="I78">
+        <v>1441698</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" t="s">
+        <v>219</v>
+      </c>
+      <c r="C79" t="s">
+        <v>280</v>
+      </c>
+      <c r="D79" t="s">
+        <v>349</v>
+      </c>
+      <c r="E79" t="s">
+        <v>396</v>
+      </c>
+      <c r="F79" t="s">
+        <v>447</v>
+      </c>
+      <c r="G79">
+        <v>3006234263</v>
+      </c>
+      <c r="H79" t="s">
+        <v>537</v>
+      </c>
+      <c r="I79">
+        <v>1265122</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" t="s">
+        <v>220</v>
+      </c>
+      <c r="C80" t="s">
+        <v>283</v>
+      </c>
+      <c r="D80" t="s">
+        <v>350</v>
+      </c>
+      <c r="E80" t="s">
+        <v>396</v>
+      </c>
+      <c r="F80" t="s">
+        <v>421</v>
+      </c>
+      <c r="G80">
+        <v>3052428112</v>
+      </c>
+      <c r="H80" t="s">
+        <v>538</v>
+      </c>
+      <c r="I80">
+        <v>256660</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" t="s">
+        <v>221</v>
+      </c>
+      <c r="C81" t="s">
+        <v>280</v>
+      </c>
+      <c r="D81" t="s">
+        <v>351</v>
+      </c>
+      <c r="E81" t="s">
+        <v>397</v>
+      </c>
+      <c r="F81" t="s">
+        <v>448</v>
+      </c>
+      <c r="G81">
+        <v>3506697092</v>
+      </c>
+      <c r="H81" t="s">
+        <v>539</v>
+      </c>
+      <c r="I81">
+        <v>564586</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" t="s">
+        <v>222</v>
+      </c>
+      <c r="C82" t="s">
+        <v>277</v>
+      </c>
+      <c r="D82" t="s">
+        <v>352</v>
+      </c>
+      <c r="E82" t="s">
+        <v>396</v>
+      </c>
+      <c r="F82" t="s">
+        <v>449</v>
+      </c>
+      <c r="G82">
+        <v>3166226027</v>
+      </c>
+      <c r="H82" t="s">
+        <v>540</v>
+      </c>
+      <c r="I82">
+        <v>614324</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" t="s">
+        <v>223</v>
+      </c>
+      <c r="C83" t="s">
+        <v>284</v>
+      </c>
+      <c r="D83" t="s">
+        <v>353</v>
+      </c>
+      <c r="E83" t="s">
+        <v>396</v>
+      </c>
+      <c r="F83" t="s">
+        <v>450</v>
+      </c>
+      <c r="G83">
+        <v>3147159077</v>
+      </c>
+      <c r="H83" t="s">
+        <v>541</v>
+      </c>
+      <c r="I83">
+        <v>484360</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" t="s">
+        <v>224</v>
+      </c>
+      <c r="C84" t="s">
+        <v>280</v>
+      </c>
+      <c r="D84" t="s">
+        <v>354</v>
+      </c>
+      <c r="E84" t="s">
+        <v>396</v>
+      </c>
+      <c r="F84" t="s">
+        <v>451</v>
+      </c>
+      <c r="G84">
+        <v>3184398000</v>
+      </c>
+      <c r="H84" t="s">
+        <v>542</v>
+      </c>
+      <c r="I84">
+        <v>598074</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" t="s">
+        <v>278</v>
+      </c>
+      <c r="D85" t="s">
+        <v>355</v>
+      </c>
+      <c r="E85" t="s">
+        <v>397</v>
+      </c>
+      <c r="F85" t="s">
+        <v>405</v>
+      </c>
+      <c r="G85">
+        <v>5614641026</v>
+      </c>
+      <c r="H85" t="s">
+        <v>543</v>
+      </c>
+      <c r="I85">
+        <v>591342</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" t="s">
+        <v>226</v>
+      </c>
+      <c r="C86" t="s">
+        <v>285</v>
+      </c>
+      <c r="D86" t="s">
+        <v>356</v>
+      </c>
+      <c r="E86" t="s">
+        <v>396</v>
+      </c>
+      <c r="F86" t="s">
+        <v>452</v>
+      </c>
+      <c r="G86">
+        <v>3122962941</v>
+      </c>
+      <c r="H86" t="s">
+        <v>544</v>
+      </c>
+      <c r="I86">
+        <v>534411</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
         <v>94</v>
       </c>
-      <c r="E27" t="s">
+      <c r="B87" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" t="s">
+        <v>276</v>
+      </c>
+      <c r="D87" t="s">
+        <v>357</v>
+      </c>
+      <c r="E87" t="s">
+        <v>396</v>
+      </c>
+      <c r="F87" t="s">
+        <v>405</v>
+      </c>
+      <c r="G87">
+        <v>3168316927</v>
+      </c>
+      <c r="H87" t="s">
+        <v>545</v>
+      </c>
+      <c r="I87">
+        <v>569872</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" t="s">
+        <v>228</v>
+      </c>
+      <c r="C88" t="s">
+        <v>278</v>
+      </c>
+      <c r="D88" t="s">
+        <v>358</v>
+      </c>
+      <c r="E88" t="s">
+        <v>397</v>
+      </c>
+      <c r="F88" t="s">
+        <v>453</v>
+      </c>
+      <c r="G88">
+        <v>3177063250</v>
+      </c>
+      <c r="H88" t="s">
+        <v>546</v>
+      </c>
+      <c r="I88">
+        <v>663548</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" t="s">
+        <v>229</v>
+      </c>
+      <c r="C89" t="s">
+        <v>282</v>
+      </c>
+      <c r="D89" t="s">
+        <v>359</v>
+      </c>
+      <c r="E89" t="s">
+        <v>396</v>
+      </c>
+      <c r="F89" t="s">
+        <v>454</v>
+      </c>
+      <c r="G89">
+        <v>3178333446</v>
+      </c>
+      <c r="H89" t="s">
+        <v>547</v>
+      </c>
+      <c r="I89">
+        <v>1212598</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" t="s">
+        <v>230</v>
+      </c>
+      <c r="C90" t="s">
+        <v>281</v>
+      </c>
+      <c r="D90" t="s">
+        <v>359</v>
+      </c>
+      <c r="E90" t="s">
+        <v>396</v>
+      </c>
+      <c r="F90" t="s">
+        <v>454</v>
+      </c>
+      <c r="G90">
+        <v>3178333446</v>
+      </c>
+      <c r="H90" t="s">
+        <v>547</v>
+      </c>
+      <c r="I90">
+        <v>1103508</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
         <v>98</v>
       </c>
-      <c r="F27" t="s">
+      <c r="B91" t="s">
+        <v>231</v>
+      </c>
+      <c r="C91" t="s">
+        <v>285</v>
+      </c>
+      <c r="D91" t="s">
+        <v>360</v>
+      </c>
+      <c r="E91" t="s">
+        <v>397</v>
+      </c>
+      <c r="F91" t="s">
+        <v>405</v>
+      </c>
+      <c r="G91">
+        <v>3226367303</v>
+      </c>
+      <c r="H91" t="s">
+        <v>548</v>
+      </c>
+      <c r="I91">
+        <v>1007440</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" t="s">
+        <v>232</v>
+      </c>
+      <c r="C92" t="s">
+        <v>281</v>
+      </c>
+      <c r="D92" t="s">
+        <v>361</v>
+      </c>
+      <c r="E92" t="s">
+        <v>397</v>
+      </c>
+      <c r="F92" t="s">
+        <v>405</v>
+      </c>
+      <c r="G92">
+        <v>3175177575</v>
+      </c>
+      <c r="H92" t="s">
+        <v>549</v>
+      </c>
+      <c r="I92">
+        <v>585486</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" t="s">
+        <v>233</v>
+      </c>
+      <c r="C93" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" t="s">
+        <v>362</v>
+      </c>
+      <c r="E93" t="s">
+        <v>397</v>
+      </c>
+      <c r="F93" t="s">
+        <v>455</v>
+      </c>
+      <c r="G93">
+        <v>3006019149</v>
+      </c>
+      <c r="H93" t="s">
+        <v>550</v>
+      </c>
+      <c r="I93">
+        <v>569936</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>234</v>
+      </c>
+      <c r="C94" t="s">
+        <v>282</v>
+      </c>
+      <c r="D94" t="s">
+        <v>363</v>
+      </c>
+      <c r="E94" t="s">
+        <v>400</v>
+      </c>
+      <c r="F94" t="s">
+        <v>456</v>
+      </c>
+      <c r="G94">
+        <v>3112860092</v>
+      </c>
+      <c r="H94" t="s">
+        <v>551</v>
+      </c>
+      <c r="I94">
+        <v>609299</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" t="s">
+        <v>235</v>
+      </c>
+      <c r="C95" t="s">
+        <v>285</v>
+      </c>
+      <c r="D95" t="s">
+        <v>363</v>
+      </c>
+      <c r="E95" t="s">
+        <v>401</v>
+      </c>
+      <c r="F95" t="s">
+        <v>456</v>
+      </c>
+      <c r="G95">
+        <v>3112860092</v>
+      </c>
+      <c r="H95" t="s">
+        <v>551</v>
+      </c>
+      <c r="I95">
+        <v>506720</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" t="s">
+        <v>236</v>
+      </c>
+      <c r="C96" t="s">
+        <v>280</v>
+      </c>
+      <c r="D96" t="s">
+        <v>364</v>
+      </c>
+      <c r="E96" t="s">
+        <v>396</v>
+      </c>
+      <c r="F96" t="s">
+        <v>457</v>
+      </c>
+      <c r="G96">
+        <v>3113681582</v>
+      </c>
+      <c r="H96" t="s">
+        <v>552</v>
+      </c>
+      <c r="I96">
+        <v>531099</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" t="s">
+        <v>237</v>
+      </c>
+      <c r="C97" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" t="s">
+        <v>365</v>
+      </c>
+      <c r="E97" t="s">
+        <v>397</v>
+      </c>
+      <c r="F97" t="s">
+        <v>458</v>
+      </c>
+      <c r="G97">
+        <v>3053761653</v>
+      </c>
+      <c r="H97" t="s">
+        <v>553</v>
+      </c>
+      <c r="I97">
+        <v>569936</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
         <v>105</v>
       </c>
-      <c r="G27">
+      <c r="B98" t="s">
+        <v>238</v>
+      </c>
+      <c r="C98" t="s">
+        <v>278</v>
+      </c>
+      <c r="D98" t="s">
+        <v>366</v>
+      </c>
+      <c r="E98" t="s">
+        <v>396</v>
+      </c>
+      <c r="F98" t="s">
+        <v>405</v>
+      </c>
+      <c r="G98">
+        <v>3108699380</v>
+      </c>
+      <c r="H98" t="s">
+        <v>554</v>
+      </c>
+      <c r="I98">
+        <v>628360</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" t="s">
+        <v>239</v>
+      </c>
+      <c r="C99" t="s">
+        <v>286</v>
+      </c>
+      <c r="D99" t="s">
+        <v>366</v>
+      </c>
+      <c r="E99" t="s">
+        <v>396</v>
+      </c>
+      <c r="F99" t="s">
+        <v>405</v>
+      </c>
+      <c r="G99">
+        <v>3108699380</v>
+      </c>
+      <c r="H99" t="s">
+        <v>554</v>
+      </c>
+      <c r="I99">
+        <v>587205</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" t="s">
+        <v>240</v>
+      </c>
+      <c r="C100" t="s">
+        <v>277</v>
+      </c>
+      <c r="D100" t="s">
+        <v>367</v>
+      </c>
+      <c r="E100" t="s">
+        <v>396</v>
+      </c>
+      <c r="F100" t="s">
+        <v>459</v>
+      </c>
+      <c r="G100">
+        <v>3022703240</v>
+      </c>
+      <c r="H100" t="s">
+        <v>555</v>
+      </c>
+      <c r="I100">
+        <v>1303544</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" t="s">
+        <v>241</v>
+      </c>
+      <c r="C101" t="s">
+        <v>282</v>
+      </c>
+      <c r="D101" t="s">
+        <v>368</v>
+      </c>
+      <c r="E101" t="s">
+        <v>397</v>
+      </c>
+      <c r="F101" t="s">
+        <v>460</v>
+      </c>
+      <c r="G101">
+        <v>3508996381</v>
+      </c>
+      <c r="H101" t="s">
+        <v>556</v>
+      </c>
+      <c r="I101">
+        <v>643482</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" t="s">
+        <v>242</v>
+      </c>
+      <c r="C102" t="s">
+        <v>285</v>
+      </c>
+      <c r="D102" t="s">
+        <v>368</v>
+      </c>
+      <c r="E102" t="s">
+        <v>397</v>
+      </c>
+      <c r="F102" t="s">
+        <v>460</v>
+      </c>
+      <c r="G102">
+        <v>3508996381</v>
+      </c>
+      <c r="H102" t="s">
+        <v>556</v>
+      </c>
+      <c r="I102">
+        <v>534411</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" t="s">
+        <v>243</v>
+      </c>
+      <c r="C103" t="s">
+        <v>283</v>
+      </c>
+      <c r="D103" t="s">
+        <v>369</v>
+      </c>
+      <c r="E103" t="s">
+        <v>400</v>
+      </c>
+      <c r="F103" t="s">
+        <v>405</v>
+      </c>
+      <c r="G103">
+        <v>3194309799</v>
+      </c>
+      <c r="H103" t="s">
+        <v>557</v>
+      </c>
+      <c r="I103">
+        <v>706502</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" t="s">
+        <v>244</v>
+      </c>
+      <c r="C104" t="s">
+        <v>284</v>
+      </c>
+      <c r="D104" t="s">
+        <v>370</v>
+      </c>
+      <c r="E104" t="s">
+        <v>396</v>
+      </c>
+      <c r="F104" t="s">
+        <v>405</v>
+      </c>
+      <c r="G104">
+        <v>3106368274</v>
+      </c>
+      <c r="H104" t="s">
+        <v>558</v>
+      </c>
+      <c r="I104">
+        <v>970720</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" t="s">
+        <v>245</v>
+      </c>
+      <c r="C105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D105" t="s">
+        <v>371</v>
+      </c>
+      <c r="E105" t="s">
+        <v>396</v>
+      </c>
+      <c r="F105" t="s">
+        <v>461</v>
+      </c>
+      <c r="G105">
+        <v>3008674834</v>
+      </c>
+      <c r="H105" t="s">
+        <v>559</v>
+      </c>
+      <c r="I105">
+        <v>483720</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" t="s">
+        <v>246</v>
+      </c>
+      <c r="C106" t="s">
+        <v>276</v>
+      </c>
+      <c r="D106" t="s">
+        <v>372</v>
+      </c>
+      <c r="E106" t="s">
+        <v>397</v>
+      </c>
+      <c r="F106" t="s">
+        <v>462</v>
+      </c>
+      <c r="G106">
+        <v>3002900521</v>
+      </c>
+      <c r="H106" t="s">
+        <v>560</v>
+      </c>
+      <c r="I106">
+        <v>538030</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" t="s">
+        <v>247</v>
+      </c>
+      <c r="C107" t="s">
+        <v>275</v>
+      </c>
+      <c r="D107" t="s">
+        <v>372</v>
+      </c>
+      <c r="E107" t="s">
+        <v>397</v>
+      </c>
+      <c r="F107" t="s">
+        <v>462</v>
+      </c>
+      <c r="G107">
+        <v>3002900521</v>
+      </c>
+      <c r="H107" t="s">
+        <v>560</v>
+      </c>
+      <c r="I107">
+        <v>671161</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" t="s">
+        <v>248</v>
+      </c>
+      <c r="C108" t="s">
+        <v>283</v>
+      </c>
+      <c r="D108" t="s">
+        <v>373</v>
+      </c>
+      <c r="E108" t="s">
+        <v>397</v>
+      </c>
+      <c r="F108" t="s">
+        <v>463</v>
+      </c>
+      <c r="G108">
+        <v>3154129094</v>
+      </c>
+      <c r="H108" t="s">
+        <v>561</v>
+      </c>
+      <c r="I108">
+        <v>429726</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>116</v>
+      </c>
+      <c r="B109" t="s">
+        <v>249</v>
+      </c>
+      <c r="C109" t="s">
+        <v>277</v>
+      </c>
+      <c r="D109" t="s">
+        <v>374</v>
+      </c>
+      <c r="E109" t="s">
+        <v>397</v>
+      </c>
+      <c r="F109" t="s">
+        <v>464</v>
+      </c>
+      <c r="G109">
+        <v>3022424243</v>
+      </c>
+      <c r="H109" t="s">
+        <v>562</v>
+      </c>
+      <c r="I109">
+        <v>800648</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" t="s">
+        <v>250</v>
+      </c>
+      <c r="C110" t="s">
+        <v>276</v>
+      </c>
+      <c r="D110" t="s">
+        <v>375</v>
+      </c>
+      <c r="E110" t="s">
+        <v>397</v>
+      </c>
+      <c r="F110" t="s">
+        <v>465</v>
+      </c>
+      <c r="G110">
+        <v>3127382747</v>
+      </c>
+      <c r="H110" t="s">
+        <v>563</v>
+      </c>
+      <c r="I110">
+        <v>506123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" t="s">
+        <v>251</v>
+      </c>
+      <c r="C111" t="s">
+        <v>281</v>
+      </c>
+      <c r="D111" t="s">
+        <v>375</v>
+      </c>
+      <c r="E111" t="s">
+        <v>397</v>
+      </c>
+      <c r="F111" t="s">
+        <v>465</v>
+      </c>
+      <c r="G111">
+        <v>3127382747</v>
+      </c>
+      <c r="H111" t="s">
+        <v>563</v>
+      </c>
+      <c r="I111">
+        <v>550754</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" t="s">
+        <v>252</v>
+      </c>
+      <c r="C112" t="s">
+        <v>282</v>
+      </c>
+      <c r="D112" t="s">
+        <v>376</v>
+      </c>
+      <c r="E112" t="s">
+        <v>396</v>
+      </c>
+      <c r="F112" t="s">
+        <v>405</v>
+      </c>
+      <c r="G112">
+        <v>3168660548</v>
+      </c>
+      <c r="H112" t="s">
+        <v>564</v>
+      </c>
+      <c r="I112">
+        <v>1212598</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" t="s">
+        <v>275</v>
+      </c>
+      <c r="D113" t="s">
+        <v>377</v>
+      </c>
+      <c r="E113" t="s">
+        <v>396</v>
+      </c>
+      <c r="F113" t="s">
+        <v>405</v>
+      </c>
+      <c r="G113">
+        <v>3207608861</v>
+      </c>
+      <c r="H113" t="s">
+        <v>565</v>
+      </c>
+      <c r="I113">
+        <v>1423984</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" t="s">
+        <v>285</v>
+      </c>
+      <c r="D114" t="s">
+        <v>378</v>
+      </c>
+      <c r="E114" t="s">
+        <v>396</v>
+      </c>
+      <c r="F114" t="s">
+        <v>405</v>
+      </c>
+      <c r="G114">
+        <v>3207608861</v>
+      </c>
+      <c r="H114" t="s">
+        <v>565</v>
+      </c>
+      <c r="I114">
+        <v>1134204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" t="s">
+        <v>255</v>
+      </c>
+      <c r="C115" t="s">
+        <v>281</v>
+      </c>
+      <c r="D115" t="s">
+        <v>379</v>
+      </c>
+      <c r="E115" t="s">
+        <v>396</v>
+      </c>
+      <c r="F115" t="s">
+        <v>466</v>
+      </c>
+      <c r="G115">
+        <v>3148214908</v>
+      </c>
+      <c r="H115" t="s">
+        <v>566</v>
+      </c>
+      <c r="I115">
+        <v>1172972</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" t="s">
+        <v>256</v>
+      </c>
+      <c r="C116" t="s">
+        <v>283</v>
+      </c>
+      <c r="D116" t="s">
+        <v>379</v>
+      </c>
+      <c r="E116" t="s">
+        <v>396</v>
+      </c>
+      <c r="F116" t="s">
+        <v>466</v>
+      </c>
+      <c r="G116">
+        <v>3148214908</v>
+      </c>
+      <c r="H116" t="s">
+        <v>566</v>
+      </c>
+      <c r="I116">
+        <v>1016660</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" t="s">
+        <v>257</v>
+      </c>
+      <c r="C117" t="s">
+        <v>282</v>
+      </c>
+      <c r="D117" t="s">
+        <v>380</v>
+      </c>
+      <c r="E117" t="s">
+        <v>399</v>
+      </c>
+      <c r="F117" t="s">
+        <v>405</v>
+      </c>
+      <c r="G117">
+        <v>3108331104</v>
+      </c>
+      <c r="H117" t="s">
+        <v>567</v>
+      </c>
+      <c r="I117">
+        <v>388880</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" t="s">
+        <v>258</v>
+      </c>
+      <c r="C118" t="s">
+        <v>285</v>
+      </c>
+      <c r="D118" t="s">
+        <v>381</v>
+      </c>
+      <c r="E118" t="s">
+        <v>397</v>
+      </c>
+      <c r="F118" t="s">
+        <v>467</v>
+      </c>
+      <c r="G118">
+        <v>3003438170</v>
+      </c>
+      <c r="H118" t="s">
+        <v>568</v>
+      </c>
+      <c r="I118">
+        <v>452720</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" t="s">
+        <v>259</v>
+      </c>
+      <c r="C119" t="s">
+        <v>278</v>
+      </c>
+      <c r="D119" t="s">
+        <v>382</v>
+      </c>
+      <c r="E119" t="s">
+        <v>397</v>
+      </c>
+      <c r="F119" t="s">
+        <v>405</v>
+      </c>
+      <c r="G119">
+        <v>3004608087</v>
+      </c>
+      <c r="H119" t="s">
+        <v>569</v>
+      </c>
+      <c r="I119">
+        <v>1047586</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" t="s">
+        <v>260</v>
+      </c>
+      <c r="C120" t="s">
+        <v>281</v>
+      </c>
+      <c r="D120" t="s">
+        <v>382</v>
+      </c>
+      <c r="E120" t="s">
+        <v>397</v>
+      </c>
+      <c r="F120" t="s">
+        <v>405</v>
+      </c>
+      <c r="G120">
+        <v>3004608087</v>
+      </c>
+      <c r="H120" t="s">
+        <v>569</v>
+      </c>
+      <c r="I120">
+        <v>1034046</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" t="s">
+        <v>261</v>
+      </c>
+      <c r="C121" t="s">
+        <v>280</v>
+      </c>
+      <c r="D121" t="s">
+        <v>383</v>
+      </c>
+      <c r="E121" t="s">
+        <v>396</v>
+      </c>
+      <c r="F121" t="s">
+        <v>468</v>
+      </c>
+      <c r="G121">
+        <v>3115341734</v>
+      </c>
+      <c r="H121" t="s">
+        <v>570</v>
+      </c>
+      <c r="I121">
+        <v>1131172</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" t="s">
+        <v>262</v>
+      </c>
+      <c r="C122" t="s">
+        <v>285</v>
+      </c>
+      <c r="D122" t="s">
+        <v>384</v>
+      </c>
+      <c r="E122" t="s">
+        <v>396</v>
+      </c>
+      <c r="F122" t="s">
+        <v>469</v>
+      </c>
+      <c r="G122">
+        <v>3008765266</v>
+      </c>
+      <c r="H122" t="s">
+        <v>571</v>
+      </c>
+      <c r="I122">
+        <v>374688</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" t="s">
+        <v>263</v>
+      </c>
+      <c r="C123" t="s">
+        <v>284</v>
+      </c>
+      <c r="D123" t="s">
+        <v>384</v>
+      </c>
+      <c r="E123" t="s">
+        <v>396</v>
+      </c>
+      <c r="F123" t="s">
+        <v>469</v>
+      </c>
+      <c r="G123">
+        <v>3008765266</v>
+      </c>
+      <c r="H123" t="s">
+        <v>571</v>
+      </c>
+      <c r="I123">
+        <v>339652</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" t="s">
+        <v>264</v>
+      </c>
+      <c r="C124" t="s">
+        <v>278</v>
+      </c>
+      <c r="D124" t="s">
+        <v>385</v>
+      </c>
+      <c r="E124" t="s">
+        <v>396</v>
+      </c>
+      <c r="F124" t="s">
+        <v>470</v>
+      </c>
+      <c r="G124">
+        <v>3206353393</v>
+      </c>
+      <c r="H124" t="s">
+        <v>572</v>
+      </c>
+      <c r="I124">
+        <v>557982</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" t="s">
+        <v>265</v>
+      </c>
+      <c r="C125" t="s">
+        <v>278</v>
+      </c>
+      <c r="D125" t="s">
+        <v>386</v>
+      </c>
+      <c r="E125" t="s">
+        <v>396</v>
+      </c>
+      <c r="F125" t="s">
+        <v>471</v>
+      </c>
+      <c r="G125">
+        <v>3205617348</v>
+      </c>
+      <c r="H125" t="s">
+        <v>573</v>
+      </c>
+      <c r="I125">
+        <v>593171</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" t="s">
+        <v>266</v>
+      </c>
+      <c r="C126" t="s">
+        <v>285</v>
+      </c>
+      <c r="D126" t="s">
+        <v>387</v>
+      </c>
+      <c r="E126" t="s">
+        <v>397</v>
+      </c>
+      <c r="F126" t="s">
+        <v>405</v>
+      </c>
+      <c r="G126">
+        <v>3206798318</v>
+      </c>
+      <c r="H126" t="s">
+        <v>574</v>
+      </c>
+      <c r="I126">
+        <v>899987</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" t="s">
+        <v>267</v>
+      </c>
+      <c r="C127" t="s">
+        <v>277</v>
+      </c>
+      <c r="D127" t="s">
+        <v>388</v>
+      </c>
+      <c r="E127" t="s">
+        <v>397</v>
+      </c>
+      <c r="F127" t="s">
+        <v>472</v>
+      </c>
+      <c r="G127">
+        <v>3175795524</v>
+      </c>
+      <c r="H127" t="s">
+        <v>575</v>
+      </c>
+      <c r="I127">
+        <v>650772</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>135</v>
+      </c>
+      <c r="B128" t="s">
+        <v>268</v>
+      </c>
+      <c r="C128" t="s">
+        <v>276</v>
+      </c>
+      <c r="D128" t="s">
+        <v>389</v>
+      </c>
+      <c r="E128" t="s">
+        <v>397</v>
+      </c>
+      <c r="F128" t="s">
+        <v>405</v>
+      </c>
+      <c r="G128">
+        <v>3116803238</v>
+      </c>
+      <c r="H128" t="s">
+        <v>576</v>
+      </c>
+      <c r="I128">
+        <v>506123</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" t="s">
+        <v>269</v>
+      </c>
+      <c r="C129" t="s">
+        <v>278</v>
+      </c>
+      <c r="D129" t="s">
+        <v>390</v>
+      </c>
+      <c r="I129">
+        <v>1329096</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" t="s">
+        <v>270</v>
+      </c>
+      <c r="C130" t="s">
+        <v>278</v>
+      </c>
+      <c r="D130" t="s">
+        <v>391</v>
+      </c>
+      <c r="E130" t="s">
+        <v>396</v>
+      </c>
+      <c r="F130" t="s">
+        <v>405</v>
+      </c>
+      <c r="G130">
+        <v>3128021315</v>
+      </c>
+      <c r="H130" t="s">
+        <v>577</v>
+      </c>
+      <c r="I130">
+        <v>1047586</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>138</v>
+      </c>
+      <c r="B131" t="s">
+        <v>271</v>
+      </c>
+      <c r="C131" t="s">
+        <v>281</v>
+      </c>
+      <c r="D131" t="s">
+        <v>392</v>
+      </c>
+      <c r="E131" t="s">
+        <v>396</v>
+      </c>
+      <c r="F131" t="s">
+        <v>473</v>
+      </c>
+      <c r="G131">
+        <v>3002799011</v>
+      </c>
+      <c r="H131" t="s">
+        <v>578</v>
+      </c>
+      <c r="I131">
+        <v>1034046</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" t="s">
+        <v>272</v>
+      </c>
+      <c r="C132" t="s">
+        <v>283</v>
+      </c>
+      <c r="D132" t="s">
+        <v>393</v>
+      </c>
+      <c r="E132" t="s">
+        <v>396</v>
+      </c>
+      <c r="F132" t="s">
+        <v>474</v>
+      </c>
+      <c r="G132">
+        <v>3113582464</v>
+      </c>
+      <c r="H132" t="s">
+        <v>579</v>
+      </c>
+      <c r="I132">
+        <v>477251</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" t="s">
+        <v>273</v>
+      </c>
+      <c r="C133" t="s">
+        <v>278</v>
+      </c>
+      <c r="D133" t="s">
+        <v>394</v>
+      </c>
+      <c r="I133">
+        <v>143171</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" t="s">
+        <v>274</v>
+      </c>
+      <c r="C134" t="s">
+        <v>282</v>
+      </c>
+      <c r="D134" t="s">
+        <v>395</v>
+      </c>
+      <c r="E134" t="s">
+        <v>402</v>
+      </c>
+      <c r="F134" t="s">
+        <v>405</v>
+      </c>
+      <c r="G134">
         <v>3003183744</v>
       </c>
-      <c r="H27" t="s">
-        <v>139</v>
-      </c>
-      <c r="I27">
-        <v>2380588</v>
+      <c r="H134" t="s">
+        <v>580</v>
+      </c>
+      <c r="I134">
+        <v>605299</v>
       </c>
     </row>
   </sheetData>

--- a/Morosos/informe_reporte_morosos_50.xlsx
+++ b/Morosos/informe_reporte_morosos_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="341">
   <si>
     <t>identificacion</t>
   </si>
@@ -43,15 +43,15 @@
     <t>deuda total</t>
   </si>
   <si>
-    <t>1192469248</t>
-  </si>
-  <si>
-    <t>1192466240</t>
-  </si>
-  <si>
     <t>1036521142</t>
   </si>
   <si>
+    <t>1025661559</t>
+  </si>
+  <si>
+    <t>1035424821</t>
+  </si>
+  <si>
     <t>1021940719</t>
   </si>
   <si>
@@ -61,112 +61,82 @@
     <t>1011519538</t>
   </si>
   <si>
-    <t>1020319550</t>
-  </si>
-  <si>
-    <t>1192467267</t>
-  </si>
-  <si>
-    <t>1020317989</t>
+    <t>1020322501</t>
+  </si>
+  <si>
+    <t>1020327607</t>
+  </si>
+  <si>
+    <t>1020317655</t>
   </si>
   <si>
     <t>1033198496</t>
   </si>
   <si>
-    <t>1011515041</t>
-  </si>
-  <si>
     <t>1037130310</t>
   </si>
   <si>
+    <t>1013464926</t>
+  </si>
+  <si>
     <t>1013466654</t>
   </si>
   <si>
-    <t>1023540172</t>
+    <t>1025657990</t>
+  </si>
+  <si>
+    <t>1023165980</t>
   </si>
   <si>
     <t>1013358746</t>
   </si>
   <si>
-    <t>1020323596</t>
-  </si>
-  <si>
-    <t>1021935485</t>
-  </si>
-  <si>
-    <t>1033192943</t>
-  </si>
-  <si>
     <t>1025898446</t>
   </si>
   <si>
+    <t>1025895387</t>
+  </si>
+  <si>
     <t>1035003747</t>
   </si>
   <si>
-    <t>1021933529</t>
-  </si>
-  <si>
     <t>1202213225</t>
   </si>
   <si>
+    <t>1025678788</t>
+  </si>
+  <si>
+    <t>1023550049</t>
+  </si>
+  <si>
+    <t>1021930204</t>
+  </si>
+  <si>
     <t>1011515086</t>
   </si>
   <si>
-    <t>1038872200</t>
-  </si>
-  <si>
-    <t>1038873057</t>
-  </si>
-  <si>
-    <t>1020230331</t>
-  </si>
-  <si>
-    <t>1023554520</t>
-  </si>
-  <si>
-    <t>1020319583</t>
-  </si>
-  <si>
-    <t>1011412933</t>
-  </si>
-  <si>
-    <t>1018254177</t>
-  </si>
-  <si>
     <t>1013353521</t>
   </si>
   <si>
     <t>1013362371</t>
   </si>
   <si>
-    <t>1011517846</t>
-  </si>
-  <si>
-    <t>1013364053</t>
-  </si>
-  <si>
-    <t>1025906150</t>
-  </si>
-  <si>
-    <t>1025902964</t>
-  </si>
-  <si>
-    <t>1018258929</t>
-  </si>
-  <si>
-    <t>1018248468</t>
-  </si>
-  <si>
-    <t>1017283173</t>
-  </si>
-  <si>
-    <t>1023538982</t>
-  </si>
-  <si>
-    <t>1013369943</t>
-  </si>
-  <si>
-    <t>1018254830</t>
+    <t>1013349020</t>
+  </si>
+  <si>
+    <t>1013366022</t>
+  </si>
+  <si>
+    <t>1018248214</t>
+  </si>
+  <si>
+    <t>1042587012</t>
+  </si>
+  <si>
+    <t>1018269052</t>
+  </si>
+  <si>
+    <t>1041634370</t>
   </si>
   <si>
     <t>1013350043</t>
@@ -175,42 +145,36 @@
     <t>1021931357</t>
   </si>
   <si>
-    <t>1020232494</t>
-  </si>
-  <si>
-    <t>1020228828</t>
+    <t>1020308169</t>
   </si>
   <si>
     <t>1018271477</t>
   </si>
   <si>
-    <t>1192469448</t>
-  </si>
-  <si>
     <t>1025899613</t>
   </si>
   <si>
     <t>1035005666</t>
   </si>
   <si>
-    <t>1018253841</t>
+    <t>1020225476</t>
   </si>
   <si>
     <t>1025770324</t>
   </si>
   <si>
+    <t>1025776867</t>
+  </si>
+  <si>
+    <t>1013377365</t>
+  </si>
+  <si>
+    <t>1013370057</t>
+  </si>
+  <si>
     <t>1020307672</t>
   </si>
   <si>
-    <t>1029301914</t>
-  </si>
-  <si>
-    <t>1011519079</t>
-  </si>
-  <si>
-    <t>1011516886</t>
-  </si>
-  <si>
     <t>1011518615</t>
   </si>
   <si>
@@ -220,114 +184,108 @@
     <t>1020239882</t>
   </si>
   <si>
-    <t>1025896458</t>
-  </si>
-  <si>
     <t>1020323103</t>
   </si>
   <si>
-    <t>1034304812</t>
-  </si>
-  <si>
-    <t>1020321827</t>
-  </si>
-  <si>
     <t>1020312315</t>
   </si>
   <si>
+    <t>1020226915</t>
+  </si>
+  <si>
+    <t>1016601695</t>
+  </si>
+  <si>
     <t>1015079466</t>
   </si>
   <si>
     <t>1015077703</t>
   </si>
   <si>
-    <t>1011517041</t>
-  </si>
-  <si>
-    <t>1021941636</t>
+    <t>1096705038</t>
+  </si>
+  <si>
+    <t>1018273200</t>
   </si>
   <si>
     <t>1025895823</t>
   </si>
   <si>
+    <t>1013368945</t>
+  </si>
+  <si>
+    <t>1015075125</t>
+  </si>
+  <si>
+    <t>1025894543</t>
+  </si>
+  <si>
     <t>1035008500</t>
   </si>
   <si>
     <t>1011404208</t>
   </si>
   <si>
+    <t>1022004383</t>
+  </si>
+  <si>
     <t>1011410559</t>
   </si>
   <si>
     <t>1025904957</t>
   </si>
   <si>
-    <t>1020231885</t>
-  </si>
-  <si>
-    <t>1219213288</t>
-  </si>
-  <si>
     <t>1018271176</t>
   </si>
   <si>
     <t>1018254757</t>
   </si>
   <si>
-    <t>1141722491</t>
-  </si>
-  <si>
     <t>1141719278</t>
   </si>
   <si>
+    <t>1035978921</t>
+  </si>
+  <si>
     <t>1092540648</t>
   </si>
   <si>
-    <t>1020228682</t>
-  </si>
-  <si>
-    <t>1011330426</t>
-  </si>
-  <si>
     <t>1084474489</t>
   </si>
   <si>
     <t>1025667898</t>
   </si>
   <si>
-    <t>1033200952</t>
-  </si>
-  <si>
-    <t>1033190800</t>
-  </si>
-  <si>
-    <t>1025908734</t>
+    <t>1025896997</t>
   </si>
   <si>
     <t>1025901666</t>
   </si>
   <si>
+    <t>1034925183</t>
+  </si>
+  <si>
     <t>1034924450</t>
   </si>
   <si>
     <t>1025900606</t>
   </si>
   <si>
-    <t>1020226620</t>
-  </si>
-  <si>
-    <t>1013383991</t>
-  </si>
-  <si>
-    <t>Aguirre Gomez Ariana</t>
-  </si>
-  <si>
-    <t>Aguirre Gomez Susana</t>
+    <t>1023654563</t>
+  </si>
+  <si>
+    <t>1023655835</t>
   </si>
   <si>
     <t>Alzate Monsalve David</t>
   </si>
   <si>
+    <t>Arango Salazar Luciana</t>
+  </si>
+  <si>
+    <t>Arango Salazar Ximena</t>
+  </si>
+  <si>
     <t>Arbelaez Torres Maksimilian</t>
   </si>
   <si>
@@ -337,112 +295,82 @@
     <t>Arenas Calderon Salomon</t>
   </si>
   <si>
-    <t>Arroyave Gonzalez Elisabet</t>
-  </si>
-  <si>
-    <t>Betancur Cardona Samuel</t>
-  </si>
-  <si>
-    <t>Betancur Mesa Sara</t>
+    <t>Artunduaga Burgos Emmanuel</t>
+  </si>
+  <si>
+    <t>Artunduaga Burgos Isaac</t>
+  </si>
+  <si>
+    <t>Artunduaga Burgos Sarahy</t>
   </si>
   <si>
     <t>Bran Arrieta Saray</t>
   </si>
   <si>
-    <t>Calle Ortiz Danya</t>
-  </si>
-  <si>
     <t>Cardenas Martinez Cristian Mathias</t>
   </si>
   <si>
+    <t>Cardona Mosquera Isaac</t>
+  </si>
+  <si>
     <t>Cardona Mosquera Roxana</t>
   </si>
   <si>
-    <t>Caro Soto Samuel</t>
+    <t>Carvajal Gomez Shari Lined</t>
+  </si>
+  <si>
+    <t>Castaño Patiño Juan Jose</t>
   </si>
   <si>
     <t>Chavarria Osorio Luna Celeste</t>
   </si>
   <si>
-    <t>Chaverra Gomez Rebeca</t>
-  </si>
-  <si>
-    <t>Clavijo Quiceno Sara</t>
-  </si>
-  <si>
-    <t>Correa Castaño Christopher</t>
-  </si>
-  <si>
     <t>Cortes Correa Rebeca</t>
   </si>
   <si>
+    <t>Cortes Correa Salome</t>
+  </si>
+  <si>
     <t>Cuervo Consuegra Tamara</t>
   </si>
   <si>
-    <t>De La Ossa Mejia Micaias</t>
-  </si>
-  <si>
     <t>De Luquez Bernal Mabel Sarai</t>
   </si>
   <si>
+    <t>Diaz Gamboa Isaac</t>
+  </si>
+  <si>
+    <t>Diaz Gamboa Moises Uzziel</t>
+  </si>
+  <si>
+    <t>Diaz Gonzalez Matias</t>
+  </si>
+  <si>
     <t>Echeverri Agudelo Samuel</t>
   </si>
   <si>
-    <t>Escalante Martinez Samuel</t>
-  </si>
-  <si>
-    <t>Escalante Martinez Sara</t>
-  </si>
-  <si>
-    <t>Ferraro Gallego Santiago</t>
-  </si>
-  <si>
-    <t>Florez Alvarez Juan David</t>
-  </si>
-  <si>
-    <t>Florez Henao Stefany</t>
-  </si>
-  <si>
-    <t>Florez Puerta Sofia</t>
-  </si>
-  <si>
-    <t>Garcia Correa Andres Esteban</t>
-  </si>
-  <si>
     <t>Garcia Ramirez Nicolas</t>
   </si>
   <si>
     <t>Garcia Ramirez Thomás</t>
   </si>
   <si>
-    <t>Giraldo Lozano Emma</t>
-  </si>
-  <si>
-    <t>Henao Pinilla Simon</t>
-  </si>
-  <si>
-    <t>Hincapie Rosales Jose Ricardo</t>
-  </si>
-  <si>
-    <t>Hurtado Hurtado Sara</t>
-  </si>
-  <si>
-    <t>Jaramillo Carranza Camila</t>
-  </si>
-  <si>
-    <t>Jaramillo Carranza Santiago</t>
-  </si>
-  <si>
-    <t>Jarvis Estrada Arya Elowyn</t>
-  </si>
-  <si>
-    <t>Londoño Jaramillo Ezequiel</t>
-  </si>
-  <si>
-    <t>Londoño Jaramillo Samuel</t>
-  </si>
-  <si>
-    <t>Londoño Sanchez Antonia</t>
+    <t>Gaviria Cespedes Brenda</t>
+  </si>
+  <si>
+    <t>Gaviria Cespedes Evelyn</t>
+  </si>
+  <si>
+    <t>Gomez Buitrago Mariangel</t>
+  </si>
+  <si>
+    <t>Guette Ortiz Ashley Carolina</t>
+  </si>
+  <si>
+    <t>Guette Ortiz Norah Isabella</t>
+  </si>
+  <si>
+    <t>Jaramillo Agudelo Ana Sofia</t>
   </si>
   <si>
     <t>Luna Rincon Juan Sebastian</t>
@@ -451,42 +379,36 @@
     <t>Machado Taborda Mateo</t>
   </si>
   <si>
-    <t>Mariaca Montagut Alejandra</t>
-  </si>
-  <si>
-    <t>Mariaca Montagut Maria Clara</t>
+    <t>Manco Fonnegra Samuel</t>
   </si>
   <si>
     <t>Marin Vergara Nicolas</t>
   </si>
   <si>
-    <t>Marquez Mora Emilia</t>
-  </si>
-  <si>
     <t>Martinez Alvarez Thiago</t>
   </si>
   <si>
     <t>Martinez Ciro Josue</t>
   </si>
   <si>
-    <t>Mendoza Alvarez Abigail</t>
+    <t>Martinez Correa Tomas</t>
   </si>
   <si>
     <t>Mesa Cardona Mariangel</t>
   </si>
   <si>
+    <t>Montoya Crumb Ahavah Joy</t>
+  </si>
+  <si>
+    <t>Montoya Crumb Aviva Faith</t>
+  </si>
+  <si>
+    <t>Montoya Crumb Samuel Robert</t>
+  </si>
+  <si>
     <t>Muñoz Vellojin Mateo</t>
   </si>
   <si>
-    <t>Narvaez Martinez Samuel</t>
-  </si>
-  <si>
-    <t>Orrego Jimenez Analucia</t>
-  </si>
-  <si>
-    <t>Orrego Jimenez Benjamin</t>
-  </si>
-  <si>
     <t>Ortega Zabala Abigail</t>
   </si>
   <si>
@@ -496,247 +418,205 @@
     <t>Ortiz Cano Sara</t>
   </si>
   <si>
-    <t>Pacheco Giraldo Santiago</t>
-  </si>
-  <si>
     <t>Perez Pino Susana</t>
   </si>
   <si>
-    <t>Perilla Chica Isabella</t>
-  </si>
-  <si>
-    <t>Posada Alzate Abraham</t>
-  </si>
-  <si>
     <t>Pérez Hernández Salomé</t>
   </si>
   <si>
+    <t>Ramirez Avila Daniel</t>
+  </si>
+  <si>
+    <t>Ramirez Avila Sara</t>
+  </si>
+  <si>
     <t>Restrepo Cortes Isabella</t>
   </si>
   <si>
     <t>Restrepo Cortes Juan Manuel</t>
   </si>
   <si>
-    <t>Rios Hurtado Miguel Angel</t>
-  </si>
-  <si>
-    <t>Rojas Jimenez Sofia</t>
+    <t>Rizo Paez David Armando</t>
+  </si>
+  <si>
+    <t>Rizo Paez Elisa Victoria</t>
   </si>
   <si>
     <t>Ruiz Aristizabal Nicolas</t>
   </si>
   <si>
+    <t>Ruiz Estrada Sofia Camila</t>
+  </si>
+  <si>
+    <t>Ruiz Rodas Jacobo</t>
+  </si>
+  <si>
+    <t>Saldarriaga Isaza Ana Sofia</t>
+  </si>
+  <si>
     <t>Sanabria Cardona Santiago</t>
   </si>
   <si>
     <t>Sanchez Bustamante Genesis</t>
   </si>
   <si>
+    <t>Sanchez Bustamante Manuela</t>
+  </si>
+  <si>
     <t>Sanchez Bustamante Sarah Joann</t>
   </si>
   <si>
     <t>Sanchez Justiniano Jose David</t>
   </si>
   <si>
-    <t>Sanchez Otalvaro Guadalupe</t>
-  </si>
-  <si>
-    <t>Sauls Peña Joshua</t>
-  </si>
-  <si>
     <t>Sayago Acevedo Isabella</t>
   </si>
   <si>
     <t>Sayago Acevedo Samuel</t>
   </si>
   <si>
-    <t>Segura Rios Emmanuel David</t>
-  </si>
-  <si>
     <t>Segura Rios Samuel Felipe</t>
   </si>
   <si>
+    <t>Serna Ramirez Luciana</t>
+  </si>
+  <si>
     <t>Sierra Peñaranda Miguel Angel</t>
   </si>
   <si>
-    <t>Suescun Yepes Juan Manuel</t>
-  </si>
-  <si>
-    <t>Taborda Reyes Samuel Esteban</t>
-  </si>
-  <si>
     <t>Tenorio Maya Liam</t>
   </si>
   <si>
     <t>Troya Rendon Emanuel</t>
   </si>
   <si>
-    <t>Usma Jaramillo Maria Celeste</t>
-  </si>
-  <si>
-    <t>Usuga Hidalgo Juan Sebastian</t>
-  </si>
-  <si>
-    <t>Vanegas Cano Matias</t>
+    <t>Vanegas Olaya Cristopher</t>
   </si>
   <si>
     <t>Vanegas Olaya Simon</t>
   </si>
   <si>
+    <t>Vanegas Pulgarin Sheray</t>
+  </si>
+  <si>
     <t>Vasquez Rodas Josue</t>
   </si>
   <si>
     <t>Velez Ortiz Simon</t>
   </si>
   <si>
-    <t>Viloria Quiceno Isaac</t>
-  </si>
-  <si>
-    <t>Zorrilla Jaramillo Santiago</t>
+    <t>Yepes Murillo Mariangel</t>
+  </si>
+  <si>
+    <t>Zapata Echeverry Abigail</t>
+  </si>
+  <si>
+    <t>CUARTO</t>
+  </si>
+  <si>
+    <t>DÉCIMO</t>
+  </si>
+  <si>
+    <t>ONCE</t>
+  </si>
+  <si>
+    <t>OCTAVO</t>
   </si>
   <si>
     <t>SEGUNDO</t>
   </si>
   <si>
+    <t>QUINTO</t>
+  </si>
+  <si>
+    <t>TRANSICIÓN</t>
+  </si>
+  <si>
+    <t>SEPTIMO</t>
+  </si>
+  <si>
+    <t>SEXTO</t>
+  </si>
+  <si>
+    <t>PRE-JARDIN</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
     <t>NOVENO</t>
   </si>
   <si>
-    <t>CUARTO</t>
-  </si>
-  <si>
-    <t>OCTAVO</t>
-  </si>
-  <si>
-    <t>SEXTO</t>
-  </si>
-  <si>
-    <t>QUINTO</t>
-  </si>
-  <si>
-    <t>DÉCIMO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>SEPTIMO</t>
-  </si>
-  <si>
     <t>PRIMERO</t>
   </si>
   <si>
-    <t>ONCE</t>
-  </si>
-  <si>
-    <t>Aguirre Naranjo Bryan Stiven</t>
-  </si>
-  <si>
     <t>Alzate Villa William</t>
   </si>
   <si>
+    <t>Castellanos Pinoz Johan Mateo</t>
+  </si>
+  <si>
     <t>Arbelaez Londoño Alexander</t>
   </si>
   <si>
     <t>Arenas Villa Harold Alexander</t>
   </si>
   <si>
-    <t>Arroyave Mesa Juan Carlos</t>
-  </si>
-  <si>
-    <t>Cardona Gómez Marcela</t>
-  </si>
-  <si>
-    <t>Mesa Concha Veronica Maria</t>
+    <t>Artunduaga Cabrera Anderson</t>
   </si>
   <si>
     <t>Arrieta Mendoza Liseth</t>
   </si>
   <si>
-    <t>Taborda Uribe Gladys Amparo</t>
-  </si>
-  <si>
     <t>Cardenas Cordero Christian Enrique</t>
   </si>
   <si>
     <t>Mosquera Rodriguez Tania Karina</t>
   </si>
   <si>
-    <t>Caro Rivas Grovis Yinois</t>
+    <t>Gomez Montes Jaime William</t>
+  </si>
+  <si>
+    <t>Castaño Zapata Jose Fernando</t>
   </si>
   <si>
     <t>Chavarria Ramirez Roman Alberto</t>
   </si>
   <si>
-    <t>Chaverra Chaverra Juan David</t>
-  </si>
-  <si>
-    <t>Carreño Bohorquez Nora Maria</t>
-  </si>
-  <si>
-    <t>Correa Santana Edwin Andres</t>
-  </si>
-  <si>
     <t>Cortes Velasquez Juan Pablo</t>
   </si>
   <si>
     <t>Cuervo Paternina Eder Andres</t>
   </si>
   <si>
-    <t>De La Ossa Mendoza Abel Jesus</t>
-  </si>
-  <si>
     <t>De Luquez Diaz Ezequiel</t>
   </si>
   <si>
+    <t>Diaz Moncaleano Carlos Andres</t>
+  </si>
+  <si>
+    <t>Diaz Rico John Edwin</t>
+  </si>
+  <si>
     <t>Echeverry Agudelo Sara Catalina</t>
   </si>
   <si>
-    <t>Forero Reyes Janeth</t>
-  </si>
-  <si>
-    <t>Ferraro Trejos Diego Gian Franco</t>
-  </si>
-  <si>
-    <t>Alvarez Cifuentes Jorge William</t>
-  </si>
-  <si>
-    <t>Florez Sanchez Miguel Angel</t>
-  </si>
-  <si>
-    <t>Florez Oliveros Uberney</t>
-  </si>
-  <si>
-    <t>Correa Osorio Luisa Fernanda</t>
-  </si>
-  <si>
     <t>Ramirez Suarez Leidy Tatiana</t>
   </si>
   <si>
     <t>Garcia Valencia Cesar Augusto</t>
   </si>
   <si>
-    <t>Lozano Mosquera Mariam</t>
-  </si>
-  <si>
-    <t>Henao Betancur Jorge Humberto</t>
-  </si>
-  <si>
-    <t>Rosales Quintero Yomaira</t>
-  </si>
-  <si>
-    <t>Hurtado Orozco Yudi Andrea</t>
-  </si>
-  <si>
-    <t>Carranza Ricardo Diana Marcela</t>
-  </si>
-  <si>
-    <t>Estrada Vargas Susana</t>
-  </si>
-  <si>
-    <t>Londoño Moreno Andres Felipe</t>
-  </si>
-  <si>
-    <t>Sanchez Isaura Pilar</t>
+    <t>Cespedes Restrepo Maria Alejandra</t>
+  </si>
+  <si>
+    <t>Gomez Rios Geovanny Arley</t>
+  </si>
+  <si>
+    <t>Ortiz Julio Sirly Dayana</t>
+  </si>
+  <si>
+    <t>Agudelo Torres Sumilde Elena</t>
   </si>
   <si>
     <t>Rincon Lopera Liliana Maria</t>
@@ -745,69 +625,63 @@
     <t>Sas Inversiones Myt</t>
   </si>
   <si>
-    <t>Montagut Ortiz Clariveth</t>
+    <t>Manco Echavarria Reynel De Jesus</t>
   </si>
   <si>
     <t>Vergara Mejia Sara Valentina</t>
   </si>
   <si>
-    <t>Mora Cardona Katherine</t>
-  </si>
-  <si>
     <t>Hernandez Morelo Liliana</t>
   </si>
   <si>
     <t>Martinez Moreno Devinson</t>
   </si>
   <si>
-    <t>Alvarez Martinez Glenys Yanet</t>
+    <t>Correa Mejia Catalina</t>
   </si>
   <si>
     <t>Cardona Gaviria Maribel</t>
   </si>
   <si>
+    <t>Montoya Diaz Luis Fernando</t>
+  </si>
+  <si>
     <t>Vellojin Cavadia Tania Marjolia</t>
   </si>
   <si>
-    <t>Martinez Florez Yerlys Sadit</t>
-  </si>
-  <si>
-    <t>Orrego Zuluaga Juan Esteban</t>
-  </si>
-  <si>
     <t>Zabala Cuervo Diana Rocio</t>
   </si>
   <si>
     <t>Cano Guarin Sandra Milena</t>
   </si>
   <si>
-    <t>Pacheco Basilio Wiliam</t>
-  </si>
-  <si>
     <t>Perez Toro Juan Pablo</t>
   </si>
   <si>
-    <t>Perilla Alarcon Elisio</t>
-  </si>
-  <si>
-    <t>Posada Suarez Gabriel Fernando</t>
-  </si>
-  <si>
     <t>Hernandez Cardona Mauricio</t>
   </si>
   <si>
+    <t>Ramirez Urrutia Fredy</t>
+  </si>
+  <si>
     <t>Restrepo Silva Jeison</t>
   </si>
   <si>
-    <t>Hurtado Garzon Rosalba</t>
-  </si>
-  <si>
-    <t>Marino Millan Yelitza Rossana</t>
+    <t>Rizo Ibanez Jorge Armando</t>
   </si>
   <si>
     <t>Agudelo Ruiz Sergio Mario</t>
   </si>
   <si>
+    <t>Estrada Colon Yerica Del Carmen</t>
+  </si>
+  <si>
+    <t>Rodas Marin Monica Janeth</t>
+  </si>
+  <si>
+    <t>Saldarriaga Gonzalez Carlos Mario</t>
+  </si>
+  <si>
     <t>Sanabria Ballen Andres Leonardo</t>
   </si>
   <si>
@@ -817,12 +691,6 @@
     <t>Sanchez Justiniano Martha Catherine</t>
   </si>
   <si>
-    <t>Sanchez Agudelo Uber Herney</t>
-  </si>
-  <si>
-    <t>Peña Morales Eliana Patricia</t>
-  </si>
-  <si>
     <t>Sayago Montes Juan Esteban</t>
   </si>
   <si>
@@ -832,54 +700,45 @@
     <t>Segura Camacho Oscar Dario</t>
   </si>
   <si>
+    <t>Arboleda Ramirez Daniel Andres</t>
+  </si>
+  <si>
     <t>Hernandez Ospina Juan Camilo</t>
   </si>
   <si>
-    <t>Suescun Gomez Jhony Alexander</t>
-  </si>
-  <si>
-    <t>Taborda Yepes Juan Esteban</t>
-  </si>
-  <si>
     <t>Marin Osorio Johny Alexander</t>
   </si>
   <si>
     <t>Troya Osorio Manuel Enrique</t>
   </si>
   <si>
-    <t>Usma Acevedo Elkin Humberto</t>
-  </si>
-  <si>
-    <t>Usuga Sepulveda Henrry</t>
-  </si>
-  <si>
-    <t>Vanegas Pineda Bladimir</t>
-  </si>
-  <si>
     <t>Olaya Rojas Liliana Maria</t>
   </si>
   <si>
+    <t>Vanegas Zuñiga Ray Andres</t>
+  </si>
+  <si>
     <t>Vasquez Gomez Alejandro</t>
   </si>
   <si>
     <t>Ortiz Velez Laura Catalina</t>
   </si>
   <si>
-    <t>Viloria Montoya Enrique Alexander</t>
-  </si>
-  <si>
-    <t>Zorrilla Adarve Oscar Wilfredo</t>
+    <t>Yepes Arias Angela Maria</t>
+  </si>
+  <si>
+    <t>Echeverry Giraldo Estefania</t>
   </si>
   <si>
     <t>Madre</t>
   </si>
   <si>
+    <t>Padrastro</t>
+  </si>
+  <si>
     <t>Padre</t>
   </si>
   <si>
-    <t>Abuela</t>
-  </si>
-  <si>
     <t>Abuelo</t>
   </si>
   <si>
@@ -889,7 +748,7 @@
     <t>Otro</t>
   </si>
   <si>
-    <t>6045060067</t>
+    <t>Tía</t>
   </si>
   <si>
     <t>3008486499</t>
@@ -901,70 +760,46 @@
     <t>2988855</t>
   </si>
   <si>
-    <t>5993988</t>
-  </si>
-  <si>
-    <t>4210191</t>
-  </si>
-  <si>
     <t>3235009283</t>
   </si>
   <si>
-    <t>3137445572</t>
-  </si>
-  <si>
     <t>5671163</t>
   </si>
   <si>
     <t>5095498</t>
   </si>
   <si>
-    <t>6044444614</t>
+    <t>5075518</t>
   </si>
   <si>
     <t>3104067600</t>
   </si>
   <si>
-    <t>4579679</t>
-  </si>
-  <si>
-    <t>4432431</t>
-  </si>
-  <si>
     <t>2973675</t>
   </si>
   <si>
     <t>2068714</t>
   </si>
   <si>
-    <t>4945166</t>
-  </si>
-  <si>
     <t>5823889</t>
   </si>
   <si>
+    <t>,</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>3015686911</t>
-  </si>
-  <si>
-    <t>4667872</t>
-  </si>
-  <si>
-    <t>3013564721</t>
-  </si>
-  <si>
     <t>4076883</t>
   </si>
   <si>
-    <t>3204103173</t>
-  </si>
-  <si>
-    <t>4811500</t>
-  </si>
-  <si>
-    <t>2678435</t>
+    <t>4337791</t>
+  </si>
+  <si>
+    <t>5O9 80 21</t>
+  </si>
+  <si>
+    <t>6045038065</t>
   </si>
   <si>
     <t>5060713</t>
@@ -973,43 +808,28 @@
     <t>4195996</t>
   </si>
   <si>
-    <t>4224748</t>
-  </si>
-  <si>
-    <t>2050489</t>
+    <t>3136549427</t>
+  </si>
+  <si>
+    <t>4773589</t>
   </si>
   <si>
     <t>5700932</t>
   </si>
   <si>
-    <t>4420606</t>
-  </si>
-  <si>
-    <t>3006234263</t>
-  </si>
-  <si>
     <t>6044420606</t>
   </si>
   <si>
-    <t>4075494</t>
-  </si>
-  <si>
     <t>6045061121</t>
   </si>
   <si>
-    <t>6125258</t>
-  </si>
-  <si>
-    <t>5839111</t>
-  </si>
-  <si>
     <t>3112860092</t>
   </si>
   <si>
-    <t>5042146</t>
-  </si>
-  <si>
-    <t>3134633058</t>
+    <t>2840252</t>
+  </si>
+  <si>
+    <t>5590297</t>
   </si>
   <si>
     <t>2347767</t>
@@ -1018,142 +838,94 @@
     <t>4330808</t>
   </si>
   <si>
-    <t>4613821</t>
-  </si>
-  <si>
     <t>5863905</t>
   </si>
   <si>
+    <t>5771821</t>
+  </si>
+  <si>
     <t>6008276</t>
   </si>
   <si>
-    <t>6045901145</t>
-  </si>
-  <si>
     <t>3205617348</t>
   </si>
   <si>
-    <t>4381023</t>
-  </si>
-  <si>
-    <t>2971462</t>
-  </si>
-  <si>
     <t>4984861</t>
   </si>
   <si>
     <t>4882576</t>
   </si>
   <si>
-    <t>3413859</t>
-  </si>
-  <si>
-    <t>bryansan87@gmail.com</t>
+    <t>3104440838</t>
   </si>
   <si>
     <t>kellyj2914@hotmail.com</t>
   </si>
   <si>
+    <t>jmcpinzon@gmail.com</t>
+  </si>
+  <si>
     <t>xander1209@hotmail.com</t>
   </si>
   <si>
     <t>EVOLETHARENAS@GMAIL.COM</t>
   </si>
   <si>
-    <t>ARROYAVE1215@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>FUEGOVITAL760@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ACOMERCIALRICARDO@GMAIL.COM</t>
+    <t>macartin01@hotmail.es</t>
   </si>
   <si>
     <t>YAQUESKA@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>maurocalle8507@gmail.com</t>
-  </si>
-  <si>
     <t>christian.cardenas@correo.policia.gov.co</t>
   </si>
   <si>
     <t>ANDRESCARDONA70@GMAIL.COM</t>
   </si>
   <si>
-    <t>alejandrasotoh@gmail.com</t>
+    <t>tapiceriajg@hotmail.com</t>
+  </si>
+  <si>
+    <t>CTATIANAP@HOTMAIL.COM</t>
   </si>
   <si>
     <t>veronicaosoriocarvajal@gmail.com</t>
   </si>
   <si>
-    <t>PAO1825@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>marybella2905@gmail.com</t>
-  </si>
-  <si>
-    <t>linacastano065@gmail.com</t>
-  </si>
-  <si>
     <t>ALEJANDRA210187@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>mercadeo@vertigologistica.com</t>
+  </si>
+  <si>
     <t>marlencj@hotmail.com</t>
   </si>
   <si>
-    <t>desaossa@gmail.com</t>
-  </si>
-  <si>
     <t>EZDEDI7@YAHOO.ES</t>
   </si>
   <si>
+    <t>ladyjohannaggl@gmail.com</t>
+  </si>
+  <si>
+    <t>jhondiazrico@gmail.com</t>
+  </si>
+  <si>
     <t>SARITA-ECHEVERRI@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>jafore0809@hotmail.comsan</t>
-  </si>
-  <si>
-    <t>GIANFRANCO1077@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>nakelwk@hotmail.com</t>
-  </si>
-  <si>
-    <t>ANGELAMHENAO33@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>uberney1983@hotmail.com</t>
-  </si>
-  <si>
-    <t>fercorreaosorio25@gmail.com</t>
-  </si>
-  <si>
     <t>Ramirezsuarezt@gmail.com</t>
   </si>
   <si>
-    <t>esteban.g0104@hotmail.com</t>
-  </si>
-  <si>
-    <t>zuleimapv4@hotmail.com</t>
-  </si>
-  <si>
-    <t>yomaira.rosales@colmayor.edu.co</t>
-  </si>
-  <si>
-    <t>yudyhurtado@hotmail.com</t>
-  </si>
-  <si>
-    <t>carranza.dm21@hotmail.es</t>
-  </si>
-  <si>
-    <t>susanaestrada0121@gmail.com</t>
-  </si>
-  <si>
-    <t>ledisjaramillo0@gmail.com</t>
-  </si>
-  <si>
-    <t>ISAPISAN@GMAIL.COM</t>
+    <t>alejandra.cespedes.r@hotmail.com</t>
+  </si>
+  <si>
+    <t>GIOVA.GO8124@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>Sirlydayana@hotmail.com</t>
+  </si>
+  <si>
+    <t>seagudelo@gmail.com</t>
   </si>
   <si>
     <t>jclunapublicidad@gmail.com</t>
@@ -1162,72 +934,66 @@
     <t>SELVAAZUL_07@YAHOO.ES</t>
   </si>
   <si>
-    <t>klariveth@gmail.com</t>
-  </si>
-  <si>
-    <t>alejomtoro1@gmail.com</t>
+    <t>REYNELM1980@GMAIL.COM</t>
   </si>
   <si>
     <t>saravergara775@gmail.com</t>
   </si>
   <si>
-    <t>ktmc-10@hotmail.com</t>
-  </si>
-  <si>
     <t>EZEQUIELMARTINEZ-5@HOTMAIL.COM</t>
   </si>
   <si>
     <t>alexandraa200906@gmail.com</t>
   </si>
   <si>
-    <t>glenysyanett@hotmail.com</t>
+    <t>CATALINACORREA1327@GMAIL.COM</t>
   </si>
   <si>
     <t>TONERYPCS@GMAIL.COM</t>
   </si>
   <si>
+    <t>luisfmd.28@hotmail.com</t>
+  </si>
+  <si>
     <t>TANIAVELCAV@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>ysmartinez01@gmail.com</t>
-  </si>
-  <si>
-    <t>NATALIAJIMENEZCOMUNICACIONES@GMAIL.COM</t>
-  </si>
-  <si>
     <t>dianiazabal@hotmail.com</t>
   </si>
   <si>
     <t>canosandy173@gmail.com</t>
   </si>
   <si>
-    <t>alisanmedellin@gmail.com</t>
-  </si>
-  <si>
     <t>khathik18@gmail.com</t>
   </si>
   <si>
-    <t>mariat169@yahoo.com</t>
-  </si>
-  <si>
-    <t>posadagabriel@hotmail.com</t>
-  </si>
-  <si>
     <t>PAOLAHC0312@GMAIL.COM</t>
   </si>
   <si>
+    <t>PFREDYSBA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SGAM82@gmail.com</t>
+  </si>
+  <si>
     <t>jeison.restrepo5280@correopolicia.gov.co</t>
   </si>
   <si>
-    <t>auxcontable.arcilaloaizasas@gmail.com</t>
-  </si>
-  <si>
-    <t>yelitza.marino@hotmail.com</t>
+    <t>wendyyuranypaez2016@gmail.com</t>
   </si>
   <si>
     <t>sergio02marzo@gmail.com</t>
   </si>
   <si>
+    <t>estradayerica2430@gmail.com</t>
+  </si>
+  <si>
+    <t>MONICA.RODASM@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CAMASAGO@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>sanabriaandres501@Gmail.com</t>
   </si>
   <si>
@@ -1237,55 +1003,40 @@
     <t>marthacsanchezj@gmail.com</t>
   </si>
   <si>
-    <t>FERNEY1981-@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>8701alan@gmail.com</t>
-  </si>
-  <si>
     <t>VIACEGA@GMAIL.COM</t>
   </si>
   <si>
     <t>lilios12@hotmail.com</t>
   </si>
   <si>
+    <t>lucianaserna32@gmail.com</t>
+  </si>
+  <si>
     <t>JUANCAMILOHERNANDEZHO@GMAIL.COM</t>
   </si>
   <si>
-    <t>deisyferr@hotmail.com</t>
-  </si>
-  <si>
-    <t>t.amirey.tr@gmail.com</t>
-  </si>
-  <si>
     <t>sunandbeach88@hotmail.com</t>
   </si>
   <si>
     <t>manuel.troya734@casur.gov.co</t>
   </si>
   <si>
-    <t>HECHIS83@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>USUGA2310@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>bvanegasp@gmail.com</t>
-  </si>
-  <si>
     <t>lmolaya@hotmail.com</t>
   </si>
   <si>
+    <t>sherayvp@gmail.com</t>
+  </si>
+  <si>
     <t>VASQUEZG@YAHOO.ES</t>
   </si>
   <si>
     <t>LAURAORTIZ.PSICOLOGIA@GMAIL.COM</t>
   </si>
   <si>
-    <t>ENRIQUE.VILORIA@AUTOLARTE.COM.CO</t>
-  </si>
-  <si>
-    <t>nury.jara71@gmail.com</t>
+    <t>admisiones@colombosueco.com</t>
+  </si>
+  <si>
+    <t>abigailzapata133@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1680,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F2" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="G2">
-        <v>3117739445</v>
+        <v>3006800473</v>
       </c>
       <c r="H2" t="s">
-        <v>344</v>
+        <v>281</v>
       </c>
       <c r="I2">
-        <v>750646</v>
+        <v>1157380</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1709,28 +1460,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="G3">
-        <v>3117739445</v>
+        <v>3193086213</v>
       </c>
       <c r="H3" t="s">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="I3">
-        <v>601684</v>
+        <v>477251</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1738,28 +1489,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="F4" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="G4">
-        <v>3006800473</v>
+        <v>3193086213</v>
       </c>
       <c r="H4" t="s">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="I4">
-        <v>577504</v>
+        <v>455648</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1767,28 +1518,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F5" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G5">
         <v>3103748194</v>
       </c>
       <c r="H5" t="s">
-        <v>346</v>
+        <v>283</v>
       </c>
       <c r="I5">
-        <v>614324</v>
+        <v>618324</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1796,28 +1547,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="E6" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F6" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="G6">
         <v>3223079151</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="I6">
-        <v>1007440</v>
+        <v>1514160</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1825,28 +1576,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F7" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="G7">
         <v>3223079151</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="I7">
-        <v>1264660</v>
+        <v>1899990</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1854,28 +1605,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F8" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="G8">
-        <v>3005041266</v>
+        <v>3105262606</v>
       </c>
       <c r="H8" t="s">
-        <v>348</v>
+        <v>285</v>
       </c>
       <c r="I8">
-        <v>591486</v>
+        <v>628360</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1883,28 +1634,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F9" t="s">
-        <v>296</v>
+        <v>246</v>
       </c>
       <c r="G9">
-        <v>3226255509</v>
+        <v>3105262606</v>
       </c>
       <c r="H9" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="I9">
-        <v>540030</v>
+        <v>613673</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1912,28 +1663,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" t="s">
+        <v>246</v>
+      </c>
+      <c r="G10">
+        <v>3105262606</v>
+      </c>
+      <c r="H10" t="s">
         <v>285</v>
       </c>
-      <c r="F10" t="s">
-        <v>293</v>
-      </c>
-      <c r="G10">
-        <v>3232339870</v>
-      </c>
-      <c r="H10" t="s">
-        <v>350</v>
-      </c>
       <c r="I10">
-        <v>585486</v>
+        <v>598074</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1941,28 +1692,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F11" t="s">
-        <v>297</v>
+        <v>248</v>
       </c>
       <c r="G11">
         <v>3164020842</v>
       </c>
       <c r="H11" t="s">
-        <v>351</v>
+        <v>286</v>
       </c>
       <c r="I11">
-        <v>592684</v>
+        <v>582855</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1970,28 +1721,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="E12" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="G12">
-        <v>3137445572</v>
+        <v>3108914534</v>
       </c>
       <c r="H12" t="s">
-        <v>352</v>
+        <v>287</v>
       </c>
       <c r="I12">
-        <v>537409</v>
+        <v>588855</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1999,28 +1750,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="E13" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F13" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="G13">
-        <v>3108914534</v>
+        <v>3185029620</v>
       </c>
       <c r="H13" t="s">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="I13">
-        <v>591684</v>
+        <v>620217</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2028,28 +1779,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="E14" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F14" t="s">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G14">
         <v>3185029620</v>
       </c>
       <c r="H14" t="s">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="I14">
-        <v>1423984</v>
+        <v>2138976</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2057,28 +1808,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="F15" t="s">
-        <v>301</v>
+        <v>246</v>
       </c>
       <c r="G15">
-        <v>3117996256</v>
+        <v>3206373767</v>
       </c>
       <c r="H15" t="s">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="I15">
-        <v>605299</v>
+        <v>484360</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2086,28 +1837,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="E16" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F16" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="G16">
-        <v>3104067600</v>
+        <v>3212776005</v>
       </c>
       <c r="H16" t="s">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="I16">
-        <v>541428</v>
+        <v>475350</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2115,28 +1866,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="D17" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F17" t="s">
-        <v>303</v>
+        <v>252</v>
       </c>
       <c r="G17">
-        <v>3003767391</v>
+        <v>3104067600</v>
       </c>
       <c r="H17" t="s">
-        <v>357</v>
+        <v>291</v>
       </c>
       <c r="I17">
-        <v>614324</v>
+        <v>1084856</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2144,28 +1895,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="E18" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F18" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="G18">
-        <v>3016959292</v>
+        <v>3012457263</v>
       </c>
       <c r="H18" t="s">
-        <v>358</v>
+        <v>292</v>
       </c>
       <c r="I18">
-        <v>620217</v>
+        <v>1514160</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2173,28 +1924,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="E19" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F19" t="s">
+        <v>253</v>
+      </c>
+      <c r="G19">
+        <v>3012457266</v>
+      </c>
+      <c r="H19" t="s">
         <v>293</v>
       </c>
-      <c r="G19">
-        <v>3046838460</v>
-      </c>
-      <c r="H19" t="s">
-        <v>359</v>
-      </c>
       <c r="I19">
-        <v>502720</v>
+        <v>455648</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2202,28 +1953,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="E20" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F20" t="s">
-        <v>305</v>
+        <v>254</v>
       </c>
       <c r="G20">
-        <v>3012457263</v>
+        <v>3233179080</v>
       </c>
       <c r="H20" t="s">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="I20">
-        <v>1007440</v>
+        <v>631561</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2231,28 +1982,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="D21" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="G21">
-        <v>3233179080</v>
+        <v>3156803375</v>
       </c>
       <c r="H21" t="s">
-        <v>361</v>
+        <v>295</v>
       </c>
       <c r="I21">
-        <v>1265122</v>
+        <v>567488</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2260,28 +2011,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="D22" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="E22" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F22" t="s">
-        <v>307</v>
+        <v>246</v>
       </c>
       <c r="G22">
-        <v>3148195799</v>
+        <v>3007291017</v>
       </c>
       <c r="H22" t="s">
-        <v>362</v>
+        <v>296</v>
       </c>
       <c r="I22">
-        <v>598048</v>
+        <v>565363</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2289,28 +2040,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="D23" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="E23" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F23" t="s">
-        <v>308</v>
+        <v>246</v>
       </c>
       <c r="G23">
-        <v>3156803375</v>
+        <v>3007291017</v>
       </c>
       <c r="H23" t="s">
-        <v>363</v>
+        <v>296</v>
       </c>
       <c r="I23">
-        <v>567488</v>
+        <v>631330</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2318,28 +2069,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="D24" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="E24" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F24" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="G24">
-        <v>3143828183</v>
+        <v>3045957277</v>
       </c>
       <c r="H24" t="s">
-        <v>364</v>
+        <v>297</v>
       </c>
       <c r="I24">
-        <v>506464</v>
+        <v>477251</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2347,28 +2098,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" t="s">
         <v>194</v>
       </c>
-      <c r="D25" t="s">
-        <v>225</v>
-      </c>
       <c r="E25" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="F25" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="G25">
-        <v>3015686911</v>
+        <v>3143828183</v>
       </c>
       <c r="H25" t="s">
-        <v>365</v>
+        <v>298</v>
       </c>
       <c r="I25">
-        <v>1078060</v>
+        <v>567488</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2376,28 +2127,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="E26" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="F26" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="G26">
-        <v>3015686911</v>
+        <v>3146320382</v>
       </c>
       <c r="H26" t="s">
-        <v>365</v>
+        <v>299</v>
       </c>
       <c r="I26">
-        <v>1131172</v>
+        <v>1360262</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2405,28 +2156,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="D27" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="E27" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F27" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="G27">
-        <v>3116347838</v>
+        <v>3146320382</v>
       </c>
       <c r="H27" t="s">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="I27">
-        <v>564172</v>
+        <v>2194495</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2434,28 +2185,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="F28" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="G28">
-        <v>3217540562</v>
+        <v>3108384796</v>
       </c>
       <c r="H28" t="s">
-        <v>367</v>
+        <v>300</v>
       </c>
       <c r="I28">
-        <v>488574</v>
+        <v>506046</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2463,28 +2214,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" t="s">
         <v>197</v>
       </c>
-      <c r="D29" t="s">
-        <v>228</v>
-      </c>
       <c r="E29" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F29" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="G29">
-        <v>3207147950</v>
+        <v>3108384796</v>
       </c>
       <c r="H29" t="s">
-        <v>368</v>
+        <v>300</v>
       </c>
       <c r="I29">
-        <v>1172972</v>
+        <v>631330</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2492,28 +2243,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="D30" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="E30" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F30" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G30">
-        <v>3226038092</v>
+        <v>3004353149</v>
       </c>
       <c r="H30" t="s">
-        <v>369</v>
+        <v>301</v>
       </c>
       <c r="I30">
-        <v>577876</v>
+        <v>284360</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2521,28 +2272,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="D31" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="E31" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F31" t="s">
-        <v>312</v>
+        <v>260</v>
       </c>
       <c r="G31">
-        <v>3013564721</v>
+        <v>3013531871</v>
       </c>
       <c r="H31" t="s">
-        <v>370</v>
+        <v>302</v>
       </c>
       <c r="I31">
-        <v>502720</v>
+        <v>484080</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2550,28 +2301,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D32" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="E32" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F32" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="G32">
-        <v>3146320382</v>
+        <v>3013531871</v>
       </c>
       <c r="H32" t="s">
-        <v>371</v>
+        <v>302</v>
       </c>
       <c r="I32">
-        <v>1403508</v>
+        <v>643482</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2579,28 +2330,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" t="s">
         <v>200</v>
       </c>
-      <c r="D33" t="s">
-        <v>232</v>
-      </c>
       <c r="E33" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F33" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="G33">
-        <v>3146320382</v>
+        <v>3102013484</v>
       </c>
       <c r="H33" t="s">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="I33">
-        <v>1583196</v>
+        <v>473255</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2608,28 +2359,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F34" t="s">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="G34">
-        <v>3147398657</v>
+        <v>3113200460</v>
       </c>
       <c r="H34" t="s">
-        <v>372</v>
+        <v>304</v>
       </c>
       <c r="I34">
-        <v>1258720</v>
+        <v>2164120</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2637,28 +2388,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D35" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="E35" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F35" t="s">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="G35">
-        <v>3008092108</v>
+        <v>3136146481</v>
       </c>
       <c r="H35" t="s">
-        <v>373</v>
+        <v>305</v>
       </c>
       <c r="I35">
-        <v>605196</v>
+        <v>1715680</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2666,28 +2417,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D36" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="E36" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F36" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="G36">
-        <v>3216428160</v>
+        <v>3017206508</v>
       </c>
       <c r="H36" t="s">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="I36">
-        <v>714992</v>
+        <v>476502</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2695,28 +2446,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="D37" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="E37" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F37" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G37">
-        <v>3185529619</v>
+        <v>3022977529</v>
       </c>
       <c r="H37" t="s">
-        <v>375</v>
+        <v>307</v>
       </c>
       <c r="I37">
-        <v>522793</v>
+        <v>521451</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2724,28 +2475,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="D38" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="E38" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F38" t="s">
-        <v>315</v>
+        <v>246</v>
       </c>
       <c r="G38">
-        <v>3206768830</v>
+        <v>3013807813</v>
       </c>
       <c r="H38" t="s">
-        <v>376</v>
+        <v>308</v>
       </c>
       <c r="I38">
-        <v>1103508</v>
+        <v>1198148</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2753,28 +2504,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="D39" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="E39" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F39" t="s">
-        <v>315</v>
+        <v>246</v>
       </c>
       <c r="G39">
-        <v>3206768830</v>
+        <v>3186656220</v>
       </c>
       <c r="H39" t="s">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="I39">
-        <v>913296</v>
+        <v>1762458</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2782,28 +2533,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="D40" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="E40" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F40" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="G40">
-        <v>3018734931</v>
+        <v>3003934941</v>
       </c>
       <c r="H40" t="s">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="I40">
-        <v>1176410</v>
+        <v>482800</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2811,28 +2562,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="E41" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F41" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G41">
-        <v>3177519337</v>
+        <v>3015656941</v>
       </c>
       <c r="H41" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="I41">
-        <v>361958</v>
+        <v>1096770</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2840,28 +2591,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="D42" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="E42" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F42" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G42">
-        <v>3177519337</v>
+        <v>3017266368</v>
       </c>
       <c r="H42" t="s">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="I42">
-        <v>484895</v>
+        <v>707348</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2869,28 +2620,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="D43" t="s">
+        <v>209</v>
+      </c>
+      <c r="E43" t="s">
         <v>240</v>
       </c>
-      <c r="E43" t="s">
-        <v>285</v>
-      </c>
       <c r="F43" t="s">
-        <v>316</v>
+        <v>246</v>
       </c>
       <c r="G43">
-        <v>3122327344</v>
+        <v>3017266368</v>
       </c>
       <c r="H43" t="s">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="I43">
-        <v>1070822</v>
+        <v>579310</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2898,28 +2649,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E44" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F44" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="G44">
-        <v>3113200460</v>
+        <v>3017266368</v>
       </c>
       <c r="H44" t="s">
-        <v>380</v>
+        <v>312</v>
       </c>
       <c r="I44">
-        <v>1620090</v>
+        <v>671161</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2927,28 +2678,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E45" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F45" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
       <c r="G45">
-        <v>3136146481</v>
+        <v>3015954319</v>
       </c>
       <c r="H45" t="s">
-        <v>381</v>
+        <v>313</v>
       </c>
       <c r="I45">
-        <v>1141744</v>
+        <v>2556650</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2956,28 +2707,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="D46" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="E46" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F46" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
       <c r="G46">
-        <v>3113815076</v>
+        <v>3124291951</v>
       </c>
       <c r="H46" t="s">
-        <v>382</v>
+        <v>314</v>
       </c>
       <c r="I46">
-        <v>585486</v>
+        <v>814324</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2985,28 +2736,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="E47" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F47" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
       <c r="G47">
-        <v>3113448104</v>
+        <v>3124291951</v>
       </c>
       <c r="H47" t="s">
-        <v>383</v>
+        <v>314</v>
       </c>
       <c r="I47">
-        <v>534411</v>
+        <v>199330</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3014,28 +2765,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="D48" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="E48" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F48" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G48">
-        <v>3022977529</v>
+        <v>3117316210</v>
       </c>
       <c r="H48" t="s">
-        <v>384</v>
+        <v>315</v>
       </c>
       <c r="I48">
-        <v>521451</v>
+        <v>1044902</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3043,28 +2794,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D49" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="E49" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F49" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="G49">
-        <v>3116823407</v>
+        <v>3166226027</v>
       </c>
       <c r="H49" t="s">
-        <v>385</v>
+        <v>316</v>
       </c>
       <c r="I49">
-        <v>431330</v>
+        <v>608296</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3072,28 +2823,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C50" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="D50" t="s">
+        <v>214</v>
+      </c>
+      <c r="E50" t="s">
+        <v>240</v>
+      </c>
+      <c r="F50" t="s">
         <v>246</v>
       </c>
-      <c r="E50" t="s">
-        <v>285</v>
-      </c>
-      <c r="F50" t="s">
-        <v>293</v>
-      </c>
       <c r="G50">
-        <v>3013807813</v>
+        <v>3226367303</v>
       </c>
       <c r="H50" t="s">
-        <v>386</v>
+        <v>317</v>
       </c>
       <c r="I50">
-        <v>1800222</v>
+        <v>2428600</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3101,28 +2852,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D51" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="E51" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F51" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G51">
-        <v>3186656220</v>
+        <v>3112833518</v>
       </c>
       <c r="H51" t="s">
-        <v>387</v>
+        <v>318</v>
       </c>
       <c r="I51">
-        <v>1172972</v>
+        <v>455985</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3130,28 +2881,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D52" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="E52" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F52" t="s">
-        <v>320</v>
+        <v>246</v>
       </c>
       <c r="G52">
-        <v>3012100135</v>
+        <v>3103161676</v>
       </c>
       <c r="H52" t="s">
-        <v>388</v>
+        <v>319</v>
       </c>
       <c r="I52">
-        <v>1141872</v>
+        <v>505635</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3159,28 +2910,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="D53" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="E53" t="s">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="F53" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="G53">
-        <v>3015656941</v>
+        <v>3112860092</v>
       </c>
       <c r="H53" t="s">
-        <v>389</v>
+        <v>320</v>
       </c>
       <c r="I53">
-        <v>1102016</v>
+        <v>1233196</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3188,28 +2939,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="D54" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="E54" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="F54" t="s">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="G54">
-        <v>3015954319</v>
+        <v>3112860092</v>
       </c>
       <c r="H54" t="s">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I54">
-        <v>2041320</v>
+        <v>1022880</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3217,28 +2968,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C55" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="E55" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F55" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="G55">
-        <v>3103980290</v>
+        <v>3108699380</v>
       </c>
       <c r="H55" t="s">
-        <v>391</v>
+        <v>321</v>
       </c>
       <c r="I55">
-        <v>206099</v>
+        <v>628360</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3246,28 +2997,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D56" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="E56" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F56" t="s">
-        <v>323</v>
+        <v>246</v>
       </c>
       <c r="G56">
-        <v>3006234263</v>
+        <v>3108699380</v>
       </c>
       <c r="H56" t="s">
-        <v>392</v>
+        <v>321</v>
       </c>
       <c r="I56">
-        <v>1446547</v>
+        <v>587205</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3275,28 +3026,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C57" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="D57" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="E57" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="F57" t="s">
-        <v>323</v>
+        <v>246</v>
       </c>
       <c r="G57">
-        <v>3006234263</v>
+        <v>3194309799</v>
       </c>
       <c r="H57" t="s">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="I57">
-        <v>1265122</v>
+        <v>476255</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3304,28 +3055,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C58" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="D58" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="E58" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F58" t="s">
-        <v>324</v>
+        <v>246</v>
       </c>
       <c r="G58">
-        <v>3124291951</v>
+        <v>3106368274</v>
       </c>
       <c r="H58" t="s">
-        <v>393</v>
+        <v>323</v>
       </c>
       <c r="I58">
-        <v>614296</v>
+        <v>481800</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3333,28 +3084,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="D59" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="E59" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F59" t="s">
+        <v>270</v>
+      </c>
+      <c r="G59">
+        <v>3008674834</v>
+      </c>
+      <c r="H59" t="s">
         <v>324</v>
       </c>
-      <c r="G59">
-        <v>3124291951</v>
-      </c>
-      <c r="H59" t="s">
-        <v>393</v>
-      </c>
       <c r="I59">
-        <v>100000</v>
+        <v>484300</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3362,28 +3113,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="D60" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="E60" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F60" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="G60">
-        <v>3117316210</v>
+        <v>3104534612</v>
       </c>
       <c r="H60" t="s">
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="I60">
-        <v>1044902</v>
+        <v>484360</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3391,28 +3142,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="D61" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="E61" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F61" t="s">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="G61">
-        <v>3216167718</v>
+        <v>3022424243</v>
       </c>
       <c r="H61" t="s">
-        <v>395</v>
+        <v>326</v>
       </c>
       <c r="I61">
-        <v>433753</v>
+        <v>1155620</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3420,28 +3171,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C62" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D62" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="E62" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F62" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="G62">
-        <v>3166226027</v>
+        <v>3127382747</v>
       </c>
       <c r="H62" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="I62">
-        <v>1229972</v>
+        <v>1014246</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3449,28 +3200,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C63" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="D63" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="E63" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F63" t="s">
+        <v>273</v>
+      </c>
+      <c r="G63">
+        <v>3127382747</v>
+      </c>
+      <c r="H63" t="s">
         <v>327</v>
       </c>
-      <c r="G63">
-        <v>3184398000</v>
-      </c>
-      <c r="H63" t="s">
-        <v>397</v>
-      </c>
       <c r="I63">
-        <v>598074</v>
+        <v>455648</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3478,28 +3229,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C64" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="D64" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="E64" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F64" t="s">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="G64">
-        <v>3177063250</v>
+        <v>3127382747</v>
       </c>
       <c r="H64" t="s">
-        <v>398</v>
+        <v>327</v>
       </c>
       <c r="I64">
-        <v>663548</v>
+        <v>1103508</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3507,28 +3258,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="D65" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E65" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F65" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G65">
-        <v>3226367303</v>
+        <v>3168660548</v>
       </c>
       <c r="H65" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
       <c r="I65">
-        <v>2017880</v>
+        <v>2044495</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3536,28 +3287,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C66" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="D66" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="E66" t="s">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="F66" t="s">
+        <v>246</v>
+      </c>
+      <c r="G66">
+        <v>3145672233</v>
+      </c>
+      <c r="H66" t="s">
         <v>329</v>
       </c>
-      <c r="G66">
-        <v>3112860092</v>
-      </c>
-      <c r="H66" t="s">
-        <v>400</v>
-      </c>
       <c r="I66">
-        <v>623897</v>
+        <v>3574960</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3565,28 +3316,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="D67" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="E67" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="F67" t="s">
+        <v>246</v>
+      </c>
+      <c r="G67">
+        <v>3145672233</v>
+      </c>
+      <c r="H67" t="s">
         <v>329</v>
       </c>
-      <c r="G67">
-        <v>3112860092</v>
-      </c>
-      <c r="H67" t="s">
-        <v>400</v>
-      </c>
       <c r="I67">
-        <v>516160</v>
+        <v>1704306</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3594,28 +3345,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="C68" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="D68" t="s">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="E68" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F68" t="s">
+        <v>274</v>
+      </c>
+      <c r="G68">
+        <v>3148214908</v>
+      </c>
+      <c r="H68" t="s">
         <v>330</v>
       </c>
-      <c r="G68">
-        <v>3113681582</v>
-      </c>
-      <c r="H68" t="s">
-        <v>401</v>
-      </c>
       <c r="I68">
-        <v>531099</v>
+        <v>1016660</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3623,28 +3374,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C69" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="D69" t="s">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="E69" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="F69" t="s">
+        <v>275</v>
+      </c>
+      <c r="G69">
+        <v>3207611691</v>
+      </c>
+      <c r="H69" t="s">
         <v>331</v>
       </c>
-      <c r="G69">
-        <v>3134633058</v>
-      </c>
-      <c r="H69" t="s">
-        <v>402</v>
-      </c>
       <c r="I69">
-        <v>650088</v>
+        <v>477251</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3652,28 +3403,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="D70" t="s">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="E70" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="F70" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="G70">
-        <v>3194309799</v>
+        <v>3003438170</v>
       </c>
       <c r="H70" t="s">
-        <v>403</v>
+        <v>332</v>
       </c>
       <c r="I70">
-        <v>637004</v>
+        <v>1462880</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3681,28 +3432,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
+        <v>156</v>
+      </c>
+      <c r="C71" t="s">
         <v>170</v>
       </c>
-      <c r="C71" t="s">
-        <v>195</v>
-      </c>
       <c r="D71" t="s">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="E71" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F71" t="s">
-        <v>332</v>
+        <v>277</v>
       </c>
       <c r="G71">
-        <v>3022424243</v>
+        <v>3205617348</v>
       </c>
       <c r="H71" t="s">
-        <v>404</v>
+        <v>333</v>
       </c>
       <c r="I71">
-        <v>539296</v>
+        <v>587684</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3710,28 +3461,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="D72" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="E72" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F72" t="s">
-        <v>333</v>
+        <v>246</v>
       </c>
       <c r="G72">
-        <v>3127382747</v>
+        <v>3206798318</v>
       </c>
       <c r="H72" t="s">
-        <v>405</v>
+        <v>334</v>
       </c>
       <c r="I72">
-        <v>506123</v>
+        <v>2331074</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3739,28 +3490,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C73" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D73" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="E73" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F73" t="s">
-        <v>333</v>
+        <v>246</v>
       </c>
       <c r="G73">
-        <v>3127382747</v>
+        <v>3004106594</v>
       </c>
       <c r="H73" t="s">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="I73">
-        <v>550754</v>
+        <v>601842</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3768,28 +3519,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="D74" t="s">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="E74" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F74" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="G74">
-        <v>3168660548</v>
+        <v>3004106594</v>
       </c>
       <c r="H74" t="s">
-        <v>406</v>
+        <v>335</v>
       </c>
       <c r="I74">
-        <v>1433196</v>
+        <v>1996644</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3797,28 +3548,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C75" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="D75" t="s">
-        <v>267</v>
+        <v>233</v>
       </c>
       <c r="E75" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F75" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="G75">
-        <v>3113050346</v>
+        <v>3128021315</v>
       </c>
       <c r="H75" t="s">
-        <v>407</v>
+        <v>336</v>
       </c>
       <c r="I75">
-        <v>585486</v>
+        <v>522793</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3826,28 +3577,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C76" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="D76" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="E76" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="F76" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="G76">
-        <v>3041077684</v>
+        <v>3052245305</v>
       </c>
       <c r="H76" t="s">
-        <v>408</v>
+        <v>337</v>
       </c>
       <c r="I76">
-        <v>557982</v>
+        <v>1172972</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3855,28 +3606,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C77" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D77" t="s">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="E77" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="F77" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="G77">
-        <v>3145672233</v>
+        <v>3002799011</v>
       </c>
       <c r="H77" t="s">
-        <v>409</v>
+        <v>338</v>
       </c>
       <c r="I77">
-        <v>2855968</v>
+        <v>2600115</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3884,28 +3635,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C78" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="D78" t="s">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="E78" t="s">
-        <v>285</v>
+        <v>244</v>
       </c>
       <c r="F78" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="G78">
-        <v>3145672233</v>
+        <v>3104440838</v>
       </c>
       <c r="H78" t="s">
-        <v>409</v>
+        <v>339</v>
       </c>
       <c r="I78">
-        <v>1134204</v>
+        <v>544969</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3913,434 +3664,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C79" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="D79" t="s">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="E79" t="s">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="F79" t="s">
-        <v>335</v>
+        <v>246</v>
       </c>
       <c r="G79">
-        <v>3148214908</v>
+        <v>3022250446</v>
       </c>
       <c r="H79" t="s">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="I79">
-        <v>585486</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" t="s">
-        <v>87</v>
-      </c>
-      <c r="B80" t="s">
-        <v>179</v>
-      </c>
-      <c r="C80" t="s">
-        <v>199</v>
-      </c>
-      <c r="D80" t="s">
-        <v>271</v>
-      </c>
-      <c r="E80" t="s">
-        <v>285</v>
-      </c>
-      <c r="F80" t="s">
-        <v>335</v>
-      </c>
-      <c r="G80">
-        <v>3148214908</v>
-      </c>
-      <c r="H80" t="s">
-        <v>410</v>
-      </c>
-      <c r="I80">
-        <v>1016660</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" t="s">
-        <v>180</v>
-      </c>
-      <c r="C81" t="s">
-        <v>196</v>
-      </c>
-      <c r="D81" t="s">
-        <v>272</v>
-      </c>
-      <c r="E81" t="s">
-        <v>286</v>
-      </c>
-      <c r="F81" t="s">
-        <v>336</v>
-      </c>
-      <c r="G81">
-        <v>3003438170</v>
-      </c>
-      <c r="H81" t="s">
-        <v>411</v>
-      </c>
-      <c r="I81">
-        <v>1074160</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82" t="s">
-        <v>89</v>
-      </c>
-      <c r="B82" t="s">
-        <v>181</v>
-      </c>
-      <c r="C82" t="s">
-        <v>196</v>
-      </c>
-      <c r="D82" t="s">
-        <v>273</v>
-      </c>
-      <c r="E82" t="s">
-        <v>285</v>
-      </c>
-      <c r="F82" t="s">
-        <v>337</v>
-      </c>
-      <c r="G82">
-        <v>3008765266</v>
-      </c>
-      <c r="H82" t="s">
-        <v>412</v>
-      </c>
-      <c r="I82">
-        <v>751376</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="A83" t="s">
-        <v>90</v>
-      </c>
-      <c r="B83" t="s">
-        <v>182</v>
-      </c>
-      <c r="C83" t="s">
-        <v>193</v>
-      </c>
-      <c r="D83" t="s">
-        <v>274</v>
-      </c>
-      <c r="E83" t="s">
-        <v>285</v>
-      </c>
-      <c r="F83" t="s">
-        <v>293</v>
-      </c>
-      <c r="G83">
-        <v>3213605700</v>
-      </c>
-      <c r="H83" t="s">
-        <v>413</v>
-      </c>
-      <c r="I83">
-        <v>116420</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84" t="s">
-        <v>91</v>
-      </c>
-      <c r="B84" t="s">
-        <v>183</v>
-      </c>
-      <c r="C84" t="s">
-        <v>198</v>
-      </c>
-      <c r="D84" t="s">
-        <v>275</v>
-      </c>
-      <c r="E84" t="s">
-        <v>285</v>
-      </c>
-      <c r="F84" t="s">
-        <v>338</v>
-      </c>
-      <c r="G84">
-        <v>3205617348</v>
-      </c>
-      <c r="H84" t="s">
-        <v>414</v>
-      </c>
-      <c r="I84">
-        <v>592513</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85" t="s">
-        <v>184</v>
-      </c>
-      <c r="C85" t="s">
-        <v>196</v>
-      </c>
-      <c r="D85" t="s">
-        <v>276</v>
-      </c>
-      <c r="E85" t="s">
-        <v>286</v>
-      </c>
-      <c r="F85" t="s">
-        <v>293</v>
-      </c>
-      <c r="G85">
-        <v>3206798318</v>
-      </c>
-      <c r="H85" t="s">
-        <v>415</v>
-      </c>
-      <c r="I85">
-        <v>1852045</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" t="s">
-        <v>185</v>
-      </c>
-      <c r="C86" t="s">
-        <v>195</v>
-      </c>
-      <c r="D86" t="s">
-        <v>277</v>
-      </c>
-      <c r="E86" t="s">
-        <v>286</v>
-      </c>
-      <c r="F86" t="s">
-        <v>339</v>
-      </c>
-      <c r="G86">
-        <v>3175795524</v>
-      </c>
-      <c r="H86" t="s">
-        <v>416</v>
-      </c>
-      <c r="I86">
-        <v>650772</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" t="s">
-        <v>94</v>
-      </c>
-      <c r="B87" t="s">
-        <v>186</v>
-      </c>
-      <c r="C87" t="s">
-        <v>194</v>
-      </c>
-      <c r="D87" t="s">
-        <v>278</v>
-      </c>
-      <c r="E87" t="s">
-        <v>286</v>
-      </c>
-      <c r="F87" t="s">
-        <v>293</v>
-      </c>
-      <c r="G87">
-        <v>3116803238</v>
-      </c>
-      <c r="H87" t="s">
-        <v>417</v>
-      </c>
-      <c r="I87">
-        <v>506123</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" t="s">
-        <v>95</v>
-      </c>
-      <c r="B88" t="s">
-        <v>187</v>
-      </c>
-      <c r="C88" t="s">
-        <v>202</v>
-      </c>
-      <c r="D88" t="s">
-        <v>279</v>
-      </c>
-      <c r="E88" t="s">
-        <v>285</v>
-      </c>
-      <c r="F88" t="s">
-        <v>340</v>
-      </c>
-      <c r="G88">
-        <v>3105250380</v>
-      </c>
-      <c r="H88" t="s">
-        <v>418</v>
-      </c>
-      <c r="I88">
-        <v>554327</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" t="s">
-        <v>188</v>
-      </c>
-      <c r="C89" t="s">
-        <v>198</v>
-      </c>
-      <c r="D89" t="s">
-        <v>280</v>
-      </c>
-      <c r="E89" t="s">
-        <v>285</v>
-      </c>
-      <c r="F89" t="s">
-        <v>293</v>
-      </c>
-      <c r="G89">
-        <v>3004106594</v>
-      </c>
-      <c r="H89" t="s">
-        <v>419</v>
-      </c>
-      <c r="I89">
-        <v>1329096</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" t="s">
-        <v>189</v>
-      </c>
-      <c r="C90" t="s">
-        <v>197</v>
-      </c>
-      <c r="D90" t="s">
-        <v>281</v>
-      </c>
-      <c r="E90" t="s">
-        <v>286</v>
-      </c>
-      <c r="F90" t="s">
-        <v>341</v>
-      </c>
-      <c r="G90">
-        <v>3052245305</v>
-      </c>
-      <c r="H90" t="s">
-        <v>420</v>
-      </c>
-      <c r="I90">
-        <v>585486</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" t="s">
-        <v>98</v>
-      </c>
-      <c r="B91" t="s">
-        <v>190</v>
-      </c>
-      <c r="C91" t="s">
-        <v>197</v>
-      </c>
-      <c r="D91" t="s">
-        <v>282</v>
-      </c>
-      <c r="E91" t="s">
-        <v>285</v>
-      </c>
-      <c r="F91" t="s">
-        <v>342</v>
-      </c>
-      <c r="G91">
-        <v>3002799011</v>
-      </c>
-      <c r="H91" t="s">
-        <v>421</v>
-      </c>
-      <c r="I91">
-        <v>2076092</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
-      <c r="A92" t="s">
-        <v>99</v>
-      </c>
-      <c r="B92" t="s">
-        <v>191</v>
-      </c>
-      <c r="C92" t="s">
-        <v>199</v>
-      </c>
-      <c r="D92" t="s">
-        <v>283</v>
-      </c>
-      <c r="E92" t="s">
-        <v>286</v>
-      </c>
-      <c r="F92" t="s">
-        <v>343</v>
-      </c>
-      <c r="G92">
-        <v>3104093964</v>
-      </c>
-      <c r="H92" t="s">
-        <v>422</v>
-      </c>
-      <c r="I92">
-        <v>507330</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93" t="s">
-        <v>100</v>
-      </c>
-      <c r="B93" t="s">
-        <v>192</v>
-      </c>
-      <c r="C93" t="s">
-        <v>195</v>
-      </c>
-      <c r="D93" t="s">
-        <v>284</v>
-      </c>
-      <c r="E93" t="s">
-        <v>285</v>
-      </c>
-      <c r="F93" t="s">
-        <v>293</v>
-      </c>
-      <c r="G93">
-        <v>3006871156</v>
-      </c>
-      <c r="H93" t="s">
-        <v>423</v>
-      </c>
-      <c r="I93">
-        <v>614324</v>
+        <v>670805</v>
       </c>
     </row>
   </sheetData>

--- a/Morosos/informe_reporte_morosos_50.xlsx
+++ b/Morosos/informe_reporte_morosos_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="837">
   <si>
     <t>identificacion</t>
   </si>
@@ -43,9 +43,30 @@
     <t>deuda total</t>
   </si>
   <si>
+    <t>1192469248</t>
+  </si>
+  <si>
+    <t>1192466240</t>
+  </si>
+  <si>
+    <t>1031942599</t>
+  </si>
+  <si>
+    <t>1031943765</t>
+  </si>
+  <si>
+    <t>1015194657</t>
+  </si>
+  <si>
+    <t>1020309249</t>
+  </si>
+  <si>
     <t>1036521142</t>
   </si>
   <si>
+    <t>1155715569</t>
+  </si>
+  <si>
     <t>1025661559</t>
   </si>
   <si>
@@ -61,6 +82,9 @@
     <t>1011519538</t>
   </si>
   <si>
+    <t>1020319550</t>
+  </si>
+  <si>
     <t>1020322501</t>
   </si>
   <si>
@@ -70,9 +94,36 @@
     <t>1020317655</t>
   </si>
   <si>
+    <t>1011410509</t>
+  </si>
+  <si>
+    <t>1020235465</t>
+  </si>
+  <si>
+    <t>1018274619</t>
+  </si>
+  <si>
+    <t>1032187811</t>
+  </si>
+  <si>
+    <t>1192467267</t>
+  </si>
+  <si>
+    <t>1020317989</t>
+  </si>
+  <si>
+    <t>1035006417</t>
+  </si>
+  <si>
+    <t>1025665738</t>
+  </si>
+  <si>
     <t>1033198496</t>
   </si>
   <si>
+    <t>1011412659</t>
+  </si>
+  <si>
     <t>1037130310</t>
   </si>
   <si>
@@ -82,15 +133,48 @@
     <t>1013466654</t>
   </si>
   <si>
-    <t>1025657990</t>
+    <t>1033198814</t>
+  </si>
+  <si>
+    <t>1023540172</t>
+  </si>
+  <si>
+    <t>1020317267</t>
+  </si>
+  <si>
+    <t>1020227680</t>
   </si>
   <si>
     <t>1023165980</t>
   </si>
   <si>
+    <t>1036458174</t>
+  </si>
+  <si>
+    <t>1011514095</t>
+  </si>
+  <si>
+    <t>1021935307</t>
+  </si>
+  <si>
     <t>1013358746</t>
   </si>
   <si>
+    <t>1020323596</t>
+  </si>
+  <si>
+    <t>1021935485</t>
+  </si>
+  <si>
+    <t>1025659461</t>
+  </si>
+  <si>
+    <t>1033192943</t>
+  </si>
+  <si>
+    <t>1020314407</t>
+  </si>
+  <si>
     <t>1025898446</t>
   </si>
   <si>
@@ -100,45 +184,144 @@
     <t>1035003747</t>
   </si>
   <si>
-    <t>1202213225</t>
-  </si>
-  <si>
-    <t>1025678788</t>
-  </si>
-  <si>
-    <t>1023550049</t>
+    <t>1033205457</t>
   </si>
   <si>
     <t>1021930204</t>
   </si>
   <si>
+    <t>1018275537</t>
+  </si>
+  <si>
+    <t>1020313616</t>
+  </si>
+  <si>
+    <t>1025906631</t>
+  </si>
+  <si>
+    <t>1020228180</t>
+  </si>
+  <si>
     <t>1011515086</t>
   </si>
   <si>
+    <t>1038872200</t>
+  </si>
+  <si>
+    <t>1038873057</t>
+  </si>
+  <si>
+    <t>1020230331</t>
+  </si>
+  <si>
+    <t>1020319583</t>
+  </si>
+  <si>
+    <t>1011412933</t>
+  </si>
+  <si>
+    <t>1039311523</t>
+  </si>
+  <si>
+    <t>1018254177</t>
+  </si>
+  <si>
+    <t>1018252964</t>
+  </si>
+  <si>
     <t>1013353521</t>
   </si>
   <si>
     <t>1013362371</t>
   </si>
   <si>
+    <t>1011410413</t>
+  </si>
+  <si>
+    <t>1020227383</t>
+  </si>
+  <si>
     <t>1013349020</t>
   </si>
   <si>
     <t>1013366022</t>
   </si>
   <si>
+    <t>1011517901</t>
+  </si>
+  <si>
+    <t>1011517846</t>
+  </si>
+  <si>
+    <t>1023536842</t>
+  </si>
+  <si>
     <t>1018248214</t>
   </si>
   <si>
+    <t>1020228417</t>
+  </si>
+  <si>
+    <t>1020226198</t>
+  </si>
+  <si>
+    <t>1020321633</t>
+  </si>
+  <si>
+    <t>1033204959</t>
+  </si>
+  <si>
+    <t>1033198863</t>
+  </si>
+  <si>
     <t>1042587012</t>
   </si>
   <si>
     <t>1018269052</t>
   </si>
   <si>
+    <t>1013364053</t>
+  </si>
+  <si>
+    <t>1013357048</t>
+  </si>
+  <si>
+    <t>1020227802</t>
+  </si>
+  <si>
+    <t>1035004228</t>
+  </si>
+  <si>
+    <t>1025902964</t>
+  </si>
+  <si>
+    <t>1023595038</t>
+  </si>
+  <si>
     <t>1041634370</t>
   </si>
   <si>
+    <t>1018258929</t>
+  </si>
+  <si>
+    <t>1018248468</t>
+  </si>
+  <si>
+    <t>1017283173</t>
+  </si>
+  <si>
+    <t>1021934224</t>
+  </si>
+  <si>
+    <t>1013369943</t>
+  </si>
+  <si>
+    <t>1018254830</t>
+  </si>
+  <si>
+    <t>1027663018</t>
+  </si>
+  <si>
     <t>1013350043</t>
   </si>
   <si>
@@ -148,9 +331,18 @@
     <t>1020308169</t>
   </si>
   <si>
+    <t>1018253746</t>
+  </si>
+  <si>
     <t>1018271477</t>
   </si>
   <si>
+    <t>1192469448</t>
+  </si>
+  <si>
+    <t>1025901451</t>
+  </si>
+  <si>
     <t>1025899613</t>
   </si>
   <si>
@@ -160,9 +352,18 @@
     <t>1020225476</t>
   </si>
   <si>
+    <t>1032020916</t>
+  </si>
+  <si>
     <t>1025770324</t>
   </si>
   <si>
+    <t>1013351247</t>
+  </si>
+  <si>
+    <t>1038874283</t>
+  </si>
+  <si>
     <t>1025776867</t>
   </si>
   <si>
@@ -172,9 +373,30 @@
     <t>1013370057</t>
   </si>
   <si>
+    <t>1023554474</t>
+  </si>
+  <si>
+    <t>1192465340</t>
+  </si>
+  <si>
     <t>1020307672</t>
   </si>
   <si>
+    <t>1013356816</t>
+  </si>
+  <si>
+    <t>1017935653</t>
+  </si>
+  <si>
+    <t>1020321755</t>
+  </si>
+  <si>
+    <t>1011519079</t>
+  </si>
+  <si>
+    <t>1011516886</t>
+  </si>
+  <si>
     <t>1011518615</t>
   </si>
   <si>
@@ -184,9 +406,60 @@
     <t>1020239882</t>
   </si>
   <si>
+    <t>1022150058</t>
+  </si>
+  <si>
+    <t>1020317344</t>
+  </si>
+  <si>
+    <t>1127538441</t>
+  </si>
+  <si>
+    <t>1127538440</t>
+  </si>
+  <si>
+    <t>1038871132</t>
+  </si>
+  <si>
+    <t>1025896458</t>
+  </si>
+  <si>
+    <t>1032028471</t>
+  </si>
+  <si>
+    <t>1025898909</t>
+  </si>
+  <si>
+    <t>1023648346</t>
+  </si>
+  <si>
     <t>1020323103</t>
   </si>
   <si>
+    <t>1018261585</t>
+  </si>
+  <si>
+    <t>1025897300</t>
+  </si>
+  <si>
+    <t>1201471037</t>
+  </si>
+  <si>
+    <t>1020321827</t>
+  </si>
+  <si>
+    <t>1027664379</t>
+  </si>
+  <si>
+    <t>1027663704</t>
+  </si>
+  <si>
+    <t>1020228568</t>
+  </si>
+  <si>
+    <t>1020231131</t>
+  </si>
+  <si>
     <t>1020312315</t>
   </si>
   <si>
@@ -196,18 +469,42 @@
     <t>1016601695</t>
   </si>
   <si>
+    <t>1023641253</t>
+  </si>
+  <si>
+    <t>1036457627</t>
+  </si>
+  <si>
+    <t>1195213635</t>
+  </si>
+  <si>
+    <t>1025656333</t>
+  </si>
+  <si>
     <t>1015079466</t>
   </si>
   <si>
     <t>1015077703</t>
   </si>
   <si>
+    <t>1011517041</t>
+  </si>
+  <si>
     <t>1096705038</t>
   </si>
   <si>
     <t>1018273200</t>
   </si>
   <si>
+    <t>1021941636</t>
+  </si>
+  <si>
+    <t>1035011673</t>
+  </si>
+  <si>
+    <t>1035001646</t>
+  </si>
+  <si>
     <t>1025895823</t>
   </si>
   <si>
@@ -217,6 +514,15 @@
     <t>1015075125</t>
   </si>
   <si>
+    <t>1025663772</t>
+  </si>
+  <si>
+    <t>1031943917</t>
+  </si>
+  <si>
+    <t>1021929020</t>
+  </si>
+  <si>
     <t>1025894543</t>
   </si>
   <si>
@@ -235,12 +541,21 @@
     <t>1025904957</t>
   </si>
   <si>
+    <t>1020231885</t>
+  </si>
+  <si>
+    <t>1094062535</t>
+  </si>
+  <si>
     <t>1018271176</t>
   </si>
   <si>
     <t>1018254757</t>
   </si>
   <si>
+    <t>1141722491</t>
+  </si>
+  <si>
     <t>1141719278</t>
   </si>
   <si>
@@ -250,12 +565,30 @@
     <t>1092540648</t>
   </si>
   <si>
+    <t>1020228682</t>
+  </si>
+  <si>
+    <t>1023638076</t>
+  </si>
+  <si>
+    <t>1023595113</t>
+  </si>
+  <si>
     <t>1084474489</t>
   </si>
   <si>
+    <t>1015194725</t>
+  </si>
+  <si>
     <t>1025667898</t>
   </si>
   <si>
+    <t>1033200952</t>
+  </si>
+  <si>
+    <t>1033190800</t>
+  </si>
+  <si>
     <t>1025896997</t>
   </si>
   <si>
@@ -265,21 +598,60 @@
     <t>1034925183</t>
   </si>
   <si>
+    <t>1021929142</t>
+  </si>
+  <si>
     <t>1034924450</t>
   </si>
   <si>
     <t>1025900606</t>
   </si>
   <si>
+    <t>1023652438</t>
+  </si>
+  <si>
+    <t>1021929216</t>
+  </si>
+  <si>
     <t>1023654563</t>
   </si>
   <si>
+    <t>1023655274</t>
+  </si>
+  <si>
+    <t>1021939636</t>
+  </si>
+  <si>
     <t>1023655835</t>
   </si>
   <si>
+    <t>1042153354</t>
+  </si>
+  <si>
+    <t>Aguirre Gomez Ariana</t>
+  </si>
+  <si>
+    <t>Aguirre Gomez Susana</t>
+  </si>
+  <si>
+    <t>Alvarez Cano Elizabeth</t>
+  </si>
+  <si>
+    <t>Alvarez Cano Yerik</t>
+  </si>
+  <si>
+    <t>Alvarez Teran Josue</t>
+  </si>
+  <si>
+    <t>Alvarez Valencia Ana Elisa</t>
+  </si>
+  <si>
     <t>Alzate Monsalve David</t>
   </si>
   <si>
+    <t>Arango Gomez Julieta</t>
+  </si>
+  <si>
     <t>Arango Salazar Luciana</t>
   </si>
   <si>
@@ -295,6 +667,9 @@
     <t>Arenas Calderon Salomon</t>
   </si>
   <si>
+    <t>Arroyave Gonzalez Elisabet</t>
+  </si>
+  <si>
     <t>Artunduaga Burgos Emmanuel</t>
   </si>
   <si>
@@ -304,9 +679,36 @@
     <t>Artunduaga Burgos Sarahy</t>
   </si>
   <si>
+    <t>Atehortua Quintero Miguel Angel</t>
+  </si>
+  <si>
+    <t>Atehortua Quintero Simon</t>
+  </si>
+  <si>
+    <t>Bedoya Garcia Juana Valentina</t>
+  </si>
+  <si>
+    <t>Betancur Buenaño Valeria</t>
+  </si>
+  <si>
+    <t>Betancur Cardona Samuel</t>
+  </si>
+  <si>
+    <t>Betancur Mesa Sara</t>
+  </si>
+  <si>
+    <t>Betancur Ortiz Isabella</t>
+  </si>
+  <si>
+    <t>Betancur Zapata Emanuel</t>
+  </si>
+  <si>
     <t>Bran Arrieta Saray</t>
   </si>
   <si>
+    <t>Buitrago Caicedo Juan Sebastian</t>
+  </si>
+  <si>
     <t>Cardenas Martinez Cristian Mathias</t>
   </si>
   <si>
@@ -316,15 +718,48 @@
     <t>Cardona Mosquera Roxana</t>
   </si>
   <si>
-    <t>Carvajal Gomez Shari Lined</t>
+    <t>Carmona Taborda Luciana</t>
+  </si>
+  <si>
+    <t>Caro Soto Samuel</t>
+  </si>
+  <si>
+    <t>Caro Vidal Isabella</t>
+  </si>
+  <si>
+    <t>Castañeda Gil Valeria</t>
   </si>
   <si>
     <t>Castaño Patiño Juan Jose</t>
   </si>
   <si>
+    <t>Castaño Ramirez Matias</t>
+  </si>
+  <si>
+    <t>Castaño Viloria Sara</t>
+  </si>
+  <si>
+    <t>Castaño Zapata Ambar</t>
+  </si>
+  <si>
     <t>Chavarria Osorio Luna Celeste</t>
   </si>
   <si>
+    <t>Chaverra Gomez Rebeca</t>
+  </si>
+  <si>
+    <t>Clavijo Quiceno Sara</t>
+  </si>
+  <si>
+    <t>Correa Castañeda Laura</t>
+  </si>
+  <si>
+    <t>Correa Castaño Christopher</t>
+  </si>
+  <si>
+    <t>Correa Henao Sofia</t>
+  </si>
+  <si>
     <t>Cortes Correa Rebeca</t>
   </si>
   <si>
@@ -334,45 +769,144 @@
     <t>Cuervo Consuegra Tamara</t>
   </si>
   <si>
-    <t>De Luquez Bernal Mabel Sarai</t>
-  </si>
-  <si>
-    <t>Diaz Gamboa Isaac</t>
-  </si>
-  <si>
-    <t>Diaz Gamboa Moises Uzziel</t>
+    <t>Diaz Castaño Emilia</t>
   </si>
   <si>
     <t>Diaz Gonzalez Matias</t>
   </si>
   <si>
+    <t>Diez Ortega Isaac</t>
+  </si>
+  <si>
+    <t>Duque Bermudez Juan Andres</t>
+  </si>
+  <si>
+    <t>Durango Vasco Mara</t>
+  </si>
+  <si>
+    <t>Echavarria Muñoz Isabella</t>
+  </si>
+  <si>
     <t>Echeverri Agudelo Samuel</t>
   </si>
   <si>
+    <t>Escalante Martinez Samuel</t>
+  </si>
+  <si>
+    <t>Escalante Martinez Sara</t>
+  </si>
+  <si>
+    <t>Ferraro Gallego Santiago</t>
+  </si>
+  <si>
+    <t>Florez Henao Stefany</t>
+  </si>
+  <si>
+    <t>Florez Puerta Sofia</t>
+  </si>
+  <si>
+    <t>Garcia Arias Jheremy David</t>
+  </si>
+  <si>
+    <t>Garcia Correa Andres Esteban</t>
+  </si>
+  <si>
+    <t>Garcia Gonzalez Juan Manuel</t>
+  </si>
+  <si>
     <t>Garcia Ramirez Nicolas</t>
   </si>
   <si>
     <t>Garcia Ramirez Thomás</t>
   </si>
   <si>
+    <t>Garzon Herrera Joel</t>
+  </si>
+  <si>
+    <t>Garzon Moreno Cristian</t>
+  </si>
+  <si>
     <t>Gaviria Cespedes Brenda</t>
   </si>
   <si>
     <t>Gaviria Cespedes Evelyn</t>
   </si>
   <si>
+    <t>Gil Arroyo David</t>
+  </si>
+  <si>
+    <t>Giraldo Lozano Emma</t>
+  </si>
+  <si>
+    <t>Giraldo Ramirez Susana</t>
+  </si>
+  <si>
     <t>Gomez Buitrago Mariangel</t>
   </si>
   <si>
+    <t>Gonzalez Bedoya Gracia</t>
+  </si>
+  <si>
+    <t>Gonzalez Bedoya Juanita</t>
+  </si>
+  <si>
+    <t>Gonzalez Gamboa Julieta</t>
+  </si>
+  <si>
+    <t>Granda Jaramillo Agustin</t>
+  </si>
+  <si>
+    <t>Granda Jaramillo Benjamin</t>
+  </si>
+  <si>
     <t>Guette Ortiz Ashley Carolina</t>
   </si>
   <si>
     <t>Guette Ortiz Norah Isabella</t>
   </si>
   <si>
+    <t>Henao Pinilla Simon</t>
+  </si>
+  <si>
+    <t>Herrera Higuita Antonia</t>
+  </si>
+  <si>
+    <t>Higuita Hurtado Matias</t>
+  </si>
+  <si>
+    <t>Hoyos Barrera Maximiliano</t>
+  </si>
+  <si>
+    <t>Hurtado Hurtado Sara</t>
+  </si>
+  <si>
+    <t>Isaza España Guadalupe</t>
+  </si>
+  <si>
     <t>Jaramillo Agudelo Ana Sofia</t>
   </si>
   <si>
+    <t>Jaramillo Carranza Camila</t>
+  </si>
+  <si>
+    <t>Jaramillo Carranza Santiago</t>
+  </si>
+  <si>
+    <t>Jarvis Estrada Arya Elowyn</t>
+  </si>
+  <si>
+    <t>Jovel Gomez Pedro Manuel</t>
+  </si>
+  <si>
+    <t>Londoño Jaramillo Samuel</t>
+  </si>
+  <si>
+    <t>Londoño Sanchez Antonia</t>
+  </si>
+  <si>
+    <t>Lopera Pino Simon</t>
+  </si>
+  <si>
     <t>Luna Rincon Juan Sebastian</t>
   </si>
   <si>
@@ -382,9 +916,18 @@
     <t>Manco Fonnegra Samuel</t>
   </si>
   <si>
+    <t>Marin Jaramillo Nicolas</t>
+  </si>
+  <si>
     <t>Marin Vergara Nicolas</t>
   </si>
   <si>
+    <t>Marquez Mora Emilia</t>
+  </si>
+  <si>
+    <t>Martinez Alvarez Daniella</t>
+  </si>
+  <si>
     <t>Martinez Alvarez Thiago</t>
   </si>
   <si>
@@ -394,9 +937,18 @@
     <t>Martinez Correa Tomas</t>
   </si>
   <si>
+    <t>Meneses Jimenez Mariangel</t>
+  </si>
+  <si>
     <t>Mesa Cardona Mariangel</t>
   </si>
   <si>
+    <t>Miranda Florez Josue David</t>
+  </si>
+  <si>
+    <t>Monroy Garcia Sharon Yissel</t>
+  </si>
+  <si>
     <t>Montoya Crumb Ahavah Joy</t>
   </si>
   <si>
@@ -406,9 +958,30 @@
     <t>Montoya Crumb Samuel Robert</t>
   </si>
   <si>
+    <t>Montoya Serrano Isaac</t>
+  </si>
+  <si>
+    <t>Munive Echeverri Ariadna</t>
+  </si>
+  <si>
     <t>Muñoz Vellojin Mateo</t>
   </si>
   <si>
+    <t>Ochoa Herrera Michelle</t>
+  </si>
+  <si>
+    <t>Ochoa Herrera Sara</t>
+  </si>
+  <si>
+    <t>Orozco Velez Emiliano</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Analucia</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Benjamin</t>
+  </si>
+  <si>
     <t>Ortega Zabala Abigail</t>
   </si>
   <si>
@@ -418,9 +991,60 @@
     <t>Ortiz Cano Sara</t>
   </si>
   <si>
+    <t>Ortiz Monsalve Sebastian</t>
+  </si>
+  <si>
+    <t>Ortiz Montoya Matias</t>
+  </si>
+  <si>
+    <t>Ospina Perez Isabella</t>
+  </si>
+  <si>
+    <t>Ospina Perez Samuel</t>
+  </si>
+  <si>
+    <t>Ospina Tuberquia Miguel Angel</t>
+  </si>
+  <si>
+    <t>Pacheco Giraldo Santiago</t>
+  </si>
+  <si>
+    <t>Perea Sanchez Maycol Stiven</t>
+  </si>
+  <si>
+    <t>Perez Coronado David</t>
+  </si>
+  <si>
+    <t>Perez Cortes Sara</t>
+  </si>
+  <si>
     <t>Perez Pino Susana</t>
   </si>
   <si>
+    <t>Peña González Sophia</t>
+  </si>
+  <si>
+    <t>Piedrahita Restrepo Mariana</t>
+  </si>
+  <si>
+    <t>Pineda Perez Emily Marian</t>
+  </si>
+  <si>
+    <t>Posada Alzate Abraham</t>
+  </si>
+  <si>
+    <t>Prieto Albán Isaac</t>
+  </si>
+  <si>
+    <t>Prieto Albán Mathías</t>
+  </si>
+  <si>
+    <t>Puerta Vanegas Isabel</t>
+  </si>
+  <si>
+    <t>Puerta Vanegas Maria Antonia</t>
+  </si>
+  <si>
     <t>Pérez Hernández Salomé</t>
   </si>
   <si>
@@ -430,18 +1054,42 @@
     <t>Ramirez Avila Sara</t>
   </si>
   <si>
+    <t>Ramirez Morales Salome</t>
+  </si>
+  <si>
+    <t>Ramirez Ramirez Luciana</t>
+  </si>
+  <si>
+    <t>Restrepo Cadavid Emanuel</t>
+  </si>
+  <si>
+    <t>Restrepo Cadavid Isabela</t>
+  </si>
+  <si>
     <t>Restrepo Cortes Isabella</t>
   </si>
   <si>
     <t>Restrepo Cortes Juan Manuel</t>
   </si>
   <si>
+    <t>Rios Hurtado Miguel Angel</t>
+  </si>
+  <si>
     <t>Rizo Paez David Armando</t>
   </si>
   <si>
     <t>Rizo Paez Elisa Victoria</t>
   </si>
   <si>
+    <t>Rojas Jimenez Sofia</t>
+  </si>
+  <si>
+    <t>Rueda Alvarez Josue</t>
+  </si>
+  <si>
+    <t>Rueda Alvarez Julieta</t>
+  </si>
+  <si>
     <t>Ruiz Aristizabal Nicolas</t>
   </si>
   <si>
@@ -451,6 +1099,15 @@
     <t>Ruiz Rodas Jacobo</t>
   </si>
   <si>
+    <t>Ruiz Urquijo Martin</t>
+  </si>
+  <si>
+    <t>Ruiz Urquijo Violeta</t>
+  </si>
+  <si>
+    <t>Saldarriaga Aguirre Hannah</t>
+  </si>
+  <si>
     <t>Saldarriaga Isaza Ana Sofia</t>
   </si>
   <si>
@@ -469,12 +1126,21 @@
     <t>Sanchez Justiniano Jose David</t>
   </si>
   <si>
+    <t>Sanchez Otalvaro Guadalupe</t>
+  </si>
+  <si>
+    <t>Sanchez Peñaranda Hernan Enrique</t>
+  </si>
+  <si>
     <t>Sayago Acevedo Isabella</t>
   </si>
   <si>
     <t>Sayago Acevedo Samuel</t>
   </si>
   <si>
+    <t>Segura Rios Emmanuel David</t>
+  </si>
+  <si>
     <t>Segura Rios Samuel Felipe</t>
   </si>
   <si>
@@ -484,12 +1150,30 @@
     <t>Sierra Peñaranda Miguel Angel</t>
   </si>
   <si>
+    <t>Suescun Yepes Juan Manuel</t>
+  </si>
+  <si>
+    <t>Suescun Yepes Luciana</t>
+  </si>
+  <si>
+    <t>Tabares Martinez Martina</t>
+  </si>
+  <si>
     <t>Tenorio Maya Liam</t>
   </si>
   <si>
+    <t>Torres Ramirez Cristian David</t>
+  </si>
+  <si>
     <t>Troya Rendon Emanuel</t>
   </si>
   <si>
+    <t>Usma Jaramillo Maria Celeste</t>
+  </si>
+  <si>
+    <t>Usuga Hidalgo Juan Sebastian</t>
+  </si>
+  <si>
     <t>Vanegas Olaya Cristopher</t>
   </si>
   <si>
@@ -499,34 +1183,61 @@
     <t>Vanegas Pulgarin Sheray</t>
   </si>
   <si>
+    <t>Vargas Wilches Maria Jose</t>
+  </si>
+  <si>
     <t>Vasquez Rodas Josue</t>
   </si>
   <si>
     <t>Velez Ortiz Simon</t>
   </si>
   <si>
+    <t>Vera Montoya Markos</t>
+  </si>
+  <si>
+    <t>Villegas Vargas Mariangel</t>
+  </si>
+  <si>
     <t>Yepes Murillo Mariangel</t>
   </si>
   <si>
+    <t>Zambrano Mejia Mariangel</t>
+  </si>
+  <si>
+    <t>Zapata Becerra Elizabeth</t>
+  </si>
+  <si>
     <t>Zapata Echeverry Abigail</t>
   </si>
   <si>
+    <t>Zapata Ochoa Mariangel</t>
+  </si>
+  <si>
+    <t>SEGUNDO</t>
+  </si>
+  <si>
+    <t>NOVENO</t>
+  </si>
+  <si>
+    <t>OCTAVO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>QUINTO</t>
+  </si>
+  <si>
+    <t>DÉCIMO</t>
+  </si>
+  <si>
     <t>CUARTO</t>
   </si>
   <si>
-    <t>DÉCIMO</t>
-  </si>
-  <si>
     <t>ONCE</t>
   </si>
   <si>
-    <t>OCTAVO</t>
-  </si>
-  <si>
-    <t>SEGUNDO</t>
-  </si>
-  <si>
-    <t>QUINTO</t>
+    <t>SEXTO</t>
   </si>
   <si>
     <t>TRANSICIÓN</t>
@@ -535,24 +1246,33 @@
     <t>SEPTIMO</t>
   </si>
   <si>
-    <t>SEXTO</t>
+    <t>PRIMERO</t>
   </si>
   <si>
     <t>PRE-JARDIN</t>
   </si>
   <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>NOVENO</t>
-  </si>
-  <si>
-    <t>PRIMERO</t>
+    <t>Aguirre Naranjo Bryan Stiven</t>
+  </si>
+  <si>
+    <t>Alvarez Velez Victor Alfonso</t>
+  </si>
+  <si>
+    <t>Cano Zapata Stefanny</t>
+  </si>
+  <si>
+    <t>Alvarez Carlos Mario</t>
+  </si>
+  <si>
+    <t>Alvarez Arbelaez Hector Dario</t>
   </si>
   <si>
     <t>Alzate Villa William</t>
   </si>
   <si>
+    <t>Gomez Ruiz Natalia</t>
+  </si>
+  <si>
     <t>Castellanos Pinoz Johan Mateo</t>
   </si>
   <si>
@@ -562,63 +1282,213 @@
     <t>Arenas Villa Harold Alexander</t>
   </si>
   <si>
+    <t>Arroyave Mesa Juan Carlos</t>
+  </si>
+  <si>
     <t>Artunduaga Cabrera Anderson</t>
   </si>
   <si>
+    <t>Atehortua Morales Didier</t>
+  </si>
+  <si>
+    <t>Garcia Payares Luz Mery</t>
+  </si>
+  <si>
+    <t>Betancur Sanchez Juan Alfonso</t>
+  </si>
+  <si>
+    <t>Cardona Gómez Marcela</t>
+  </si>
+  <si>
+    <t>Mesa Concha Veronica Maria</t>
+  </si>
+  <si>
+    <t>Ortiz Monsalve Natalia</t>
+  </si>
+  <si>
+    <t>Betancur Gomez Henry Alejandro</t>
+  </si>
+  <si>
     <t>Arrieta Mendoza Liseth</t>
   </si>
   <si>
+    <t>Buitrago Gonzalez Edison Alexander</t>
+  </si>
+  <si>
     <t>Cardenas Cordero Christian Enrique</t>
   </si>
   <si>
     <t>Mosquera Rodriguez Tania Karina</t>
   </si>
   <si>
-    <t>Gomez Montes Jaime William</t>
+    <t>Cardona Villarreal Alba Mery</t>
+  </si>
+  <si>
+    <t>Caro Rivas Grovis Yinois</t>
+  </si>
+  <si>
+    <t>Caro Gomez Jhojan Fernando</t>
+  </si>
+  <si>
+    <t>Gil Sanchez Marcela</t>
   </si>
   <si>
     <t>Castaño Zapata Jose Fernando</t>
   </si>
   <si>
+    <t>Ramirez Ortiz Melissa</t>
+  </si>
+  <si>
+    <t>Viloria Montoya Isabel Cristina</t>
+  </si>
+  <si>
+    <t>Castano Mesa Fray David</t>
+  </si>
+  <si>
     <t>Chavarria Ramirez Roman Alberto</t>
   </si>
   <si>
+    <t>Chaverra Chaverra Juan David</t>
+  </si>
+  <si>
+    <t>Carreño Bohorquez Nora Maria</t>
+  </si>
+  <si>
+    <t>Correa Correa Mauricio</t>
+  </si>
+  <si>
+    <t>Correa Santana Edwin Andres</t>
+  </si>
+  <si>
+    <t>Correa Ibarra Raul Angel</t>
+  </si>
+  <si>
     <t>Cortes Velasquez Juan Pablo</t>
   </si>
   <si>
     <t>Cuervo Paternina Eder Andres</t>
   </si>
   <si>
-    <t>De Luquez Diaz Ezequiel</t>
-  </si>
-  <si>
-    <t>Diaz Moncaleano Carlos Andres</t>
+    <t>Diaz Naranjo Jaime Orlando</t>
   </si>
   <si>
     <t>Diaz Rico John Edwin</t>
   </si>
   <si>
+    <t>Ortega Arcila Adiela Yohana</t>
+  </si>
+  <si>
+    <t>Duque Botero Johnny Yesid</t>
+  </si>
+  <si>
+    <t>Vasco Ortiz Yeimy Natalia</t>
+  </si>
+  <si>
+    <t>Echavarría Arley Fernando</t>
+  </si>
+  <si>
     <t>Echeverry Agudelo Sara Catalina</t>
   </si>
   <si>
+    <t>Forero Reyes Janeth</t>
+  </si>
+  <si>
+    <t>Ferraro Trejos Diego Gian Franco</t>
+  </si>
+  <si>
+    <t>Florez Sanchez Miguel Angel</t>
+  </si>
+  <si>
+    <t>Florez Oliveros Uberney</t>
+  </si>
+  <si>
+    <t>Garcia Gomez Reinaldo David</t>
+  </si>
+  <si>
+    <t>Correa Osorio Luisa Fernanda</t>
+  </si>
+  <si>
+    <t>Gonzalez Mora Julieth Marcela</t>
+  </si>
+  <si>
     <t>Ramirez Suarez Leidy Tatiana</t>
   </si>
   <si>
     <t>Garcia Valencia Cesar Augusto</t>
   </si>
   <si>
+    <t>Garzon Garcia Milton Arley</t>
+  </si>
+  <si>
+    <t>Garzon Prieto Nelson Fidel</t>
+  </si>
+  <si>
     <t>Cespedes Restrepo Maria Alejandra</t>
   </si>
   <si>
+    <t>Gil Clavijo Luber Mario</t>
+  </si>
+  <si>
+    <t>Lozano Mosquera Mariam</t>
+  </si>
+  <si>
+    <t>Giraldo Montoya Norberto Alonso</t>
+  </si>
+  <si>
     <t>Gomez Rios Geovanny Arley</t>
   </si>
   <si>
+    <t>Gonzalez Diaz Mauricio De Jesus</t>
+  </si>
+  <si>
+    <t>Gamboa Melendrez Jeniffer</t>
+  </si>
+  <si>
+    <t>Jaramillo Gallego Maria Eugenia</t>
+  </si>
+  <si>
     <t>Ortiz Julio Sirly Dayana</t>
   </si>
   <si>
+    <t>Henao Betancur Jorge Humberto</t>
+  </si>
+  <si>
+    <t>Herrera Serna Oscar Alejandro</t>
+  </si>
+  <si>
+    <t>Hurtado Rossi Vianey Mariela</t>
+  </si>
+  <si>
+    <t>Barrera Zapata Alejandra</t>
+  </si>
+  <si>
+    <t>Hurtado Orozco Yudi Andrea</t>
+  </si>
+  <si>
+    <t>Ramirez Quintero Maria Teresa</t>
+  </si>
+  <si>
     <t>Agudelo Torres Sumilde Elena</t>
   </si>
   <si>
+    <t>Carranza Ricardo Diana Marcela</t>
+  </si>
+  <si>
+    <t>Estrada Vargas Susana</t>
+  </si>
+  <si>
+    <t>Corena De Gomez Ena Luz</t>
+  </si>
+  <si>
+    <t>Londoño Moreno Andres Felipe</t>
+  </si>
+  <si>
+    <t>Sanchez Isaura Pilar</t>
+  </si>
+  <si>
+    <t>Lopera Echeverri John Jairo</t>
+  </si>
+  <si>
     <t>Rincon Lopera Liliana Maria</t>
   </si>
   <si>
@@ -628,9 +1498,18 @@
     <t>Manco Echavarria Reynel De Jesus</t>
   </si>
   <si>
+    <t>Marin Jaramillo Juan Camilo</t>
+  </si>
+  <si>
     <t>Vergara Mejia Sara Valentina</t>
   </si>
   <si>
+    <t>Mora Cardona Katherine</t>
+  </si>
+  <si>
+    <t>Y Esperanza - Cfe Iglesia Centro De Fe</t>
+  </si>
+  <si>
     <t>Hernandez Morelo Liliana</t>
   </si>
   <si>
@@ -640,36 +1519,120 @@
     <t>Correa Mejia Catalina</t>
   </si>
   <si>
+    <t>Meneses Schroeder Henry Harold</t>
+  </si>
+  <si>
     <t>Cardona Gaviria Maribel</t>
   </si>
   <si>
+    <t>Miranda Giraldo David</t>
+  </si>
+  <si>
+    <t>Garcia Lancheros Yurani Yissel</t>
+  </si>
+  <si>
     <t>Montoya Diaz Luis Fernando</t>
   </si>
   <si>
+    <t>Alvarez Arboleda Blanca Gladys</t>
+  </si>
+  <si>
+    <t>Echeverri Gallego Monica Patricia</t>
+  </si>
+  <si>
     <t>Vellojin Cavadia Tania Marjolia</t>
   </si>
   <si>
+    <t>Sas Prosteam</t>
+  </si>
+  <si>
+    <t>Velez Ortiz Jeniffer</t>
+  </si>
+  <si>
+    <t>Orrego Zuluaga Juan Esteban</t>
+  </si>
+  <si>
     <t>Zabala Cuervo Diana Rocio</t>
   </si>
   <si>
     <t>Cano Guarin Sandra Milena</t>
   </si>
   <si>
+    <t>Ortiz Aristizabal Gabriel Jaime</t>
+  </si>
+  <si>
+    <t>Montoya Silva Paula Andrea</t>
+  </si>
+  <si>
+    <t>Ospina Granda Diego Alexander</t>
+  </si>
+  <si>
+    <t>Ospina Diaz Carlos Arturo</t>
+  </si>
+  <si>
+    <t>Pacheco Basilio Wiliam</t>
+  </si>
+  <si>
+    <t>Perea Mosquera Jose Epifanio</t>
+  </si>
+  <si>
+    <t>Perez Bohorquez Jhon Robert</t>
+  </si>
+  <si>
+    <t>Perez Betancur Luis Geovanny</t>
+  </si>
+  <si>
     <t>Perez Toro Juan Pablo</t>
   </si>
   <si>
+    <t>Peña Solórzano Francisco Javier</t>
+  </si>
+  <si>
+    <t>Piedrahita Bracamonte Alan Yesith</t>
+  </si>
+  <si>
+    <t>Integrales Sas Areda Consultores</t>
+  </si>
+  <si>
+    <t>Posada Suarez Gabriel Fernando</t>
+  </si>
+  <si>
+    <t>Prieto Oyaga Cristhian Camilo</t>
+  </si>
+  <si>
+    <t>Puerta Mejia Luis Felipe</t>
+  </si>
+  <si>
     <t>Hernandez Cardona Mauricio</t>
   </si>
   <si>
     <t>Ramirez Urrutia Fredy</t>
   </si>
   <si>
+    <t>Callejas Acevedo Geovanny</t>
+  </si>
+  <si>
+    <t>Ramirez Puerta Johnnatan</t>
+  </si>
+  <si>
+    <t>Restrepo Duque Jorge Mauricio</t>
+  </si>
+  <si>
     <t>Restrepo Silva Jeison</t>
   </si>
   <si>
+    <t>Hurtado Garzon Rosalba</t>
+  </si>
+  <si>
     <t>Rizo Ibanez Jorge Armando</t>
   </si>
   <si>
+    <t>Marino Millan Yelitza Rossana</t>
+  </si>
+  <si>
+    <t>Rueda Piedrahita Carlos Ariel</t>
+  </si>
+  <si>
     <t>Agudelo Ruiz Sergio Mario</t>
   </si>
   <si>
@@ -679,6 +1642,12 @@
     <t>Rodas Marin Monica Janeth</t>
   </si>
   <si>
+    <t>Ruiz Cardona Pablo Andres</t>
+  </si>
+  <si>
+    <t>Claudina Estela Aguirre Diaz</t>
+  </si>
+  <si>
     <t>Saldarriaga Gonzalez Carlos Mario</t>
   </si>
   <si>
@@ -691,6 +1660,12 @@
     <t>Sanchez Justiniano Martha Catherine</t>
   </si>
   <si>
+    <t>Sanchez Agudelo Uber Herney</t>
+  </si>
+  <si>
+    <t>Hernandez Ospina Juan Camilo</t>
+  </si>
+  <si>
     <t>Sayago Montes Juan Esteban</t>
   </si>
   <si>
@@ -703,105 +1678,240 @@
     <t>Arboleda Ramirez Daniel Andres</t>
   </si>
   <si>
-    <t>Hernandez Ospina Juan Camilo</t>
+    <t>Suescun Gomez Jhony Alexander</t>
+  </si>
+  <si>
+    <t>Tabares Vergara Sergio Adrian</t>
   </si>
   <si>
     <t>Marin Osorio Johny Alexander</t>
   </si>
   <si>
+    <t>Ramirez Duque Ana Sofia</t>
+  </si>
+  <si>
     <t>Troya Osorio Manuel Enrique</t>
   </si>
   <si>
+    <t>Usma Acevedo Elkin Humberto</t>
+  </si>
+  <si>
+    <t>Usuga Sepulveda Henrry</t>
+  </si>
+  <si>
     <t>Olaya Rojas Liliana Maria</t>
   </si>
   <si>
     <t>Vanegas Zuñiga Ray Andres</t>
   </si>
   <si>
+    <t>Vargas Ramos Ivan Isidro</t>
+  </si>
+  <si>
     <t>Vasquez Gomez Alejandro</t>
   </si>
   <si>
     <t>Ortiz Velez Laura Catalina</t>
   </si>
   <si>
+    <t>Vera Villa Juan Ferney</t>
+  </si>
+  <si>
+    <t>Villegas Gonzalez Wbeimar Alexander</t>
+  </si>
+  <si>
     <t>Yepes Arias Angela Maria</t>
   </si>
   <si>
+    <t>Santana Marulanda Stuart</t>
+  </si>
+  <si>
+    <t>Zapata Andrade Yicmar Lice</t>
+  </si>
+  <si>
     <t>Echeverry Giraldo Estefania</t>
   </si>
   <si>
+    <t>Valencia Mesa Jose Antonio</t>
+  </si>
+  <si>
     <t>Madre</t>
   </si>
   <si>
+    <t>Padre</t>
+  </si>
+  <si>
     <t>Padrastro</t>
   </si>
   <si>
-    <t>Padre</t>
-  </si>
-  <si>
     <t>Abuelo</t>
   </si>
   <si>
+    <t>Abuela</t>
+  </si>
+  <si>
+    <t>Tía</t>
+  </si>
+  <si>
     <t>Tío</t>
   </si>
   <si>
     <t>Otro</t>
   </si>
   <si>
-    <t>Tía</t>
+    <t>Madrastra</t>
+  </si>
+  <si>
+    <t>6045060067</t>
+  </si>
+  <si>
+    <t>6045214174</t>
+  </si>
+  <si>
+    <t>3108365106</t>
+  </si>
+  <si>
+    <t>3639407</t>
   </si>
   <si>
     <t>3008486499</t>
   </si>
   <si>
+    <t>3177957854</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
     <t>2988855</t>
   </si>
   <si>
+    <t>5993988</t>
+  </si>
+  <si>
+    <t>4794235</t>
+  </si>
+  <si>
+    <t>4210191</t>
+  </si>
+  <si>
+    <t>3005565956</t>
+  </si>
+  <si>
+    <t>3013747979</t>
+  </si>
+  <si>
     <t>3235009283</t>
   </si>
   <si>
+    <t>5780406</t>
+  </si>
+  <si>
     <t>5671163</t>
   </si>
   <si>
     <t>5095498</t>
   </si>
   <si>
+    <t>6044444614</t>
+  </si>
+  <si>
+    <t>6042094813</t>
+  </si>
+  <si>
+    <t>4884681</t>
+  </si>
+  <si>
     <t>5075518</t>
   </si>
   <si>
+    <t>5467166</t>
+  </si>
+  <si>
     <t>3104067600</t>
   </si>
   <si>
+    <t>4579679</t>
+  </si>
+  <si>
+    <t>4432431</t>
+  </si>
+  <si>
+    <t>5036230</t>
+  </si>
+  <si>
     <t>2973675</t>
   </si>
   <si>
     <t>2068714</t>
   </si>
   <si>
-    <t>5823889</t>
-  </si>
-  <si>
     <t>,</t>
   </si>
   <si>
+    <t>2941548</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>3015686911</t>
+  </si>
+  <si>
+    <t>4667872</t>
+  </si>
+  <si>
+    <t>2612413</t>
+  </si>
+  <si>
+    <t>3013564721</t>
+  </si>
+  <si>
     <t>4076883</t>
   </si>
   <si>
+    <t>5864004</t>
+  </si>
+  <si>
     <t>4337791</t>
   </si>
   <si>
+    <t>3204743</t>
+  </si>
+  <si>
+    <t>3204103173</t>
+  </si>
+  <si>
+    <t>3135494642</t>
+  </si>
+  <si>
+    <t>4889842</t>
+  </si>
+  <si>
+    <t>5802808</t>
+  </si>
+  <si>
+    <t>3206895990</t>
+  </si>
+  <si>
     <t>5O9 80 21</t>
   </si>
   <si>
+    <t>6045039986</t>
+  </si>
+  <si>
     <t>6045038065</t>
   </si>
   <si>
+    <t>4811500</t>
+  </si>
+  <si>
+    <t>2678435</t>
+  </si>
+  <si>
+    <t>6044981533</t>
+  </si>
+  <si>
     <t>5060713</t>
   </si>
   <si>
@@ -811,24 +1921,93 @@
     <t>3136549427</t>
   </si>
   <si>
+    <t>4986408</t>
+  </si>
+  <si>
     <t>4773589</t>
   </si>
   <si>
+    <t>4778965</t>
+  </si>
+  <si>
+    <t>3137429086</t>
+  </si>
+  <si>
+    <t>6046037438</t>
+  </si>
+  <si>
     <t>5700932</t>
   </si>
   <si>
+    <t>5778513</t>
+  </si>
+  <si>
+    <t>4172927</t>
+  </si>
+  <si>
+    <t>3006234263</t>
+  </si>
+  <si>
     <t>6044420606</t>
   </si>
   <si>
+    <t>4485126</t>
+  </si>
+  <si>
+    <t>5851486</t>
+  </si>
+  <si>
+    <t>5022541</t>
+  </si>
+  <si>
+    <t>4075494</t>
+  </si>
+  <si>
+    <t>3155926149</t>
+  </si>
+  <si>
+    <t>5848983</t>
+  </si>
+  <si>
     <t>6045061121</t>
   </si>
   <si>
+    <t>5839111</t>
+  </si>
+  <si>
+    <t>3178333446</t>
+  </si>
+  <si>
+    <t>5789404</t>
+  </si>
+  <si>
+    <t>6010071</t>
+  </si>
+  <si>
+    <t>3323915</t>
+  </si>
+  <si>
     <t>3112860092</t>
   </si>
   <si>
+    <t>5042146</t>
+  </si>
+  <si>
+    <t>3134633058</t>
+  </si>
+  <si>
+    <t>5044236</t>
+  </si>
+  <si>
     <t>2840252</t>
   </si>
   <si>
+    <t>4802180</t>
+  </si>
+  <si>
+    <t>2941876</t>
+  </si>
+  <si>
     <t>5590297</t>
   </si>
   <si>
@@ -838,30 +2017,69 @@
     <t>4330808</t>
   </si>
   <si>
+    <t>4613821</t>
+  </si>
+  <si>
+    <t>6008276</t>
+  </si>
+  <si>
     <t>5863905</t>
   </si>
   <si>
     <t>5771821</t>
   </si>
   <si>
-    <t>6008276</t>
+    <t>6045901145</t>
+  </si>
+  <si>
+    <t>5797398</t>
   </si>
   <si>
     <t>3205617348</t>
   </si>
   <si>
+    <t>4381023</t>
+  </si>
+  <si>
+    <t>3184795864</t>
+  </si>
+  <si>
     <t>4984861</t>
   </si>
   <si>
     <t>4882576</t>
   </si>
   <si>
+    <t>3113582464</t>
+  </si>
+  <si>
     <t>3104440838</t>
   </si>
   <si>
+    <t>2578292</t>
+  </si>
+  <si>
+    <t>3127971899</t>
+  </si>
+  <si>
+    <t>bryansan87@gmail.com</t>
+  </si>
+  <si>
+    <t>vialve0702@hotmail.com</t>
+  </si>
+  <si>
+    <t>yadite79@hotmail.com</t>
+  </si>
+  <si>
+    <t>almontedesion@gmail.com</t>
+  </si>
+  <si>
     <t>kellyj2914@hotmail.com</t>
   </si>
   <si>
+    <t>natys870131@gmail.com</t>
+  </si>
+  <si>
     <t>jmcpinzon@gmail.com</t>
   </si>
   <si>
@@ -871,27 +2089,84 @@
     <t>EVOLETHARENAS@GMAIL.COM</t>
   </si>
   <si>
+    <t>ARROYAVE1215@GMAIL.COM</t>
+  </si>
+  <si>
     <t>macartin01@hotmail.es</t>
   </si>
   <si>
+    <t>vanequin09@gmail.com</t>
+  </si>
+  <si>
+    <t>luzmerygarcia13@hotmail.com</t>
+  </si>
+  <si>
+    <t>ingripao21@hotmail.com</t>
+  </si>
+  <si>
+    <t>FUEGOVITAL760@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ACOMERCIALRICARDO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MASMECANICA1@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>dayanazapataaleja@gmail.com</t>
+  </si>
+  <si>
     <t>YAQUESKA@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>EDISONBUITRAGO_1@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>christian.cardenas@correo.policia.gov.co</t>
   </si>
   <si>
     <t>ANDRESCARDONA70@GMAIL.COM</t>
   </si>
   <si>
-    <t>tapiceriajg@hotmail.com</t>
+    <t>alejandrasotoh@gmail.com</t>
+  </si>
+  <si>
+    <t>j.demo.nd@hotmail.com</t>
+  </si>
+  <si>
+    <t>marce-gil7@hotmail.com</t>
   </si>
   <si>
     <t>CTATIANAP@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>octavio@gmail.com</t>
+  </si>
+  <si>
+    <t>CLAUDIAYAVIMO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>mueblesyartes@hotmail.com</t>
+  </si>
+  <si>
     <t>veronicaosoriocarvajal@gmail.com</t>
   </si>
   <si>
+    <t>PAO1825@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>marybella2905@gmail.com</t>
+  </si>
+  <si>
+    <t>maurodezion@gmail.com</t>
+  </si>
+  <si>
+    <t>linacastano065@gmail.com</t>
+  </si>
+  <si>
+    <t>raultkd22@yahoo.com</t>
+  </si>
+  <si>
     <t>ALEJANDRA210187@HOTMAIL.COM</t>
   </si>
   <si>
@@ -901,33 +2176,120 @@
     <t>marlencj@hotmail.com</t>
   </si>
   <si>
-    <t>EZDEDI7@YAHOO.ES</t>
-  </si>
-  <si>
-    <t>ladyjohannaggl@gmail.com</t>
+    <t>jimmykta16@hotmail.com</t>
   </si>
   <si>
     <t>jhondiazrico@gmail.com</t>
   </si>
   <si>
+    <t>maryortega0308@hotmail.com</t>
+  </si>
+  <si>
+    <t>ABERMUDEZ1029@YAHOO.ES</t>
+  </si>
+  <si>
+    <t>nataliav.o@outlook.com</t>
+  </si>
+  <si>
+    <t>cristinamunozromeroo@gmail.com</t>
+  </si>
+  <si>
     <t>SARITA-ECHEVERRI@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>jafore0809@hotmail.comsan</t>
+  </si>
+  <si>
+    <t>GIANFRANCO1077@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>ANGELAMHENAO33@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>uberney1983@hotmail.com</t>
+  </si>
+  <si>
+    <t>REYDAVIDGJ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>fercorreaosorio25@gmail.com</t>
+  </si>
+  <si>
+    <t>marcegonzalez353@gmail.com</t>
+  </si>
+  <si>
     <t>Ramirezsuarezt@gmail.com</t>
   </si>
   <si>
+    <t>nancymj7481@gmail.com</t>
+  </si>
+  <si>
+    <t>CONTACTENOSPRAZER@GMAIL.COM</t>
+  </si>
+  <si>
     <t>alejandra.cespedes.r@hotmail.com</t>
   </si>
   <si>
+    <t>kellymargaritaarroyogonzalez@gmail.com</t>
+  </si>
+  <si>
+    <t>esteban.g0104@hotmail.com</t>
+  </si>
+  <si>
+    <t>hunberto-giraldo@hotmail.com</t>
+  </si>
+  <si>
     <t>GIOVA.GO8124@GMAIL.COM</t>
   </si>
   <si>
+    <t>nataliabedoya@hotmail.com</t>
+  </si>
+  <si>
+    <t>jennifermelendrez87@gmail.com</t>
+  </si>
+  <si>
+    <t>jcme2412@hotmail.com</t>
+  </si>
+  <si>
     <t>Sirlydayana@hotmail.com</t>
   </si>
   <si>
+    <t>zuleimapv4@hotmail.com</t>
+  </si>
+  <si>
+    <t>chiguita08@gmail.com</t>
+  </si>
+  <si>
+    <t>VIANEYHURTADOROSSI@YAHOO.ES</t>
+  </si>
+  <si>
+    <t>abarrera0723@gmail.com</t>
+  </si>
+  <si>
+    <t>yudyhurtado@hotmail.com</t>
+  </si>
+  <si>
+    <t>producciontallerkreativo@gmail.com</t>
+  </si>
+  <si>
     <t>seagudelo@gmail.com</t>
   </si>
   <si>
+    <t>carranza.dm21@hotmail.es</t>
+  </si>
+  <si>
+    <t>susanaestrada0121@gmail.com</t>
+  </si>
+  <si>
+    <t>lizgomezcemp@gmail.com</t>
+  </si>
+  <si>
+    <t>ledisjaramillo0@gmail.com</t>
+  </si>
+  <si>
+    <t>ISAPISAN@GMAIL.COM</t>
+  </si>
+  <si>
     <t>jclunapublicidad@gmail.com</t>
   </si>
   <si>
@@ -937,9 +2299,15 @@
     <t>REYNELM1980@GMAIL.COM</t>
   </si>
   <si>
+    <t>o.mairaj.opjh39@gmail.com</t>
+  </si>
+  <si>
     <t>saravergara775@gmail.com</t>
   </si>
   <si>
+    <t>ktmc-10@hotmail.com</t>
+  </si>
+  <si>
     <t>EZEQUIELMARTINEZ-5@HOTMAIL.COM</t>
   </si>
   <si>
@@ -949,24 +2317,90 @@
     <t>CATALINACORREA1327@GMAIL.COM</t>
   </si>
   <si>
+    <t>henryme1966@gmail.com</t>
+  </si>
+  <si>
     <t>TONERYPCS@GMAIL.COM</t>
   </si>
   <si>
+    <t>estefademiranda@gmail.com</t>
+  </si>
+  <si>
+    <t>herimonroy@hotmail.com</t>
+  </si>
+  <si>
     <t>luisfmd.28@hotmail.com</t>
   </si>
   <si>
+    <t>gladysalvarez2212@gmail.com</t>
+  </si>
+  <si>
+    <t>amethalejo@gmail.com</t>
+  </si>
+  <si>
     <t>TANIAVELCAV@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>paolaherrerausme@colombosueco.com</t>
+  </si>
+  <si>
+    <t>JENIFER1129@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>NATALIAJIMENEZCOMUNICACIONES@GMAIL.COM</t>
+  </si>
+  <si>
     <t>dianiazabal@hotmail.com</t>
   </si>
   <si>
     <t>canosandy173@gmail.com</t>
   </si>
   <si>
+    <t>GABRIEL19835@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>ARLEYORPIE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>11marcelaperez@gmail.com</t>
+  </si>
+  <si>
+    <t>kejumi72@gmail.com</t>
+  </si>
+  <si>
+    <t>alisanmedellin@gmail.com</t>
+  </si>
+  <si>
+    <t>quellysanchez@hotmail.com</t>
+  </si>
+  <si>
+    <t>robertpb2713@gmail.com</t>
+  </si>
+  <si>
+    <t>angy87cg@icloud.com</t>
+  </si>
+  <si>
     <t>khathik18@gmail.com</t>
   </si>
   <si>
+    <t>vanekiu1979@hotmail.com</t>
+  </si>
+  <si>
+    <t>vivianarestrepo@gmail.com</t>
+  </si>
+  <si>
+    <t>arlexpineda@hotmail.com</t>
+  </si>
+  <si>
+    <t>posadagabriel@hotmail.com</t>
+  </si>
+  <si>
+    <t>luiza1415@hotmail.es</t>
+  </si>
+  <si>
+    <t>carovanegas33@hotmail.com</t>
+  </si>
+  <si>
     <t>PAOLAHC0312@GMAIL.COM</t>
   </si>
   <si>
@@ -976,12 +2410,27 @@
     <t>SGAM82@gmail.com</t>
   </si>
   <si>
+    <t>jramirez1483@gmail.com</t>
+  </si>
+  <si>
+    <t>JMRESTREPODUQUE@GMAIL.COM</t>
+  </si>
+  <si>
     <t>jeison.restrepo5280@correopolicia.gov.co</t>
   </si>
   <si>
+    <t>auxcontable.arcilaloaizasas@gmail.com</t>
+  </si>
+  <si>
     <t>wendyyuranypaez2016@gmail.com</t>
   </si>
   <si>
+    <t>yelitza.marino@hotmail.com</t>
+  </si>
+  <si>
+    <t>litosrueda@gmail.com</t>
+  </si>
+  <si>
     <t>sergio02marzo@gmail.com</t>
   </si>
   <si>
@@ -991,6 +2440,12 @@
     <t>MONICA.RODASM@GMAIL.COM</t>
   </si>
   <si>
+    <t>RUIZ_CARDONA@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>JUANMARCOS.SAL@GMAIL.COM</t>
+  </si>
+  <si>
     <t>CAMASAGO@HOTMAIL.COM</t>
   </si>
   <si>
@@ -1003,6 +2458,12 @@
     <t>marthacsanchezj@gmail.com</t>
   </si>
   <si>
+    <t>FERNEY1981-@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>JUANCAMILOHERNANDEZHO@GMAIL.COM</t>
+  </si>
+  <si>
     <t>VIACEGA@GMAIL.COM</t>
   </si>
   <si>
@@ -1012,7 +2473,10 @@
     <t>lucianaserna32@gmail.com</t>
   </si>
   <si>
-    <t>JUANCAMILOHERNANDEZHO@GMAIL.COM</t>
+    <t>deisyferr@hotmail.com</t>
+  </si>
+  <si>
+    <t>lalamartinezg@hotmail.com</t>
   </si>
   <si>
     <t>sunandbeach88@hotmail.com</t>
@@ -1021,22 +2485,46 @@
     <t>manuel.troya734@casur.gov.co</t>
   </si>
   <si>
+    <t>HECHIS83@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>USUGA2310@GMAIL.COM</t>
+  </si>
+  <si>
     <t>lmolaya@hotmail.com</t>
   </si>
   <si>
     <t>sherayvp@gmail.com</t>
   </si>
   <si>
+    <t>ivrconsultor@gmail.com</t>
+  </si>
+  <si>
     <t>VASQUEZG@YAHOO.ES</t>
   </si>
   <si>
     <t>LAURAORTIZ.PSICOLOGIA@GMAIL.COM</t>
   </si>
   <si>
+    <t>juanveravila077@gmail.com</t>
+  </si>
+  <si>
+    <t>lauramarcelav@yahoo.es</t>
+  </si>
+  <si>
     <t>admisiones@colombosueco.com</t>
   </si>
   <si>
+    <t>zantana07@gmail.com</t>
+  </si>
+  <si>
+    <t>YICMARZ@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>abigailzapata133@gmail.com</t>
+  </si>
+  <si>
+    <t>limarabe1@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1431,28 +2919,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>399</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F2" t="s">
-        <v>245</v>
+        <v>582</v>
       </c>
       <c r="G2">
-        <v>3006800473</v>
+        <v>3117739445</v>
       </c>
       <c r="H2" t="s">
-        <v>281</v>
+        <v>682</v>
       </c>
       <c r="I2">
-        <v>1157380</v>
+        <v>750715</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1460,28 +2948,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>400</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>412</v>
       </c>
       <c r="E3" t="s">
-        <v>239</v>
+        <v>573</v>
       </c>
       <c r="F3" t="s">
-        <v>246</v>
+        <v>582</v>
       </c>
       <c r="G3">
-        <v>3193086213</v>
+        <v>3117739445</v>
       </c>
       <c r="H3" t="s">
-        <v>282</v>
+        <v>682</v>
       </c>
       <c r="I3">
-        <v>477251</v>
+        <v>601842</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1489,28 +2977,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>401</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>413</v>
       </c>
       <c r="E4" t="s">
-        <v>239</v>
+        <v>574</v>
       </c>
       <c r="F4" t="s">
-        <v>246</v>
+        <v>583</v>
       </c>
       <c r="G4">
-        <v>3193086213</v>
+        <v>3128870659</v>
       </c>
       <c r="H4" t="s">
-        <v>282</v>
+        <v>683</v>
       </c>
       <c r="I4">
-        <v>455648</v>
+        <v>471029</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1518,28 +3006,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
       <c r="D5" t="s">
-        <v>180</v>
+        <v>414</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F5" t="s">
-        <v>246</v>
+        <v>583</v>
       </c>
       <c r="G5">
-        <v>3103748194</v>
+        <v>3128870659</v>
       </c>
       <c r="H5" t="s">
-        <v>283</v>
+        <v>683</v>
       </c>
       <c r="I5">
-        <v>618324</v>
+        <v>334230</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1547,28 +3035,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>403</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>415</v>
       </c>
       <c r="E6" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F6" t="s">
-        <v>247</v>
+        <v>584</v>
       </c>
       <c r="G6">
-        <v>3223079151</v>
+        <v>3108365106</v>
       </c>
       <c r="H6" t="s">
-        <v>284</v>
+        <v>684</v>
       </c>
       <c r="I6">
-        <v>1514160</v>
+        <v>580026</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1576,28 +3064,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>404</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>416</v>
       </c>
       <c r="E7" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F7" t="s">
-        <v>247</v>
+        <v>585</v>
       </c>
       <c r="G7">
-        <v>3223079151</v>
+        <v>3006623430</v>
       </c>
       <c r="H7" t="s">
-        <v>284</v>
+        <v>685</v>
       </c>
       <c r="I7">
-        <v>1899990</v>
+        <v>507330</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1605,28 +3093,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>405</v>
       </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>417</v>
       </c>
       <c r="E8" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F8" t="s">
-        <v>246</v>
+        <v>586</v>
       </c>
       <c r="G8">
-        <v>3105262606</v>
+        <v>3006800473</v>
       </c>
       <c r="H8" t="s">
-        <v>285</v>
+        <v>686</v>
       </c>
       <c r="I8">
-        <v>628360</v>
+        <v>1157256</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1634,28 +3122,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>211</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>403</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>418</v>
       </c>
       <c r="E9" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F9" t="s">
-        <v>246</v>
+        <v>587</v>
       </c>
       <c r="G9">
-        <v>3105262606</v>
+        <v>3177957854</v>
       </c>
       <c r="H9" t="s">
-        <v>285</v>
+        <v>687</v>
       </c>
       <c r="I9">
-        <v>613673</v>
+        <v>109892</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1663,28 +3151,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>404</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>419</v>
       </c>
       <c r="E10" t="s">
-        <v>238</v>
+        <v>575</v>
       </c>
       <c r="F10" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G10">
-        <v>3105262606</v>
+        <v>3193086213</v>
       </c>
       <c r="H10" t="s">
-        <v>285</v>
+        <v>688</v>
       </c>
       <c r="I10">
-        <v>598074</v>
+        <v>956502</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1692,28 +3180,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="C11" t="s">
-        <v>170</v>
+        <v>406</v>
       </c>
       <c r="D11" t="s">
-        <v>183</v>
+        <v>419</v>
       </c>
       <c r="E11" t="s">
-        <v>238</v>
+        <v>575</v>
       </c>
       <c r="F11" t="s">
-        <v>248</v>
+        <v>588</v>
       </c>
       <c r="G11">
-        <v>3164020842</v>
+        <v>3193086213</v>
       </c>
       <c r="H11" t="s">
-        <v>286</v>
+        <v>688</v>
       </c>
       <c r="I11">
-        <v>582855</v>
+        <v>913296</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1721,28 +3209,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>214</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>405</v>
       </c>
       <c r="D12" t="s">
-        <v>184</v>
+        <v>420</v>
       </c>
       <c r="E12" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F12" t="s">
-        <v>249</v>
+        <v>588</v>
       </c>
       <c r="G12">
-        <v>3108914534</v>
+        <v>3103748194</v>
       </c>
       <c r="H12" t="s">
-        <v>287</v>
+        <v>689</v>
       </c>
       <c r="I12">
-        <v>588855</v>
+        <v>622324</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1750,28 +3238,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>401</v>
       </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>421</v>
       </c>
       <c r="E13" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F13" t="s">
-        <v>250</v>
+        <v>589</v>
       </c>
       <c r="G13">
-        <v>3185029620</v>
+        <v>3223079151</v>
       </c>
       <c r="H13" t="s">
-        <v>288</v>
+        <v>690</v>
       </c>
       <c r="I13">
-        <v>620217</v>
+        <v>2022880</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1779,28 +3267,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>399</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>421</v>
       </c>
       <c r="E14" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F14" t="s">
-        <v>250</v>
+        <v>589</v>
       </c>
       <c r="G14">
-        <v>3185029620</v>
+        <v>3223079151</v>
       </c>
       <c r="H14" t="s">
-        <v>288</v>
+        <v>690</v>
       </c>
       <c r="I14">
-        <v>2138976</v>
+        <v>2537320</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1808,28 +3296,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="C15" t="s">
-        <v>167</v>
+        <v>407</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>422</v>
       </c>
       <c r="E15" t="s">
-        <v>241</v>
+        <v>574</v>
       </c>
       <c r="F15" t="s">
-        <v>246</v>
+        <v>590</v>
       </c>
       <c r="G15">
-        <v>3206373767</v>
+        <v>3005041266</v>
       </c>
       <c r="H15" t="s">
-        <v>289</v>
+        <v>691</v>
       </c>
       <c r="I15">
-        <v>484360</v>
+        <v>590972</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1837,28 +3325,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>218</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>403</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
+        <v>423</v>
       </c>
       <c r="E16" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F16" t="s">
-        <v>251</v>
+        <v>588</v>
       </c>
       <c r="G16">
-        <v>3212776005</v>
+        <v>3105262606</v>
       </c>
       <c r="H16" t="s">
-        <v>290</v>
+        <v>692</v>
       </c>
       <c r="I16">
-        <v>475350</v>
+        <v>1258720</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1866,28 +3354,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>165</v>
+        <v>408</v>
       </c>
       <c r="D17" t="s">
-        <v>188</v>
+        <v>423</v>
       </c>
       <c r="E17" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F17" t="s">
-        <v>252</v>
+        <v>588</v>
       </c>
       <c r="G17">
-        <v>3104067600</v>
+        <v>3105262606</v>
       </c>
       <c r="H17" t="s">
-        <v>291</v>
+        <v>692</v>
       </c>
       <c r="I17">
-        <v>1084856</v>
+        <v>1229346</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1895,28 +3383,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>409</v>
       </c>
       <c r="D18" t="s">
-        <v>189</v>
+        <v>423</v>
       </c>
       <c r="E18" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F18" t="s">
-        <v>253</v>
+        <v>588</v>
       </c>
       <c r="G18">
-        <v>3012457263</v>
+        <v>3105262606</v>
       </c>
       <c r="H18" t="s">
-        <v>292</v>
+        <v>692</v>
       </c>
       <c r="I18">
-        <v>1514160</v>
+        <v>1198148</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1924,28 +3412,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="C19" t="s">
-        <v>167</v>
+        <v>403</v>
       </c>
       <c r="D19" t="s">
-        <v>189</v>
+        <v>424</v>
       </c>
       <c r="E19" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F19" t="s">
-        <v>253</v>
+        <v>591</v>
       </c>
       <c r="G19">
-        <v>3012457266</v>
+        <v>3008146051</v>
       </c>
       <c r="H19" t="s">
-        <v>293</v>
+        <v>693</v>
       </c>
       <c r="I19">
-        <v>455648</v>
+        <v>557012</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1953,28 +3441,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>405</v>
       </c>
       <c r="D20" t="s">
-        <v>190</v>
+        <v>424</v>
       </c>
       <c r="E20" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F20" t="s">
-        <v>254</v>
+        <v>591</v>
       </c>
       <c r="G20">
-        <v>3233179080</v>
+        <v>3008146051</v>
       </c>
       <c r="H20" t="s">
-        <v>294</v>
+        <v>693</v>
       </c>
       <c r="I20">
-        <v>631561</v>
+        <v>577876</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1982,28 +3470,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>223</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>408</v>
       </c>
       <c r="D21" t="s">
-        <v>191</v>
+        <v>425</v>
       </c>
       <c r="E21" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F21" t="s">
-        <v>255</v>
+        <v>588</v>
       </c>
       <c r="G21">
-        <v>3156803375</v>
+        <v>3106836174</v>
       </c>
       <c r="H21" t="s">
-        <v>295</v>
+        <v>694</v>
       </c>
       <c r="I21">
-        <v>567488</v>
+        <v>579240</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2011,28 +3499,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
       <c r="C22" t="s">
-        <v>174</v>
+        <v>407</v>
       </c>
       <c r="D22" t="s">
-        <v>192</v>
+        <v>426</v>
       </c>
       <c r="E22" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F22" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G22">
-        <v>3007291017</v>
+        <v>3207446171</v>
       </c>
       <c r="H22" t="s">
-        <v>296</v>
+        <v>695</v>
       </c>
       <c r="I22">
-        <v>565363</v>
+        <v>550754</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2040,28 +3528,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>225</v>
       </c>
       <c r="C23" t="s">
-        <v>169</v>
+        <v>400</v>
       </c>
       <c r="D23" t="s">
-        <v>192</v>
+        <v>427</v>
       </c>
       <c r="E23" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F23" t="s">
-        <v>246</v>
+        <v>592</v>
       </c>
       <c r="G23">
-        <v>3007291017</v>
+        <v>3226255509</v>
       </c>
       <c r="H23" t="s">
-        <v>296</v>
+        <v>696</v>
       </c>
       <c r="I23">
-        <v>631330</v>
+        <v>538030</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2069,28 +3557,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>226</v>
       </c>
       <c r="C24" t="s">
-        <v>166</v>
+        <v>407</v>
       </c>
       <c r="D24" t="s">
-        <v>193</v>
+        <v>428</v>
       </c>
       <c r="E24" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F24" t="s">
-        <v>256</v>
+        <v>588</v>
       </c>
       <c r="G24">
-        <v>3045957277</v>
+        <v>3232339870</v>
       </c>
       <c r="H24" t="s">
-        <v>297</v>
+        <v>697</v>
       </c>
       <c r="I24">
-        <v>477251</v>
+        <v>585486</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2098,28 +3586,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="C25" t="s">
-        <v>166</v>
+        <v>403</v>
       </c>
       <c r="D25" t="s">
-        <v>194</v>
+        <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F25" t="s">
-        <v>257</v>
+        <v>593</v>
       </c>
       <c r="G25">
-        <v>3143828183</v>
+        <v>3005565956</v>
       </c>
       <c r="H25" t="s">
-        <v>298</v>
+        <v>698</v>
       </c>
       <c r="I25">
-        <v>567488</v>
+        <v>628360</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2127,28 +3615,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
+        <v>401</v>
       </c>
       <c r="D26" t="s">
-        <v>195</v>
+        <v>430</v>
       </c>
       <c r="E26" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F26" t="s">
-        <v>258</v>
+        <v>594</v>
       </c>
       <c r="G26">
-        <v>3146320382</v>
+        <v>3013747979</v>
       </c>
       <c r="H26" t="s">
-        <v>299</v>
+        <v>699</v>
       </c>
       <c r="I26">
-        <v>1360262</v>
+        <v>566102</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2156,28 +3644,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s">
-        <v>175</v>
+        <v>403</v>
       </c>
       <c r="D27" t="s">
-        <v>196</v>
+        <v>431</v>
       </c>
       <c r="E27" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F27" t="s">
-        <v>258</v>
+        <v>595</v>
       </c>
       <c r="G27">
-        <v>3146320382</v>
+        <v>3164020842</v>
       </c>
       <c r="H27" t="s">
-        <v>299</v>
+        <v>700</v>
       </c>
       <c r="I27">
-        <v>2194495</v>
+        <v>588026</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2185,28 +3673,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>230</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>403</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>432</v>
       </c>
       <c r="E28" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F28" t="s">
-        <v>259</v>
+        <v>596</v>
       </c>
       <c r="G28">
-        <v>3108384796</v>
+        <v>3187949466</v>
       </c>
       <c r="H28" t="s">
-        <v>300</v>
+        <v>701</v>
       </c>
       <c r="I28">
-        <v>506046</v>
+        <v>522793</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2214,28 +3702,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>231</v>
       </c>
       <c r="C29" t="s">
-        <v>169</v>
+        <v>403</v>
       </c>
       <c r="D29" t="s">
-        <v>197</v>
+        <v>433</v>
       </c>
       <c r="E29" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F29" t="s">
-        <v>259</v>
+        <v>597</v>
       </c>
       <c r="G29">
-        <v>3108384796</v>
+        <v>3108914534</v>
       </c>
       <c r="H29" t="s">
-        <v>300</v>
+        <v>702</v>
       </c>
       <c r="I29">
-        <v>631330</v>
+        <v>588026</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2243,28 +3731,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>232</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>407</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>434</v>
       </c>
       <c r="E30" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F30" t="s">
-        <v>246</v>
+        <v>598</v>
       </c>
       <c r="G30">
-        <v>3004353149</v>
+        <v>3185029620</v>
       </c>
       <c r="H30" t="s">
-        <v>301</v>
+        <v>703</v>
       </c>
       <c r="I30">
-        <v>284360</v>
+        <v>1242434</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2272,28 +3760,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>399</v>
       </c>
       <c r="D31" t="s">
-        <v>199</v>
+        <v>434</v>
       </c>
       <c r="E31" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F31" t="s">
-        <v>260</v>
+        <v>598</v>
       </c>
       <c r="G31">
-        <v>3013531871</v>
+        <v>3185029620</v>
       </c>
       <c r="H31" t="s">
-        <v>302</v>
+        <v>703</v>
       </c>
       <c r="I31">
-        <v>484080</v>
+        <v>2855968</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2301,28 +3789,16 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>403</v>
       </c>
       <c r="D32" t="s">
-        <v>199</v>
-      </c>
-      <c r="E32" t="s">
-        <v>238</v>
-      </c>
-      <c r="F32" t="s">
-        <v>260</v>
-      </c>
-      <c r="G32">
-        <v>3013531871</v>
-      </c>
-      <c r="H32" t="s">
-        <v>302</v>
+        <v>435</v>
       </c>
       <c r="I32">
-        <v>643482</v>
+        <v>287982</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2330,28 +3806,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>235</v>
       </c>
       <c r="C33" t="s">
-        <v>166</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
+        <v>436</v>
       </c>
       <c r="E33" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F33" t="s">
-        <v>261</v>
+        <v>599</v>
       </c>
       <c r="G33">
-        <v>3102013484</v>
+        <v>3117996256</v>
       </c>
       <c r="H33" t="s">
-        <v>303</v>
+        <v>704</v>
       </c>
       <c r="I33">
-        <v>473255</v>
+        <v>605299</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2359,28 +3835,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>236</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>409</v>
       </c>
       <c r="D34" t="s">
-        <v>201</v>
+        <v>437</v>
       </c>
       <c r="E34" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F34" t="s">
-        <v>262</v>
+        <v>600</v>
       </c>
       <c r="G34">
-        <v>3113200460</v>
+        <v>3136884860</v>
       </c>
       <c r="H34" t="s">
-        <v>304</v>
+        <v>705</v>
       </c>
       <c r="I34">
-        <v>2164120</v>
+        <v>503612</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2388,28 +3864,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>237</v>
       </c>
       <c r="C35" t="s">
-        <v>176</v>
+        <v>400</v>
       </c>
       <c r="D35" t="s">
-        <v>202</v>
+        <v>438</v>
       </c>
       <c r="E35" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F35" t="s">
-        <v>263</v>
+        <v>601</v>
       </c>
       <c r="G35">
-        <v>3136146481</v>
+        <v>4884681</v>
       </c>
       <c r="H35" t="s">
-        <v>305</v>
+        <v>706</v>
       </c>
       <c r="I35">
-        <v>1715680</v>
+        <v>506123</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2417,28 +3893,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>238</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>404</v>
       </c>
       <c r="D36" t="s">
-        <v>203</v>
+        <v>439</v>
       </c>
       <c r="E36" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F36" t="s">
-        <v>264</v>
+        <v>602</v>
       </c>
       <c r="G36">
-        <v>3017206508</v>
+        <v>3212776005</v>
       </c>
       <c r="H36" t="s">
-        <v>306</v>
+        <v>707</v>
       </c>
       <c r="I36">
-        <v>476502</v>
+        <v>382680</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2446,28 +3922,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>239</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>403</v>
       </c>
       <c r="D37" t="s">
-        <v>204</v>
+        <v>440</v>
       </c>
       <c r="E37" t="s">
-        <v>238</v>
+        <v>576</v>
       </c>
       <c r="F37" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G37">
-        <v>3022977529</v>
+        <v>3205337291</v>
       </c>
       <c r="H37" t="s">
-        <v>307</v>
+        <v>708</v>
       </c>
       <c r="I37">
-        <v>521451</v>
+        <v>593171</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2475,28 +3951,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>240</v>
       </c>
       <c r="C38" t="s">
-        <v>172</v>
+        <v>406</v>
       </c>
       <c r="D38" t="s">
-        <v>205</v>
+        <v>441</v>
       </c>
       <c r="E38" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F38" t="s">
-        <v>246</v>
+        <v>603</v>
       </c>
       <c r="G38">
-        <v>3013807813</v>
+        <v>3148494120</v>
       </c>
       <c r="H38" t="s">
-        <v>308</v>
+        <v>709</v>
       </c>
       <c r="I38">
-        <v>1198148</v>
+        <v>484360</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2504,28 +3980,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>407</v>
       </c>
       <c r="D39" t="s">
-        <v>206</v>
+        <v>442</v>
       </c>
       <c r="E39" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F39" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G39">
-        <v>3186656220</v>
+        <v>3105441118</v>
       </c>
       <c r="H39" t="s">
-        <v>309</v>
+        <v>710</v>
       </c>
       <c r="I39">
-        <v>1762458</v>
+        <v>620217</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2533,28 +4009,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>405</v>
       </c>
       <c r="D40" t="s">
-        <v>207</v>
+        <v>443</v>
       </c>
       <c r="E40" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F40" t="s">
-        <v>265</v>
+        <v>604</v>
       </c>
       <c r="G40">
-        <v>3003934941</v>
+        <v>3104067600</v>
       </c>
       <c r="H40" t="s">
-        <v>310</v>
+        <v>711</v>
       </c>
       <c r="I40">
-        <v>482800</v>
+        <v>1080284</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2562,28 +4038,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>243</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>405</v>
       </c>
       <c r="D41" t="s">
-        <v>208</v>
+        <v>444</v>
       </c>
       <c r="E41" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F41" t="s">
-        <v>246</v>
+        <v>605</v>
       </c>
       <c r="G41">
-        <v>3015656941</v>
+        <v>3003767391</v>
       </c>
       <c r="H41" t="s">
-        <v>311</v>
+        <v>712</v>
       </c>
       <c r="I41">
-        <v>1096770</v>
+        <v>614324</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2591,28 +4067,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="C42" t="s">
-        <v>174</v>
+        <v>407</v>
       </c>
       <c r="D42" t="s">
-        <v>209</v>
+        <v>445</v>
       </c>
       <c r="E42" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F42" t="s">
-        <v>246</v>
+        <v>606</v>
       </c>
       <c r="G42">
-        <v>3017266368</v>
+        <v>3016959292</v>
       </c>
       <c r="H42" t="s">
-        <v>312</v>
+        <v>713</v>
       </c>
       <c r="I42">
-        <v>707348</v>
+        <v>620217</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2620,28 +4096,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>245</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>404</v>
       </c>
       <c r="D43" t="s">
-        <v>209</v>
+        <v>446</v>
       </c>
       <c r="E43" t="s">
-        <v>240</v>
-      </c>
-      <c r="F43" t="s">
-        <v>246</v>
+        <v>573</v>
+      </c>
+      <c r="F43">
+        <v>5055211</v>
       </c>
       <c r="G43">
-        <v>3017266368</v>
+        <v>3226169377</v>
       </c>
       <c r="H43" t="s">
-        <v>312</v>
+        <v>714</v>
       </c>
       <c r="I43">
-        <v>579310</v>
+        <v>506620</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2649,28 +4125,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>246</v>
       </c>
       <c r="C44" t="s">
-        <v>169</v>
+        <v>401</v>
       </c>
       <c r="D44" t="s">
-        <v>209</v>
+        <v>447</v>
       </c>
       <c r="E44" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F44" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G44">
-        <v>3017266368</v>
+        <v>3046838460</v>
       </c>
       <c r="H44" t="s">
-        <v>312</v>
+        <v>715</v>
       </c>
       <c r="I44">
-        <v>671161</v>
+        <v>502720</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2678,28 +4154,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="C45" t="s">
-        <v>166</v>
+        <v>401</v>
       </c>
       <c r="D45" t="s">
-        <v>210</v>
+        <v>448</v>
       </c>
       <c r="E45" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F45" t="s">
-        <v>266</v>
+        <v>607</v>
       </c>
       <c r="G45">
-        <v>3015954319</v>
+        <v>3158213376</v>
       </c>
       <c r="H45" t="s">
-        <v>313</v>
+        <v>716</v>
       </c>
       <c r="I45">
-        <v>2556650</v>
+        <v>502720</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2707,28 +4183,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>248</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>401</v>
       </c>
       <c r="D46" t="s">
-        <v>211</v>
+        <v>449</v>
       </c>
       <c r="E46" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F46" t="s">
-        <v>267</v>
+        <v>608</v>
       </c>
       <c r="G46">
-        <v>3124291951</v>
+        <v>3012457263</v>
       </c>
       <c r="H46" t="s">
-        <v>314</v>
+        <v>717</v>
       </c>
       <c r="I46">
-        <v>814324</v>
+        <v>2022880</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2736,28 +4212,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>132</v>
+        <v>249</v>
       </c>
       <c r="C47" t="s">
-        <v>166</v>
+        <v>406</v>
       </c>
       <c r="D47" t="s">
-        <v>211</v>
+        <v>449</v>
       </c>
       <c r="E47" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F47" t="s">
-        <v>267</v>
+        <v>608</v>
       </c>
       <c r="G47">
-        <v>3124291951</v>
+        <v>3012457266</v>
       </c>
       <c r="H47" t="s">
-        <v>314</v>
+        <v>718</v>
       </c>
       <c r="I47">
-        <v>199330</v>
+        <v>913296</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2765,28 +4241,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>250</v>
       </c>
       <c r="C48" t="s">
-        <v>177</v>
+        <v>409</v>
       </c>
       <c r="D48" t="s">
-        <v>212</v>
+        <v>450</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F48" t="s">
-        <v>246</v>
+        <v>609</v>
       </c>
       <c r="G48">
-        <v>3117316210</v>
+        <v>3233179080</v>
       </c>
       <c r="H48" t="s">
-        <v>315</v>
+        <v>719</v>
       </c>
       <c r="I48">
-        <v>1044902</v>
+        <v>1265122</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2794,28 +4270,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>251</v>
       </c>
       <c r="C49" t="s">
-        <v>165</v>
+        <v>410</v>
       </c>
       <c r="D49" t="s">
-        <v>213</v>
+        <v>451</v>
       </c>
       <c r="E49" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F49" t="s">
-        <v>268</v>
+        <v>588</v>
       </c>
       <c r="G49">
-        <v>3166226027</v>
+        <v>3113521455</v>
       </c>
       <c r="H49" t="s">
-        <v>316</v>
+        <v>720</v>
       </c>
       <c r="I49">
-        <v>608296</v>
+        <v>620081</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2823,28 +4299,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>252</v>
       </c>
       <c r="C50" t="s">
-        <v>168</v>
+        <v>404</v>
       </c>
       <c r="D50" t="s">
-        <v>214</v>
+        <v>452</v>
       </c>
       <c r="E50" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F50" t="s">
-        <v>246</v>
+        <v>610</v>
       </c>
       <c r="G50">
-        <v>3226367303</v>
+        <v>3045957277</v>
       </c>
       <c r="H50" t="s">
-        <v>317</v>
+        <v>721</v>
       </c>
       <c r="I50">
-        <v>2428600</v>
+        <v>956502</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2852,28 +4328,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="C51" t="s">
-        <v>166</v>
+        <v>408</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
+        <v>453</v>
       </c>
       <c r="E51" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F51" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G51">
-        <v>3112833518</v>
+        <v>3143012599</v>
       </c>
       <c r="H51" t="s">
-        <v>318</v>
+        <v>722</v>
       </c>
       <c r="I51">
-        <v>455985</v>
+        <v>544946</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2881,28 +4357,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
+        <v>254</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>401</v>
       </c>
       <c r="D52" t="s">
-        <v>215</v>
+        <v>454</v>
       </c>
       <c r="E52" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F52" t="s">
-        <v>246</v>
+        <v>611</v>
       </c>
       <c r="G52">
-        <v>3103161676</v>
+        <v>3005159999</v>
       </c>
       <c r="H52" t="s">
-        <v>319</v>
+        <v>723</v>
       </c>
       <c r="I52">
-        <v>505635</v>
+        <v>534411</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2910,28 +4386,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>255</v>
       </c>
       <c r="C53" t="s">
-        <v>175</v>
+        <v>399</v>
       </c>
       <c r="D53" t="s">
-        <v>216</v>
+        <v>455</v>
       </c>
       <c r="E53" t="s">
-        <v>242</v>
+        <v>573</v>
       </c>
       <c r="F53" t="s">
-        <v>269</v>
+        <v>588</v>
       </c>
       <c r="G53">
-        <v>3112860092</v>
+        <v>3212412336</v>
       </c>
       <c r="H53" t="s">
-        <v>320</v>
+        <v>724</v>
       </c>
       <c r="I53">
-        <v>1233196</v>
+        <v>184680</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2939,28 +4415,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>256</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>401</v>
       </c>
       <c r="D54" t="s">
-        <v>216</v>
+        <v>456</v>
       </c>
       <c r="E54" t="s">
-        <v>243</v>
+        <v>573</v>
       </c>
       <c r="F54" t="s">
-        <v>269</v>
+        <v>588</v>
       </c>
       <c r="G54">
-        <v>3112860092</v>
+        <v>3207590149</v>
       </c>
       <c r="H54" t="s">
-        <v>320</v>
+        <v>725</v>
       </c>
       <c r="I54">
-        <v>1022880</v>
+        <v>534411</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2968,28 +4444,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>140</v>
+        <v>257</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>404</v>
       </c>
       <c r="D55" t="s">
-        <v>217</v>
+        <v>457</v>
       </c>
       <c r="E55" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F55" t="s">
-        <v>246</v>
+        <v>612</v>
       </c>
       <c r="G55">
-        <v>3108699380</v>
+        <v>3143828183</v>
       </c>
       <c r="H55" t="s">
-        <v>321</v>
+        <v>726</v>
       </c>
       <c r="I55">
-        <v>628360</v>
+        <v>1136976</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2997,28 +4473,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>141</v>
+        <v>258</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>400</v>
       </c>
       <c r="D56" t="s">
-        <v>217</v>
+        <v>458</v>
       </c>
       <c r="E56" t="s">
-        <v>238</v>
+        <v>577</v>
       </c>
       <c r="F56" t="s">
-        <v>246</v>
+        <v>613</v>
       </c>
       <c r="G56">
-        <v>3108699380</v>
+        <v>3015686911</v>
       </c>
       <c r="H56" t="s">
-        <v>321</v>
+        <v>727</v>
       </c>
       <c r="I56">
-        <v>587205</v>
+        <v>538030</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3026,28 +4502,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>166</v>
+        <v>409</v>
       </c>
       <c r="D57" t="s">
-        <v>218</v>
+        <v>458</v>
       </c>
       <c r="E57" t="s">
-        <v>242</v>
+        <v>577</v>
       </c>
       <c r="F57" t="s">
-        <v>246</v>
+        <v>613</v>
       </c>
       <c r="G57">
-        <v>3194309799</v>
+        <v>3015686911</v>
       </c>
       <c r="H57" t="s">
-        <v>322</v>
+        <v>727</v>
       </c>
       <c r="I57">
-        <v>476255</v>
+        <v>564344</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3055,28 +4531,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>143</v>
+        <v>260</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>409</v>
       </c>
       <c r="D58" t="s">
-        <v>219</v>
+        <v>459</v>
       </c>
       <c r="E58" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F58" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G58">
-        <v>3106368274</v>
+        <v>3116347838</v>
       </c>
       <c r="H58" t="s">
-        <v>323</v>
+        <v>728</v>
       </c>
       <c r="I58">
-        <v>481800</v>
+        <v>564544</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3084,28 +4560,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>407</v>
       </c>
       <c r="D59" t="s">
-        <v>220</v>
+        <v>460</v>
       </c>
       <c r="E59" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F59" t="s">
-        <v>270</v>
+        <v>614</v>
       </c>
       <c r="G59">
-        <v>3008674834</v>
+        <v>3207147950</v>
       </c>
       <c r="H59" t="s">
-        <v>324</v>
+        <v>729</v>
       </c>
       <c r="I59">
-        <v>484300</v>
+        <v>585486</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3113,28 +4589,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>262</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>405</v>
       </c>
       <c r="D60" t="s">
-        <v>221</v>
+        <v>461</v>
       </c>
       <c r="E60" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F60" t="s">
-        <v>271</v>
+        <v>588</v>
       </c>
       <c r="G60">
-        <v>3104534612</v>
+        <v>3226038092</v>
       </c>
       <c r="H60" t="s">
-        <v>325</v>
+        <v>730</v>
       </c>
       <c r="I60">
-        <v>484360</v>
+        <v>577728</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3142,28 +4618,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>263</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>407</v>
       </c>
       <c r="D61" t="s">
-        <v>222</v>
+        <v>462</v>
       </c>
       <c r="E61" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F61" t="s">
-        <v>272</v>
+        <v>615</v>
       </c>
       <c r="G61">
-        <v>3022424243</v>
+        <v>3103911258</v>
       </c>
       <c r="H61" t="s">
-        <v>326</v>
+        <v>731</v>
       </c>
       <c r="I61">
-        <v>1155620</v>
+        <v>550754</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3171,28 +4647,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>264</v>
       </c>
       <c r="C62" t="s">
-        <v>176</v>
+        <v>401</v>
       </c>
       <c r="D62" t="s">
-        <v>223</v>
+        <v>463</v>
       </c>
       <c r="E62" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F62" t="s">
-        <v>273</v>
+        <v>616</v>
       </c>
       <c r="G62">
-        <v>3127382747</v>
+        <v>3013564721</v>
       </c>
       <c r="H62" t="s">
-        <v>327</v>
+        <v>732</v>
       </c>
       <c r="I62">
-        <v>1014246</v>
+        <v>502720</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3200,28 +4676,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>265</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>400</v>
       </c>
       <c r="D63" t="s">
-        <v>223</v>
+        <v>464</v>
       </c>
       <c r="E63" t="s">
-        <v>240</v>
+        <v>578</v>
       </c>
       <c r="F63" t="s">
-        <v>273</v>
+        <v>588</v>
       </c>
       <c r="G63">
-        <v>3127382747</v>
+        <v>3219014852</v>
       </c>
       <c r="H63" t="s">
-        <v>327</v>
+        <v>733</v>
       </c>
       <c r="I63">
-        <v>455648</v>
+        <v>538030</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3229,28 +4705,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>266</v>
       </c>
       <c r="C64" t="s">
-        <v>173</v>
+        <v>407</v>
       </c>
       <c r="D64" t="s">
-        <v>223</v>
+        <v>465</v>
       </c>
       <c r="E64" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F64" t="s">
-        <v>273</v>
+        <v>617</v>
       </c>
       <c r="G64">
-        <v>3127382747</v>
+        <v>3146320382</v>
       </c>
       <c r="H64" t="s">
-        <v>327</v>
+        <v>734</v>
       </c>
       <c r="I64">
-        <v>1103508</v>
+        <v>1917016</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3258,28 +4734,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>175</v>
+        <v>402</v>
       </c>
       <c r="D65" t="s">
-        <v>224</v>
+        <v>466</v>
       </c>
       <c r="E65" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F65" t="s">
-        <v>246</v>
+        <v>617</v>
       </c>
       <c r="G65">
-        <v>3168660548</v>
+        <v>3146320382</v>
       </c>
       <c r="H65" t="s">
-        <v>328</v>
+        <v>734</v>
       </c>
       <c r="I65">
-        <v>2044495</v>
+        <v>2807794</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3287,28 +4763,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>268</v>
       </c>
       <c r="C66" t="s">
-        <v>169</v>
+        <v>407</v>
       </c>
       <c r="D66" t="s">
-        <v>225</v>
+        <v>467</v>
       </c>
       <c r="E66" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F66" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G66">
-        <v>3145672233</v>
+        <v>3226071559</v>
       </c>
       <c r="H66" t="s">
-        <v>329</v>
+        <v>735</v>
       </c>
       <c r="I66">
-        <v>3574960</v>
+        <v>585486</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3316,28 +4792,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="C67" t="s">
-        <v>168</v>
+        <v>400</v>
       </c>
       <c r="D67" t="s">
-        <v>226</v>
+        <v>468</v>
       </c>
       <c r="E67" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>618</v>
       </c>
       <c r="G67">
-        <v>3145672233</v>
+        <v>3154274962</v>
       </c>
       <c r="H67" t="s">
-        <v>329</v>
+        <v>736</v>
       </c>
       <c r="I67">
-        <v>1704306</v>
+        <v>506123</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3345,28 +4821,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>153</v>
+        <v>270</v>
       </c>
       <c r="C68" t="s">
-        <v>166</v>
+        <v>400</v>
       </c>
       <c r="D68" t="s">
-        <v>227</v>
+        <v>469</v>
       </c>
       <c r="E68" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F68" t="s">
-        <v>274</v>
+        <v>619</v>
       </c>
       <c r="G68">
-        <v>3148214908</v>
+        <v>3108384796</v>
       </c>
       <c r="H68" t="s">
-        <v>330</v>
+        <v>737</v>
       </c>
       <c r="I68">
-        <v>1016660</v>
+        <v>414169</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3374,28 +4850,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>154</v>
+        <v>271</v>
       </c>
       <c r="C69" t="s">
-        <v>166</v>
+        <v>399</v>
       </c>
       <c r="D69" t="s">
-        <v>228</v>
+        <v>469</v>
       </c>
       <c r="E69" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F69" t="s">
-        <v>275</v>
+        <v>619</v>
       </c>
       <c r="G69">
-        <v>3207611691</v>
+        <v>3108384796</v>
       </c>
       <c r="H69" t="s">
-        <v>331</v>
+        <v>737</v>
       </c>
       <c r="I69">
-        <v>477251</v>
+        <v>531330</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3403,28 +4879,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>272</v>
       </c>
       <c r="C70" t="s">
-        <v>168</v>
+        <v>403</v>
       </c>
       <c r="D70" t="s">
-        <v>229</v>
+        <v>470</v>
       </c>
       <c r="E70" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F70" t="s">
-        <v>276</v>
+        <v>620</v>
       </c>
       <c r="G70">
-        <v>3003438170</v>
+        <v>3145242166</v>
       </c>
       <c r="H70" t="s">
-        <v>332</v>
+        <v>738</v>
       </c>
       <c r="I70">
-        <v>1462880</v>
+        <v>593171</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3432,28 +4908,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>156</v>
+        <v>273</v>
       </c>
       <c r="C71" t="s">
-        <v>170</v>
+        <v>403</v>
       </c>
       <c r="D71" t="s">
-        <v>230</v>
+        <v>471</v>
       </c>
       <c r="E71" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F71" t="s">
-        <v>277</v>
+        <v>621</v>
       </c>
       <c r="G71">
-        <v>3205617348</v>
+        <v>3147398657</v>
       </c>
       <c r="H71" t="s">
-        <v>333</v>
+        <v>739</v>
       </c>
       <c r="I71">
-        <v>587684</v>
+        <v>628360</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3461,28 +4937,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>157</v>
+        <v>274</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
+        <v>405</v>
       </c>
       <c r="D72" t="s">
-        <v>231</v>
+        <v>472</v>
       </c>
       <c r="E72" t="s">
-        <v>240</v>
+        <v>574</v>
       </c>
       <c r="F72" t="s">
-        <v>246</v>
+        <v>622</v>
       </c>
       <c r="G72">
-        <v>3206798318</v>
+        <v>3135494642</v>
       </c>
       <c r="H72" t="s">
-        <v>334</v>
+        <v>740</v>
       </c>
       <c r="I72">
-        <v>2331074</v>
+        <v>614324</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3490,28 +4966,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>275</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>406</v>
       </c>
       <c r="D73" t="s">
-        <v>232</v>
+        <v>473</v>
       </c>
       <c r="E73" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F73" t="s">
-        <v>246</v>
+        <v>588</v>
       </c>
       <c r="G73">
-        <v>3004106594</v>
+        <v>3004353149</v>
       </c>
       <c r="H73" t="s">
-        <v>335</v>
+        <v>741</v>
       </c>
       <c r="I73">
-        <v>601842</v>
+        <v>770720</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3519,28 +4995,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>276</v>
       </c>
       <c r="C74" t="s">
-        <v>170</v>
+        <v>401</v>
       </c>
       <c r="D74" t="s">
-        <v>232</v>
+        <v>474</v>
       </c>
       <c r="E74" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F74" t="s">
-        <v>246</v>
+        <v>623</v>
       </c>
       <c r="G74">
-        <v>3004106594</v>
+        <v>3046270488</v>
       </c>
       <c r="H74" t="s">
-        <v>335</v>
+        <v>742</v>
       </c>
       <c r="I74">
-        <v>1996644</v>
+        <v>396871</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3548,28 +5024,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>160</v>
+        <v>277</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>404</v>
       </c>
       <c r="D75" t="s">
-        <v>233</v>
+        <v>474</v>
       </c>
       <c r="E75" t="s">
-        <v>238</v>
+        <v>573</v>
       </c>
       <c r="F75" t="s">
-        <v>246</v>
+        <v>623</v>
       </c>
       <c r="G75">
-        <v>3128021315</v>
+        <v>3046270488</v>
       </c>
       <c r="H75" t="s">
-        <v>336</v>
+        <v>742</v>
       </c>
       <c r="I75">
-        <v>522793</v>
+        <v>376786</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3577,28 +5053,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>161</v>
+        <v>278</v>
       </c>
       <c r="C76" t="s">
-        <v>173</v>
+        <v>403</v>
       </c>
       <c r="D76" t="s">
-        <v>234</v>
+        <v>475</v>
       </c>
       <c r="E76" t="s">
-        <v>240</v>
+        <v>573</v>
       </c>
       <c r="F76" t="s">
-        <v>278</v>
+        <v>624</v>
       </c>
       <c r="G76">
-        <v>3052245305</v>
+        <v>3005281616</v>
       </c>
       <c r="H76" t="s">
-        <v>337</v>
+        <v>743</v>
       </c>
       <c r="I76">
-        <v>1172972</v>
+        <v>557982</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3606,28 +5082,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>162</v>
+        <v>279</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>410</v>
       </c>
       <c r="D77" t="s">
-        <v>235</v>
+        <v>476</v>
       </c>
       <c r="E77" t="s">
-        <v>238</v>
+        <v>574</v>
       </c>
       <c r="F77" t="s">
-        <v>279</v>
+        <v>625</v>
       </c>
       <c r="G77">
-        <v>3002799011</v>
+        <v>3206895990</v>
       </c>
       <c r="H77" t="s">
-        <v>338</v>
+        <v>744</v>
       </c>
       <c r="I77">
-        <v>2600115</v>
+        <v>519402</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3635,28 +5111,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>163</v>
+        <v>280</v>
       </c>
       <c r="C78" t="s">
-        <v>175</v>
+        <v>403</v>
       </c>
       <c r="D78" t="s">
-        <v>236</v>
+        <v>476</v>
       </c>
       <c r="E78" t="s">
-        <v>244</v>
+        <v>574</v>
       </c>
       <c r="F78" t="s">
-        <v>280</v>
+        <v>625</v>
       </c>
       <c r="G78">
-        <v>3104440838</v>
+        <v>3206895990</v>
       </c>
       <c r="H78" t="s">
-        <v>339</v>
+        <v>744</v>
       </c>
       <c r="I78">
-        <v>544969</v>
+        <v>555964</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3664,28 +5140,3412 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
+        <v>281</v>
+      </c>
+      <c r="C79" t="s">
+        <v>406</v>
+      </c>
+      <c r="D79" t="s">
+        <v>477</v>
+      </c>
+      <c r="E79" t="s">
+        <v>573</v>
+      </c>
+      <c r="F79" t="s">
+        <v>626</v>
+      </c>
+      <c r="G79">
+        <v>3013531871</v>
+      </c>
+      <c r="H79" t="s">
+        <v>745</v>
+      </c>
+      <c r="I79">
+        <v>970440</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" t="s">
+        <v>282</v>
+      </c>
+      <c r="C80" t="s">
+        <v>402</v>
+      </c>
+      <c r="D80" t="s">
+        <v>477</v>
+      </c>
+      <c r="E80" t="s">
+        <v>573</v>
+      </c>
+      <c r="F80" t="s">
+        <v>626</v>
+      </c>
+      <c r="G80">
+        <v>3013531871</v>
+      </c>
+      <c r="H80" t="s">
+        <v>745</v>
+      </c>
+      <c r="I80">
+        <v>1288964</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" t="s">
+        <v>283</v>
+      </c>
+      <c r="C81" t="s">
+        <v>402</v>
+      </c>
+      <c r="D81" t="s">
+        <v>478</v>
+      </c>
+      <c r="E81" t="s">
+        <v>573</v>
+      </c>
+      <c r="F81" t="s">
+        <v>588</v>
+      </c>
+      <c r="G81">
+        <v>3008092108</v>
+      </c>
+      <c r="H81" t="s">
+        <v>746</v>
+      </c>
+      <c r="I81">
+        <v>604794</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" t="s">
+        <v>284</v>
+      </c>
+      <c r="C82" t="s">
+        <v>403</v>
+      </c>
+      <c r="D82" t="s">
+        <v>479</v>
+      </c>
+      <c r="E82" t="s">
+        <v>573</v>
+      </c>
+      <c r="F82" t="s">
+        <v>588</v>
+      </c>
+      <c r="G82">
+        <v>3043539006</v>
+      </c>
+      <c r="H82" t="s">
+        <v>747</v>
+      </c>
+      <c r="I82">
+        <v>557982</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" t="s">
+        <v>285</v>
+      </c>
+      <c r="C83" t="s">
+        <v>400</v>
+      </c>
+      <c r="D83" t="s">
+        <v>480</v>
+      </c>
+      <c r="E83" t="s">
+        <v>573</v>
+      </c>
+      <c r="F83" t="s">
+        <v>588</v>
+      </c>
+      <c r="G83">
+        <v>3185289407</v>
+      </c>
+      <c r="H83" t="s">
+        <v>748</v>
+      </c>
+      <c r="I83">
+        <v>538030</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" t="s">
+        <v>286</v>
+      </c>
+      <c r="C84" t="s">
+        <v>407</v>
+      </c>
+      <c r="D84" t="s">
+        <v>481</v>
+      </c>
+      <c r="E84" t="s">
+        <v>573</v>
+      </c>
+      <c r="F84" t="s">
+        <v>627</v>
+      </c>
+      <c r="G84">
+        <v>3127587059</v>
+      </c>
+      <c r="H84" t="s">
+        <v>749</v>
+      </c>
+      <c r="I84">
+        <v>585486</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" t="s">
+        <v>287</v>
+      </c>
+      <c r="C85" t="s">
+        <v>403</v>
+      </c>
+      <c r="D85" t="s">
+        <v>482</v>
+      </c>
+      <c r="E85" t="s">
+        <v>573</v>
+      </c>
+      <c r="F85" t="s">
+        <v>588</v>
+      </c>
+      <c r="G85">
+        <v>3185529619</v>
+      </c>
+      <c r="H85" t="s">
+        <v>750</v>
+      </c>
+      <c r="I85">
+        <v>522793</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" t="s">
+        <v>288</v>
+      </c>
+      <c r="C86" t="s">
+        <v>407</v>
+      </c>
+      <c r="D86" t="s">
+        <v>483</v>
+      </c>
+      <c r="E86" t="s">
+        <v>574</v>
+      </c>
+      <c r="F86" t="s">
+        <v>588</v>
+      </c>
+      <c r="G86">
+        <v>3054229744</v>
+      </c>
+      <c r="H86" t="s">
+        <v>751</v>
+      </c>
+      <c r="I86">
+        <v>550754</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" t="s">
+        <v>289</v>
+      </c>
+      <c r="C87" t="s">
+        <v>404</v>
+      </c>
+      <c r="D87" t="s">
+        <v>484</v>
+      </c>
+      <c r="E87" t="s">
+        <v>573</v>
+      </c>
+      <c r="F87" t="s">
+        <v>628</v>
+      </c>
+      <c r="G87">
+        <v>3102013484</v>
+      </c>
+      <c r="H87" t="s">
+        <v>752</v>
+      </c>
+      <c r="I87">
+        <v>952506</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" t="s">
+        <v>290</v>
+      </c>
+      <c r="C88" t="s">
+        <v>407</v>
+      </c>
+      <c r="D88" t="s">
+        <v>485</v>
+      </c>
+      <c r="E88" t="s">
+        <v>573</v>
+      </c>
+      <c r="F88" t="s">
+        <v>629</v>
+      </c>
+      <c r="G88">
+        <v>3206768830</v>
+      </c>
+      <c r="H88" t="s">
+        <v>753</v>
+      </c>
+      <c r="I88">
+        <v>550754</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" t="s">
+        <v>291</v>
+      </c>
+      <c r="C89" t="s">
+        <v>406</v>
+      </c>
+      <c r="D89" t="s">
+        <v>485</v>
+      </c>
+      <c r="E89" t="s">
+        <v>573</v>
+      </c>
+      <c r="F89" t="s">
+        <v>629</v>
+      </c>
+      <c r="G89">
+        <v>3206768830</v>
+      </c>
+      <c r="H89" t="s">
+        <v>753</v>
+      </c>
+      <c r="I89">
+        <v>455648</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" t="s">
+        <v>292</v>
+      </c>
+      <c r="C90" t="s">
+        <v>410</v>
+      </c>
+      <c r="D90" t="s">
+        <v>486</v>
+      </c>
+      <c r="E90" t="s">
+        <v>573</v>
+      </c>
+      <c r="F90" t="s">
+        <v>588</v>
+      </c>
+      <c r="G90">
+        <v>3018734931</v>
+      </c>
+      <c r="H90" t="s">
+        <v>754</v>
+      </c>
+      <c r="I90">
+        <v>585205</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" t="s">
+        <v>293</v>
+      </c>
+      <c r="C91" t="s">
+        <v>409</v>
+      </c>
+      <c r="D91" t="s">
+        <v>487</v>
+      </c>
+      <c r="E91" t="s">
+        <v>573</v>
+      </c>
+      <c r="F91" t="s">
+        <v>588</v>
+      </c>
+      <c r="G91">
+        <v>3023743363</v>
+      </c>
+      <c r="H91" t="s">
+        <v>755</v>
+      </c>
+      <c r="I91">
+        <v>630805</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" t="s">
+        <v>294</v>
+      </c>
+      <c r="C92" t="s">
+        <v>410</v>
+      </c>
+      <c r="D92" t="s">
+        <v>488</v>
+      </c>
+      <c r="E92" t="s">
+        <v>573</v>
+      </c>
+      <c r="F92" t="s">
+        <v>588</v>
+      </c>
+      <c r="G92">
+        <v>3177519337</v>
+      </c>
+      <c r="H92" t="s">
+        <v>756</v>
+      </c>
+      <c r="I92">
+        <v>368671</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" t="s">
+        <v>295</v>
+      </c>
+      <c r="C93" t="s">
+        <v>401</v>
+      </c>
+      <c r="D93" t="s">
+        <v>489</v>
+      </c>
+      <c r="E93" t="s">
+        <v>573</v>
+      </c>
+      <c r="F93" t="s">
+        <v>630</v>
+      </c>
+      <c r="G93">
+        <v>3122327344</v>
+      </c>
+      <c r="H93" t="s">
+        <v>757</v>
+      </c>
+      <c r="I93">
+        <v>534411</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>296</v>
+      </c>
+      <c r="C94" t="s">
+        <v>401</v>
+      </c>
+      <c r="D94" t="s">
+        <v>490</v>
+      </c>
+      <c r="E94" t="s">
+        <v>573</v>
+      </c>
+      <c r="F94" t="s">
+        <v>631</v>
+      </c>
+      <c r="G94">
+        <v>3234183390</v>
+      </c>
+      <c r="I94">
+        <v>566102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" t="s">
+        <v>297</v>
+      </c>
+      <c r="C95" t="s">
+        <v>400</v>
+      </c>
+      <c r="D95" t="s">
+        <v>491</v>
+      </c>
+      <c r="E95" t="s">
+        <v>573</v>
+      </c>
+      <c r="F95" t="s">
+        <v>632</v>
+      </c>
+      <c r="G95">
+        <v>3113200460</v>
+      </c>
+      <c r="H95" t="s">
+        <v>758</v>
+      </c>
+      <c r="I95">
+        <v>2710150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" t="s">
+        <v>298</v>
+      </c>
+      <c r="C96" t="s">
+        <v>400</v>
+      </c>
+      <c r="D96" t="s">
+        <v>492</v>
+      </c>
+      <c r="E96" t="s">
+        <v>574</v>
+      </c>
+      <c r="F96" t="s">
+        <v>633</v>
+      </c>
+      <c r="G96">
+        <v>3136146481</v>
+      </c>
+      <c r="H96" t="s">
+        <v>759</v>
+      </c>
+      <c r="I96">
+        <v>1133616</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" t="s">
+        <v>299</v>
+      </c>
+      <c r="C97" t="s">
+        <v>404</v>
+      </c>
+      <c r="D97" t="s">
+        <v>493</v>
+      </c>
+      <c r="E97" t="s">
+        <v>574</v>
+      </c>
+      <c r="F97" t="s">
+        <v>634</v>
+      </c>
+      <c r="G97">
+        <v>3017206508</v>
+      </c>
+      <c r="H97" t="s">
+        <v>760</v>
+      </c>
+      <c r="I97">
+        <v>955753</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" t="s">
+        <v>300</v>
+      </c>
+      <c r="C98" t="s">
+        <v>400</v>
+      </c>
+      <c r="D98" t="s">
+        <v>494</v>
+      </c>
+      <c r="E98" t="s">
+        <v>574</v>
+      </c>
+      <c r="F98" t="s">
+        <v>635</v>
+      </c>
+      <c r="G98">
+        <v>3135319641</v>
+      </c>
+      <c r="H98" t="s">
+        <v>761</v>
+      </c>
+      <c r="I98">
+        <v>538030</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" t="s">
+        <v>301</v>
+      </c>
+      <c r="C99" t="s">
+        <v>410</v>
+      </c>
+      <c r="D99" t="s">
+        <v>495</v>
+      </c>
+      <c r="E99" t="s">
+        <v>573</v>
+      </c>
+      <c r="F99" t="s">
+        <v>588</v>
+      </c>
+      <c r="G99">
+        <v>3022977529</v>
+      </c>
+      <c r="H99" t="s">
+        <v>762</v>
+      </c>
+      <c r="I99">
+        <v>1044902</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" t="s">
+        <v>302</v>
+      </c>
+      <c r="C100" t="s">
+        <v>399</v>
+      </c>
+      <c r="D100" t="s">
+        <v>496</v>
+      </c>
+      <c r="E100" t="s">
+        <v>573</v>
+      </c>
+      <c r="F100" t="s">
+        <v>588</v>
+      </c>
+      <c r="G100">
+        <v>3116823407</v>
+      </c>
+      <c r="H100" t="s">
+        <v>763</v>
+      </c>
+      <c r="I100">
+        <v>316330</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" t="s">
+        <v>303</v>
+      </c>
+      <c r="C101" t="s">
+        <v>407</v>
+      </c>
+      <c r="D101" t="s">
+        <v>497</v>
+      </c>
+      <c r="E101" t="s">
+        <v>573</v>
+      </c>
+      <c r="F101" t="s">
+        <v>588</v>
+      </c>
+      <c r="G101">
+        <v>3013807813</v>
+      </c>
+      <c r="H101" t="s">
+        <v>764</v>
+      </c>
+      <c r="I101">
+        <v>516023</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" t="s">
+        <v>304</v>
+      </c>
+      <c r="C102" t="s">
+        <v>409</v>
+      </c>
+      <c r="D102" t="s">
+        <v>498</v>
+      </c>
+      <c r="E102" t="s">
+        <v>573</v>
+      </c>
+      <c r="F102" t="s">
+        <v>588</v>
+      </c>
+      <c r="G102">
+        <v>3013807813</v>
+      </c>
+      <c r="H102" t="s">
+        <v>764</v>
+      </c>
+      <c r="I102">
+        <v>1198148</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" t="s">
+        <v>305</v>
+      </c>
+      <c r="C103" t="s">
+        <v>407</v>
+      </c>
+      <c r="D103" t="s">
+        <v>499</v>
+      </c>
+      <c r="E103" t="s">
+        <v>573</v>
+      </c>
+      <c r="F103" t="s">
+        <v>588</v>
+      </c>
+      <c r="G103">
+        <v>3186656220</v>
+      </c>
+      <c r="H103" t="s">
+        <v>765</v>
+      </c>
+      <c r="I103">
+        <v>2353944</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" t="s">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s">
+        <v>406</v>
+      </c>
+      <c r="D104" t="s">
+        <v>500</v>
+      </c>
+      <c r="E104" t="s">
+        <v>573</v>
+      </c>
+      <c r="F104" t="s">
+        <v>636</v>
+      </c>
+      <c r="G104">
+        <v>3003934941</v>
+      </c>
+      <c r="H104" t="s">
+        <v>766</v>
+      </c>
+      <c r="I104">
+        <v>969160</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" t="s">
+        <v>307</v>
+      </c>
+      <c r="C105" t="s">
+        <v>404</v>
+      </c>
+      <c r="D105" t="s">
+        <v>501</v>
+      </c>
+      <c r="E105" t="s">
+        <v>574</v>
+      </c>
+      <c r="F105" t="s">
+        <v>637</v>
+      </c>
+      <c r="G105">
+        <v>3135826724</v>
+      </c>
+      <c r="H105" t="s">
+        <v>767</v>
+      </c>
+      <c r="I105">
+        <v>475506</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" t="s">
+        <v>308</v>
+      </c>
+      <c r="C106" t="s">
+        <v>407</v>
+      </c>
+      <c r="D106" t="s">
+        <v>502</v>
+      </c>
+      <c r="E106" t="s">
+        <v>574</v>
+      </c>
+      <c r="F106" t="s">
+        <v>588</v>
+      </c>
+      <c r="G106">
+        <v>3015656941</v>
+      </c>
+      <c r="H106" t="s">
+        <v>768</v>
+      </c>
+      <c r="I106">
+        <v>1651524</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" t="s">
+        <v>309</v>
+      </c>
+      <c r="C107" t="s">
+        <v>401</v>
+      </c>
+      <c r="D107" t="s">
+        <v>503</v>
+      </c>
+      <c r="E107" t="s">
+        <v>573</v>
+      </c>
+      <c r="F107" t="s">
+        <v>588</v>
+      </c>
+      <c r="G107">
+        <v>3147902111</v>
+      </c>
+      <c r="H107" t="s">
+        <v>769</v>
+      </c>
+      <c r="I107">
+        <v>364504</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" t="s">
+        <v>310</v>
+      </c>
+      <c r="C108" t="s">
+        <v>405</v>
+      </c>
+      <c r="D108" t="s">
+        <v>504</v>
+      </c>
+      <c r="E108" t="s">
+        <v>574</v>
+      </c>
+      <c r="F108" t="s">
+        <v>638</v>
+      </c>
+      <c r="G108">
+        <v>3137429086</v>
+      </c>
+      <c r="H108" t="s">
+        <v>770</v>
+      </c>
+      <c r="I108">
+        <v>517366</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>116</v>
+      </c>
+      <c r="B109" t="s">
+        <v>311</v>
+      </c>
+      <c r="C109" t="s">
+        <v>411</v>
+      </c>
+      <c r="D109" t="s">
+        <v>505</v>
+      </c>
+      <c r="E109" t="s">
+        <v>574</v>
+      </c>
+      <c r="F109" t="s">
+        <v>588</v>
+      </c>
+      <c r="G109">
+        <v>3017266368</v>
+      </c>
+      <c r="H109" t="s">
+        <v>771</v>
+      </c>
+      <c r="I109">
+        <v>1416696</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" t="s">
+        <v>312</v>
+      </c>
+      <c r="C110" t="s">
+        <v>408</v>
+      </c>
+      <c r="D110" t="s">
+        <v>505</v>
+      </c>
+      <c r="E110" t="s">
+        <v>574</v>
+      </c>
+      <c r="F110" t="s">
+        <v>588</v>
+      </c>
+      <c r="G110">
+        <v>3017266368</v>
+      </c>
+      <c r="H110" t="s">
+        <v>771</v>
+      </c>
+      <c r="I110">
+        <v>1160620</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" t="s">
+        <v>313</v>
+      </c>
+      <c r="C111" t="s">
+        <v>399</v>
+      </c>
+      <c r="D111" t="s">
+        <v>505</v>
+      </c>
+      <c r="E111" t="s">
+        <v>574</v>
+      </c>
+      <c r="F111" t="s">
+        <v>588</v>
+      </c>
+      <c r="G111">
+        <v>3017266368</v>
+      </c>
+      <c r="H111" t="s">
+        <v>771</v>
+      </c>
+      <c r="I111">
+        <v>1344322</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" t="s">
+        <v>314</v>
+      </c>
+      <c r="C112" t="s">
+        <v>410</v>
+      </c>
+      <c r="D112" t="s">
+        <v>506</v>
+      </c>
+      <c r="E112" t="s">
+        <v>578</v>
+      </c>
+      <c r="F112" t="s">
+        <v>588</v>
+      </c>
+      <c r="G112">
+        <v>3178566054</v>
+      </c>
+      <c r="H112" t="s">
+        <v>772</v>
+      </c>
+      <c r="I112">
+        <v>554327</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" t="s">
+        <v>315</v>
+      </c>
+      <c r="C113" t="s">
+        <v>404</v>
+      </c>
+      <c r="D113" t="s">
+        <v>507</v>
+      </c>
+      <c r="E113" t="s">
+        <v>574</v>
+      </c>
+      <c r="F113" t="s">
+        <v>639</v>
+      </c>
+      <c r="G113">
+        <v>3164904630</v>
+      </c>
+      <c r="H113" t="s">
+        <v>773</v>
+      </c>
+      <c r="I113">
+        <v>507330</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" t="s">
+        <v>316</v>
+      </c>
+      <c r="C114" t="s">
+        <v>404</v>
+      </c>
+      <c r="D114" t="s">
+        <v>508</v>
+      </c>
+      <c r="E114" t="s">
+        <v>573</v>
+      </c>
+      <c r="F114" t="s">
+        <v>640</v>
+      </c>
+      <c r="G114">
+        <v>3015954319</v>
+      </c>
+      <c r="H114" t="s">
+        <v>774</v>
+      </c>
+      <c r="I114">
+        <v>3073980</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" t="s">
+        <v>317</v>
+      </c>
+      <c r="C115" t="s">
+        <v>403</v>
+      </c>
+      <c r="D115" t="s">
+        <v>509</v>
+      </c>
+      <c r="E115" t="s">
+        <v>573</v>
+      </c>
+      <c r="F115" t="s">
+        <v>641</v>
+      </c>
+      <c r="G115">
+        <v>3103764070</v>
+      </c>
+      <c r="H115" t="s">
+        <v>775</v>
+      </c>
+      <c r="I115">
+        <v>628360</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" t="s">
+        <v>318</v>
+      </c>
+      <c r="C116" t="s">
+        <v>401</v>
+      </c>
+      <c r="D116" t="s">
+        <v>509</v>
+      </c>
+      <c r="E116" t="s">
+        <v>573</v>
+      </c>
+      <c r="F116" t="s">
+        <v>641</v>
+      </c>
+      <c r="G116">
+        <v>3103764070</v>
+      </c>
+      <c r="H116" t="s">
+        <v>775</v>
+      </c>
+      <c r="I116">
+        <v>566102</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" t="s">
+        <v>319</v>
+      </c>
+      <c r="C117" t="s">
+        <v>403</v>
+      </c>
+      <c r="D117" t="s">
+        <v>510</v>
+      </c>
+      <c r="E117" t="s">
+        <v>573</v>
+      </c>
+      <c r="F117" t="s">
+        <v>642</v>
+      </c>
+      <c r="G117">
+        <v>3104076628</v>
+      </c>
+      <c r="H117" t="s">
+        <v>776</v>
+      </c>
+      <c r="I117">
+        <v>593171</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" t="s">
+        <v>320</v>
+      </c>
+      <c r="C118" t="s">
+        <v>402</v>
+      </c>
+      <c r="D118" t="s">
+        <v>511</v>
+      </c>
+      <c r="E118" t="s">
+        <v>573</v>
+      </c>
+      <c r="F118" t="s">
+        <v>643</v>
+      </c>
+      <c r="G118">
+        <v>3006234263</v>
+      </c>
+      <c r="H118" t="s">
+        <v>777</v>
+      </c>
+      <c r="I118">
+        <v>719849</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" t="s">
+        <v>321</v>
+      </c>
+      <c r="C119" t="s">
+        <v>409</v>
+      </c>
+      <c r="D119" t="s">
+        <v>511</v>
+      </c>
+      <c r="E119" t="s">
+        <v>573</v>
+      </c>
+      <c r="F119" t="s">
+        <v>643</v>
+      </c>
+      <c r="G119">
+        <v>3006234263</v>
+      </c>
+      <c r="H119" t="s">
+        <v>777</v>
+      </c>
+      <c r="I119">
+        <v>631561</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" t="s">
+        <v>322</v>
+      </c>
+      <c r="C120" t="s">
+        <v>405</v>
+      </c>
+      <c r="D120" t="s">
+        <v>512</v>
+      </c>
+      <c r="E120" t="s">
+        <v>573</v>
+      </c>
+      <c r="F120" t="s">
+        <v>644</v>
+      </c>
+      <c r="G120">
+        <v>3124291951</v>
+      </c>
+      <c r="H120" t="s">
+        <v>778</v>
+      </c>
+      <c r="I120">
+        <v>815648</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" t="s">
+        <v>323</v>
+      </c>
+      <c r="C121" t="s">
+        <v>404</v>
+      </c>
+      <c r="D121" t="s">
+        <v>512</v>
+      </c>
+      <c r="E121" t="s">
+        <v>573</v>
+      </c>
+      <c r="F121" t="s">
+        <v>644</v>
+      </c>
+      <c r="G121">
+        <v>3124291951</v>
+      </c>
+      <c r="H121" t="s">
+        <v>778</v>
+      </c>
+      <c r="I121">
+        <v>198660</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" t="s">
+        <v>324</v>
+      </c>
+      <c r="C122" t="s">
+        <v>410</v>
+      </c>
+      <c r="D122" t="s">
+        <v>513</v>
+      </c>
+      <c r="E122" t="s">
+        <v>573</v>
+      </c>
+      <c r="F122" t="s">
+        <v>588</v>
+      </c>
+      <c r="G122">
+        <v>3117316210</v>
+      </c>
+      <c r="H122" t="s">
+        <v>779</v>
+      </c>
+      <c r="I122">
+        <v>1190353</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" t="s">
+        <v>325</v>
+      </c>
+      <c r="C123" t="s">
+        <v>406</v>
+      </c>
+      <c r="D123" t="s">
+        <v>514</v>
+      </c>
+      <c r="E123" t="s">
+        <v>574</v>
+      </c>
+      <c r="F123" t="s">
+        <v>645</v>
+      </c>
+      <c r="G123">
+        <v>3146194734</v>
+      </c>
+      <c r="H123" t="s">
+        <v>780</v>
+      </c>
+      <c r="I123">
+        <v>513072</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" t="s">
+        <v>326</v>
+      </c>
+      <c r="C124" t="s">
+        <v>409</v>
+      </c>
+      <c r="D124" t="s">
+        <v>515</v>
+      </c>
+      <c r="E124" t="s">
+        <v>574</v>
+      </c>
+      <c r="F124" t="s">
+        <v>646</v>
+      </c>
+      <c r="G124">
+        <v>3147637271</v>
+      </c>
+      <c r="H124" t="s">
+        <v>781</v>
+      </c>
+      <c r="I124">
+        <v>598074</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" t="s">
+        <v>327</v>
+      </c>
+      <c r="C125" t="s">
+        <v>409</v>
+      </c>
+      <c r="D125" t="s">
+        <v>516</v>
+      </c>
+      <c r="E125" t="s">
+        <v>573</v>
+      </c>
+      <c r="F125" t="s">
+        <v>588</v>
+      </c>
+      <c r="G125">
+        <v>3233068651</v>
+      </c>
+      <c r="H125" t="s">
+        <v>782</v>
+      </c>
+      <c r="I125">
+        <v>631561</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" t="s">
+        <v>328</v>
+      </c>
+      <c r="C126" t="s">
+        <v>400</v>
+      </c>
+      <c r="D126" t="s">
+        <v>516</v>
+      </c>
+      <c r="E126" t="s">
+        <v>573</v>
+      </c>
+      <c r="F126" t="s">
+        <v>588</v>
+      </c>
+      <c r="G126">
+        <v>3233068651</v>
+      </c>
+      <c r="H126" t="s">
+        <v>782</v>
+      </c>
+      <c r="I126">
+        <v>601842</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" t="s">
+        <v>329</v>
+      </c>
+      <c r="C127" t="s">
+        <v>406</v>
+      </c>
+      <c r="D127" t="s">
+        <v>517</v>
+      </c>
+      <c r="E127" t="s">
+        <v>574</v>
+      </c>
+      <c r="F127" t="s">
+        <v>647</v>
+      </c>
+      <c r="G127">
+        <v>3105742931</v>
+      </c>
+      <c r="H127" t="s">
+        <v>783</v>
+      </c>
+      <c r="I127">
+        <v>442160</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>135</v>
+      </c>
+      <c r="B128" t="s">
+        <v>330</v>
+      </c>
+      <c r="C128" t="s">
+        <v>404</v>
+      </c>
+      <c r="D128" t="s">
+        <v>518</v>
+      </c>
+      <c r="E128" t="s">
+        <v>574</v>
+      </c>
+      <c r="F128" t="s">
+        <v>648</v>
+      </c>
+      <c r="G128">
+        <v>3216167718</v>
+      </c>
+      <c r="H128" t="s">
+        <v>784</v>
+      </c>
+      <c r="I128">
+        <v>477251</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" t="s">
+        <v>331</v>
+      </c>
+      <c r="C129" t="s">
+        <v>403</v>
+      </c>
+      <c r="D129" t="s">
+        <v>519</v>
+      </c>
+      <c r="E129" t="s">
+        <v>573</v>
+      </c>
+      <c r="F129" t="s">
+        <v>649</v>
+      </c>
+      <c r="G129">
+        <v>3187025440</v>
+      </c>
+      <c r="H129" t="s">
+        <v>785</v>
+      </c>
+      <c r="I129">
+        <v>342417</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" t="s">
+        <v>332</v>
+      </c>
+      <c r="C130" t="s">
+        <v>409</v>
+      </c>
+      <c r="D130" t="s">
+        <v>520</v>
+      </c>
+      <c r="E130" t="s">
+        <v>574</v>
+      </c>
+      <c r="F130" t="s">
+        <v>650</v>
+      </c>
+      <c r="G130">
+        <v>3506697092</v>
+      </c>
+      <c r="H130" t="s">
+        <v>786</v>
+      </c>
+      <c r="I130">
+        <v>564586</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>138</v>
+      </c>
+      <c r="B131" t="s">
+        <v>333</v>
+      </c>
+      <c r="C131" t="s">
+        <v>407</v>
+      </c>
+      <c r="D131" t="s">
+        <v>521</v>
+      </c>
+      <c r="E131" t="s">
+        <v>573</v>
+      </c>
+      <c r="F131" t="s">
+        <v>588</v>
+      </c>
+      <c r="G131">
+        <v>3217281114</v>
+      </c>
+      <c r="H131" t="s">
+        <v>787</v>
+      </c>
+      <c r="I131">
+        <v>585486</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" t="s">
+        <v>334</v>
+      </c>
+      <c r="C132" t="s">
+        <v>405</v>
+      </c>
+      <c r="D132" t="s">
+        <v>522</v>
+      </c>
+      <c r="E132" t="s">
+        <v>573</v>
+      </c>
+      <c r="F132" t="s">
+        <v>651</v>
+      </c>
+      <c r="G132">
+        <v>3166226027</v>
+      </c>
+      <c r="H132" t="s">
+        <v>788</v>
+      </c>
+      <c r="I132">
+        <v>1224620</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" t="s">
+        <v>335</v>
+      </c>
+      <c r="C133" t="s">
+        <v>403</v>
+      </c>
+      <c r="D133" t="s">
+        <v>523</v>
+      </c>
+      <c r="E133" t="s">
+        <v>574</v>
+      </c>
+      <c r="F133" t="s">
+        <v>588</v>
+      </c>
+      <c r="G133">
+        <v>5614641026</v>
+      </c>
+      <c r="H133" t="s">
+        <v>789</v>
+      </c>
+      <c r="I133">
+        <v>584026</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" t="s">
+        <v>336</v>
+      </c>
+      <c r="C134" t="s">
+        <v>400</v>
+      </c>
+      <c r="D134" t="s">
+        <v>524</v>
+      </c>
+      <c r="E134" t="s">
+        <v>573</v>
+      </c>
+      <c r="F134" t="s">
+        <v>588</v>
+      </c>
+      <c r="G134">
+        <v>3168316927</v>
+      </c>
+      <c r="H134" t="s">
+        <v>790</v>
+      </c>
+      <c r="I134">
+        <v>569936</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135" t="s">
+        <v>337</v>
+      </c>
+      <c r="C135" t="s">
+        <v>405</v>
+      </c>
+      <c r="D135" t="s">
+        <v>525</v>
+      </c>
+      <c r="E135" t="s">
+        <v>574</v>
+      </c>
+      <c r="F135" t="s">
+        <v>588</v>
+      </c>
+      <c r="G135">
+        <v>3187935393</v>
+      </c>
+      <c r="H135" t="s">
+        <v>791</v>
+      </c>
+      <c r="I135">
+        <v>687220</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" t="s">
+        <v>338</v>
+      </c>
+      <c r="C136" t="s">
+        <v>403</v>
+      </c>
+      <c r="D136" t="s">
+        <v>526</v>
+      </c>
+      <c r="E136" t="s">
+        <v>574</v>
+      </c>
+      <c r="F136" t="s">
+        <v>652</v>
+      </c>
+      <c r="G136">
+        <v>3177063250</v>
+      </c>
+      <c r="H136" t="s">
+        <v>792</v>
+      </c>
+      <c r="I136">
+        <v>663548</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" t="s">
+        <v>339</v>
+      </c>
+      <c r="C137" t="s">
+        <v>402</v>
+      </c>
+      <c r="D137" t="s">
+        <v>527</v>
+      </c>
+      <c r="E137" t="s">
+        <v>573</v>
+      </c>
+      <c r="F137" t="s">
+        <v>653</v>
+      </c>
+      <c r="G137">
+        <v>3178333446</v>
+      </c>
+      <c r="H137" t="s">
+        <v>793</v>
+      </c>
+      <c r="I137">
+        <v>605299</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" t="s">
+        <v>340</v>
+      </c>
+      <c r="C138" t="s">
+        <v>407</v>
+      </c>
+      <c r="D138" t="s">
+        <v>527</v>
+      </c>
+      <c r="E138" t="s">
+        <v>573</v>
+      </c>
+      <c r="F138" t="s">
+        <v>653</v>
+      </c>
+      <c r="G138">
+        <v>3178333446</v>
+      </c>
+      <c r="H138" t="s">
+        <v>793</v>
+      </c>
+      <c r="I138">
+        <v>550754</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" t="s">
+        <v>341</v>
+      </c>
+      <c r="C139" t="s">
+        <v>401</v>
+      </c>
+      <c r="D139" t="s">
+        <v>528</v>
+      </c>
+      <c r="E139" t="s">
+        <v>573</v>
+      </c>
+      <c r="F139" t="s">
+        <v>654</v>
+      </c>
+      <c r="G139">
+        <v>3136720235</v>
+      </c>
+      <c r="H139" t="s">
+        <v>794</v>
+      </c>
+      <c r="I139">
+        <v>481170</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" t="s">
+        <v>342</v>
+      </c>
+      <c r="C140" t="s">
+        <v>407</v>
+      </c>
+      <c r="D140" t="s">
+        <v>528</v>
+      </c>
+      <c r="E140" t="s">
+        <v>573</v>
+      </c>
+      <c r="F140" t="s">
+        <v>654</v>
+      </c>
+      <c r="G140">
+        <v>3136720235</v>
+      </c>
+      <c r="H140" t="s">
+        <v>794</v>
+      </c>
+      <c r="I140">
+        <v>527137</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" t="s">
+        <v>343</v>
+      </c>
+      <c r="C141" t="s">
+        <v>401</v>
+      </c>
+      <c r="D141" t="s">
+        <v>529</v>
+      </c>
+      <c r="E141" t="s">
+        <v>574</v>
+      </c>
+      <c r="F141" t="s">
+        <v>588</v>
+      </c>
+      <c r="G141">
+        <v>3226367303</v>
+      </c>
+      <c r="H141" t="s">
+        <v>795</v>
+      </c>
+      <c r="I141">
+        <v>2941320</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" t="s">
+        <v>344</v>
+      </c>
+      <c r="C142" t="s">
+        <v>404</v>
+      </c>
+      <c r="D142" t="s">
+        <v>530</v>
+      </c>
+      <c r="E142" t="s">
+        <v>574</v>
+      </c>
+      <c r="F142" t="s">
+        <v>588</v>
+      </c>
+      <c r="G142">
+        <v>3112833518</v>
+      </c>
+      <c r="H142" t="s">
+        <v>796</v>
+      </c>
+      <c r="I142">
+        <v>914782</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" t="s">
+        <v>345</v>
+      </c>
+      <c r="C143" t="s">
+        <v>409</v>
+      </c>
+      <c r="D143" t="s">
+        <v>530</v>
+      </c>
+      <c r="E143" t="s">
+        <v>573</v>
+      </c>
+      <c r="F143" t="s">
+        <v>588</v>
+      </c>
+      <c r="G143">
+        <v>3103161676</v>
+      </c>
+      <c r="H143" t="s">
+        <v>797</v>
+      </c>
+      <c r="I143">
+        <v>1015962</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" t="s">
+        <v>346</v>
+      </c>
+      <c r="C144" t="s">
+        <v>400</v>
+      </c>
+      <c r="D144" t="s">
+        <v>531</v>
+      </c>
+      <c r="E144" t="s">
+        <v>574</v>
+      </c>
+      <c r="F144" t="s">
+        <v>655</v>
+      </c>
+      <c r="G144">
+        <v>3186229275</v>
+      </c>
+      <c r="I144">
+        <v>506123</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" t="s">
+        <v>347</v>
+      </c>
+      <c r="C145" t="s">
+        <v>407</v>
+      </c>
+      <c r="D145" t="s">
+        <v>532</v>
+      </c>
+      <c r="E145" t="s">
+        <v>574</v>
+      </c>
+      <c r="F145" t="s">
+        <v>588</v>
+      </c>
+      <c r="G145">
+        <v>3175177575</v>
+      </c>
+      <c r="H145" t="s">
+        <v>798</v>
+      </c>
+      <c r="I145">
+        <v>585486</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" t="s">
+        <v>348</v>
+      </c>
+      <c r="C146" t="s">
+        <v>400</v>
+      </c>
+      <c r="D146" t="s">
+        <v>533</v>
+      </c>
+      <c r="E146" t="s">
+        <v>574</v>
+      </c>
+      <c r="F146" t="s">
+        <v>656</v>
+      </c>
+      <c r="G146">
+        <v>3006019149</v>
+      </c>
+      <c r="H146" t="s">
+        <v>799</v>
+      </c>
+      <c r="I146">
+        <v>569936</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" t="s">
+        <v>349</v>
+      </c>
+      <c r="C147" t="s">
+        <v>406</v>
+      </c>
+      <c r="D147" t="s">
+        <v>533</v>
+      </c>
+      <c r="E147" t="s">
+        <v>574</v>
+      </c>
+      <c r="F147" t="s">
+        <v>656</v>
+      </c>
+      <c r="G147">
+        <v>3006019149</v>
+      </c>
+      <c r="H147" t="s">
+        <v>799</v>
+      </c>
+      <c r="I147">
+        <v>513072</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" t="s">
+        <v>350</v>
+      </c>
+      <c r="C148" t="s">
+        <v>402</v>
+      </c>
+      <c r="D148" t="s">
+        <v>534</v>
+      </c>
+      <c r="E148" t="s">
+        <v>579</v>
+      </c>
+      <c r="F148" t="s">
+        <v>657</v>
+      </c>
+      <c r="G148">
+        <v>3112860092</v>
+      </c>
+      <c r="H148" t="s">
+        <v>800</v>
+      </c>
+      <c r="I148">
+        <v>1241196</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" t="s">
+        <v>351</v>
+      </c>
+      <c r="C149" t="s">
+        <v>401</v>
+      </c>
+      <c r="D149" t="s">
+        <v>534</v>
+      </c>
+      <c r="E149" t="s">
+        <v>580</v>
+      </c>
+      <c r="F149" t="s">
+        <v>657</v>
+      </c>
+      <c r="G149">
+        <v>3112860092</v>
+      </c>
+      <c r="H149" t="s">
+        <v>800</v>
+      </c>
+      <c r="I149">
+        <v>1513600</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" t="s">
+        <v>352</v>
+      </c>
+      <c r="C150" t="s">
+        <v>409</v>
+      </c>
+      <c r="D150" t="s">
+        <v>535</v>
+      </c>
+      <c r="E150" t="s">
+        <v>573</v>
+      </c>
+      <c r="F150" t="s">
+        <v>658</v>
+      </c>
+      <c r="G150">
+        <v>3113681582</v>
+      </c>
+      <c r="H150" t="s">
+        <v>801</v>
+      </c>
+      <c r="I150">
+        <v>531099</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" t="s">
+        <v>353</v>
+      </c>
+      <c r="C151" t="s">
+        <v>403</v>
+      </c>
+      <c r="D151" t="s">
+        <v>536</v>
+      </c>
+      <c r="E151" t="s">
+        <v>573</v>
+      </c>
+      <c r="F151" t="s">
+        <v>588</v>
+      </c>
+      <c r="G151">
+        <v>3108699380</v>
+      </c>
+      <c r="H151" t="s">
+        <v>802</v>
+      </c>
+      <c r="I151">
+        <v>1258720</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" t="s">
+        <v>354</v>
+      </c>
+      <c r="C152" t="s">
+        <v>410</v>
+      </c>
+      <c r="D152" t="s">
+        <v>536</v>
+      </c>
+      <c r="E152" t="s">
+        <v>573</v>
+      </c>
+      <c r="F152" t="s">
+        <v>588</v>
+      </c>
+      <c r="G152">
+        <v>3108699380</v>
+      </c>
+      <c r="H152" t="s">
+        <v>802</v>
+      </c>
+      <c r="I152">
+        <v>1176410</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" t="s">
+        <v>355</v>
+      </c>
+      <c r="C153" t="s">
+        <v>405</v>
+      </c>
+      <c r="D153" t="s">
+        <v>537</v>
+      </c>
+      <c r="E153" t="s">
+        <v>580</v>
+      </c>
+      <c r="F153" t="s">
+        <v>659</v>
+      </c>
+      <c r="G153">
+        <v>3134633058</v>
+      </c>
+      <c r="H153" t="s">
+        <v>803</v>
+      </c>
+      <c r="I153">
+        <v>648632</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" t="s">
+        <v>356</v>
+      </c>
+      <c r="C154" t="s">
+        <v>402</v>
+      </c>
+      <c r="D154" t="s">
+        <v>538</v>
+      </c>
+      <c r="E154" t="s">
+        <v>574</v>
+      </c>
+      <c r="F154" t="s">
+        <v>660</v>
+      </c>
+      <c r="G154">
+        <v>3508996381</v>
+      </c>
+      <c r="H154" t="s">
+        <v>804</v>
+      </c>
+      <c r="I154">
+        <v>643482</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" t="s">
+        <v>357</v>
+      </c>
+      <c r="C155" t="s">
+        <v>401</v>
+      </c>
+      <c r="D155" t="s">
+        <v>538</v>
+      </c>
+      <c r="E155" t="s">
+        <v>574</v>
+      </c>
+      <c r="F155" t="s">
+        <v>660</v>
+      </c>
+      <c r="G155">
+        <v>3508996381</v>
+      </c>
+      <c r="H155" t="s">
+        <v>804</v>
+      </c>
+      <c r="I155">
+        <v>534411</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" t="s">
+        <v>358</v>
+      </c>
+      <c r="C156" t="s">
+        <v>404</v>
+      </c>
+      <c r="D156" t="s">
+        <v>539</v>
+      </c>
+      <c r="E156" t="s">
+        <v>579</v>
+      </c>
+      <c r="F156" t="s">
+        <v>588</v>
+      </c>
+      <c r="G156">
+        <v>3194309799</v>
+      </c>
+      <c r="H156" t="s">
+        <v>805</v>
+      </c>
+      <c r="I156">
+        <v>955506</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" t="s">
         <v>164</v>
       </c>
-      <c r="C79" t="s">
+      <c r="B157" t="s">
+        <v>359</v>
+      </c>
+      <c r="C157" t="s">
+        <v>406</v>
+      </c>
+      <c r="D157" t="s">
+        <v>540</v>
+      </c>
+      <c r="E157" t="s">
+        <v>573</v>
+      </c>
+      <c r="F157" t="s">
+        <v>588</v>
+      </c>
+      <c r="G157">
+        <v>3106368274</v>
+      </c>
+      <c r="H157" t="s">
+        <v>806</v>
+      </c>
+      <c r="I157">
+        <v>968160</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" t="s">
+        <v>360</v>
+      </c>
+      <c r="C158" t="s">
+        <v>406</v>
+      </c>
+      <c r="D158" t="s">
+        <v>541</v>
+      </c>
+      <c r="E158" t="s">
+        <v>573</v>
+      </c>
+      <c r="F158" t="s">
+        <v>661</v>
+      </c>
+      <c r="G158">
+        <v>3008674834</v>
+      </c>
+      <c r="H158" t="s">
+        <v>807</v>
+      </c>
+      <c r="I158">
+        <v>970660</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" t="s">
+        <v>361</v>
+      </c>
+      <c r="C159" t="s">
+        <v>400</v>
+      </c>
+      <c r="D159" t="s">
+        <v>542</v>
+      </c>
+      <c r="E159" t="s">
+        <v>574</v>
+      </c>
+      <c r="F159" t="s">
+        <v>662</v>
+      </c>
+      <c r="G159">
+        <v>3002900521</v>
+      </c>
+      <c r="H159" t="s">
+        <v>808</v>
+      </c>
+      <c r="I159">
+        <v>538030</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" t="s">
+        <v>362</v>
+      </c>
+      <c r="C160" t="s">
+        <v>399</v>
+      </c>
+      <c r="D160" t="s">
+        <v>542</v>
+      </c>
+      <c r="E160" t="s">
+        <v>574</v>
+      </c>
+      <c r="F160" t="s">
+        <v>662</v>
+      </c>
+      <c r="G160">
+        <v>3002900521</v>
+      </c>
+      <c r="H160" t="s">
+        <v>808</v>
+      </c>
+      <c r="I160">
+        <v>671161</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" t="s">
+        <v>363</v>
+      </c>
+      <c r="C161" t="s">
+        <v>404</v>
+      </c>
+      <c r="D161" t="s">
+        <v>543</v>
+      </c>
+      <c r="E161" t="s">
+        <v>574</v>
+      </c>
+      <c r="F161" t="s">
+        <v>663</v>
+      </c>
+      <c r="G161">
+        <v>3154129094</v>
+      </c>
+      <c r="H161" t="s">
+        <v>809</v>
+      </c>
+      <c r="I161">
+        <v>429726</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" t="s">
         <v>169</v>
       </c>
-      <c r="D79" t="s">
-        <v>237</v>
-      </c>
-      <c r="E79" t="s">
-        <v>240</v>
-      </c>
-      <c r="F79" t="s">
-        <v>246</v>
-      </c>
-      <c r="G79">
+      <c r="B162" t="s">
+        <v>364</v>
+      </c>
+      <c r="C162" t="s">
+        <v>406</v>
+      </c>
+      <c r="D162" t="s">
+        <v>544</v>
+      </c>
+      <c r="E162" t="s">
+        <v>574</v>
+      </c>
+      <c r="F162" t="s">
+        <v>664</v>
+      </c>
+      <c r="G162">
+        <v>3104534612</v>
+      </c>
+      <c r="H162" t="s">
+        <v>810</v>
+      </c>
+      <c r="I162">
+        <v>486360</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" t="s">
+        <v>365</v>
+      </c>
+      <c r="C163" t="s">
+        <v>405</v>
+      </c>
+      <c r="D163" t="s">
+        <v>545</v>
+      </c>
+      <c r="E163" t="s">
+        <v>574</v>
+      </c>
+      <c r="F163" t="s">
+        <v>665</v>
+      </c>
+      <c r="G163">
+        <v>3022424243</v>
+      </c>
+      <c r="H163" t="s">
+        <v>811</v>
+      </c>
+      <c r="I163">
+        <v>1773944</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" t="s">
+        <v>366</v>
+      </c>
+      <c r="C164" t="s">
+        <v>400</v>
+      </c>
+      <c r="D164" t="s">
+        <v>546</v>
+      </c>
+      <c r="E164" t="s">
+        <v>574</v>
+      </c>
+      <c r="F164" t="s">
+        <v>666</v>
+      </c>
+      <c r="G164">
+        <v>3127382747</v>
+      </c>
+      <c r="H164" t="s">
+        <v>812</v>
+      </c>
+      <c r="I164">
+        <v>1524369</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" t="s">
+        <v>367</v>
+      </c>
+      <c r="C165" t="s">
+        <v>406</v>
+      </c>
+      <c r="D165" t="s">
+        <v>546</v>
+      </c>
+      <c r="E165" t="s">
+        <v>574</v>
+      </c>
+      <c r="F165" t="s">
+        <v>666</v>
+      </c>
+      <c r="G165">
+        <v>3127382747</v>
+      </c>
+      <c r="H165" t="s">
+        <v>812</v>
+      </c>
+      <c r="I165">
+        <v>913296</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" t="s">
+        <v>368</v>
+      </c>
+      <c r="C166" t="s">
+        <v>407</v>
+      </c>
+      <c r="D166" t="s">
+        <v>546</v>
+      </c>
+      <c r="E166" t="s">
+        <v>574</v>
+      </c>
+      <c r="F166" t="s">
+        <v>666</v>
+      </c>
+      <c r="G166">
+        <v>3127382747</v>
+      </c>
+      <c r="H166" t="s">
+        <v>812</v>
+      </c>
+      <c r="I166">
+        <v>1658262</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" t="s">
+        <v>369</v>
+      </c>
+      <c r="C167" t="s">
+        <v>402</v>
+      </c>
+      <c r="D167" t="s">
+        <v>547</v>
+      </c>
+      <c r="E167" t="s">
+        <v>573</v>
+      </c>
+      <c r="F167" t="s">
+        <v>588</v>
+      </c>
+      <c r="G167">
+        <v>3168660548</v>
+      </c>
+      <c r="H167" t="s">
+        <v>813</v>
+      </c>
+      <c r="I167">
+        <v>2657794</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" t="s">
+        <v>370</v>
+      </c>
+      <c r="C168" t="s">
+        <v>407</v>
+      </c>
+      <c r="D168" t="s">
+        <v>548</v>
+      </c>
+      <c r="E168" t="s">
+        <v>574</v>
+      </c>
+      <c r="F168" t="s">
+        <v>667</v>
+      </c>
+      <c r="G168">
+        <v>3113050346</v>
+      </c>
+      <c r="H168" t="s">
+        <v>814</v>
+      </c>
+      <c r="I168">
+        <v>585458</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" t="s">
+        <v>371</v>
+      </c>
+      <c r="C169" t="s">
+        <v>403</v>
+      </c>
+      <c r="D169" t="s">
+        <v>549</v>
+      </c>
+      <c r="E169" t="s">
+        <v>575</v>
+      </c>
+      <c r="F169" t="s">
+        <v>668</v>
+      </c>
+      <c r="G169">
+        <v>3003438170</v>
+      </c>
+      <c r="H169" t="s">
+        <v>815</v>
+      </c>
+      <c r="I169">
+        <v>557982</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" t="s">
+        <v>372</v>
+      </c>
+      <c r="C170" t="s">
+        <v>399</v>
+      </c>
+      <c r="D170" t="s">
+        <v>550</v>
+      </c>
+      <c r="E170" t="s">
+        <v>573</v>
+      </c>
+      <c r="F170" t="s">
+        <v>588</v>
+      </c>
+      <c r="G170">
+        <v>3145672233</v>
+      </c>
+      <c r="H170" t="s">
+        <v>816</v>
+      </c>
+      <c r="I170">
+        <v>4295952</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" t="s">
+        <v>373</v>
+      </c>
+      <c r="C171" t="s">
+        <v>401</v>
+      </c>
+      <c r="D171" t="s">
+        <v>551</v>
+      </c>
+      <c r="E171" t="s">
+        <v>573</v>
+      </c>
+      <c r="F171" t="s">
+        <v>588</v>
+      </c>
+      <c r="G171">
+        <v>3145672233</v>
+      </c>
+      <c r="H171" t="s">
+        <v>816</v>
+      </c>
+      <c r="I171">
+        <v>2276408</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" t="s">
+        <v>374</v>
+      </c>
+      <c r="C172" t="s">
+        <v>407</v>
+      </c>
+      <c r="D172" t="s">
+        <v>552</v>
+      </c>
+      <c r="E172" t="s">
+        <v>573</v>
+      </c>
+      <c r="F172" t="s">
+        <v>669</v>
+      </c>
+      <c r="G172">
+        <v>3148214908</v>
+      </c>
+      <c r="H172" t="s">
+        <v>817</v>
+      </c>
+      <c r="I172">
+        <v>585486</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" t="s">
+        <v>180</v>
+      </c>
+      <c r="B173" t="s">
+        <v>375</v>
+      </c>
+      <c r="C173" t="s">
+        <v>404</v>
+      </c>
+      <c r="D173" t="s">
+        <v>552</v>
+      </c>
+      <c r="E173" t="s">
+        <v>573</v>
+      </c>
+      <c r="F173" t="s">
+        <v>669</v>
+      </c>
+      <c r="G173">
+        <v>3148214908</v>
+      </c>
+      <c r="H173" t="s">
+        <v>817</v>
+      </c>
+      <c r="I173">
+        <v>1527990</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" t="s">
+        <v>376</v>
+      </c>
+      <c r="C174" t="s">
+        <v>404</v>
+      </c>
+      <c r="D174" t="s">
+        <v>553</v>
+      </c>
+      <c r="E174" t="s">
+        <v>574</v>
+      </c>
+      <c r="F174" t="s">
+        <v>670</v>
+      </c>
+      <c r="G174">
+        <v>3207611691</v>
+      </c>
+      <c r="H174" t="s">
+        <v>818</v>
+      </c>
+      <c r="I174">
+        <v>956502</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" t="s">
+        <v>377</v>
+      </c>
+      <c r="C175" t="s">
+        <v>401</v>
+      </c>
+      <c r="D175" t="s">
+        <v>549</v>
+      </c>
+      <c r="E175" t="s">
+        <v>574</v>
+      </c>
+      <c r="F175" t="s">
+        <v>668</v>
+      </c>
+      <c r="G175">
+        <v>3003438170</v>
+      </c>
+      <c r="H175" t="s">
+        <v>815</v>
+      </c>
+      <c r="I175">
+        <v>1791600</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" t="s">
+        <v>183</v>
+      </c>
+      <c r="B176" t="s">
+        <v>378</v>
+      </c>
+      <c r="C176" t="s">
+        <v>401</v>
+      </c>
+      <c r="D176" t="s">
+        <v>554</v>
+      </c>
+      <c r="E176" t="s">
+        <v>573</v>
+      </c>
+      <c r="F176" t="s">
+        <v>671</v>
+      </c>
+      <c r="G176">
+        <v>3008765266</v>
+      </c>
+      <c r="H176" t="s">
+        <v>819</v>
+      </c>
+      <c r="I176">
+        <v>374688</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" t="s">
+        <v>379</v>
+      </c>
+      <c r="C177" t="s">
+        <v>406</v>
+      </c>
+      <c r="D177" t="s">
+        <v>554</v>
+      </c>
+      <c r="E177" t="s">
+        <v>573</v>
+      </c>
+      <c r="F177" t="s">
+        <v>671</v>
+      </c>
+      <c r="G177">
+        <v>3008765266</v>
+      </c>
+      <c r="H177" t="s">
+        <v>819</v>
+      </c>
+      <c r="I177">
+        <v>339652</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" t="s">
+        <v>380</v>
+      </c>
+      <c r="C178" t="s">
+        <v>403</v>
+      </c>
+      <c r="D178" t="s">
+        <v>555</v>
+      </c>
+      <c r="E178" t="s">
+        <v>573</v>
+      </c>
+      <c r="F178" t="s">
+        <v>672</v>
+      </c>
+      <c r="G178">
+        <v>3206353393</v>
+      </c>
+      <c r="H178" t="s">
+        <v>820</v>
+      </c>
+      <c r="I178">
+        <v>557982</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" t="s">
+        <v>186</v>
+      </c>
+      <c r="B179" t="s">
+        <v>381</v>
+      </c>
+      <c r="C179" t="s">
+        <v>403</v>
+      </c>
+      <c r="D179" t="s">
+        <v>556</v>
+      </c>
+      <c r="E179" t="s">
+        <v>573</v>
+      </c>
+      <c r="F179" t="s">
+        <v>673</v>
+      </c>
+      <c r="G179">
+        <v>3205617348</v>
+      </c>
+      <c r="H179" t="s">
+        <v>821</v>
+      </c>
+      <c r="I179">
+        <v>1182855</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" t="s">
+        <v>187</v>
+      </c>
+      <c r="B180" t="s">
+        <v>382</v>
+      </c>
+      <c r="C180" t="s">
+        <v>403</v>
+      </c>
+      <c r="D180" t="s">
+        <v>557</v>
+      </c>
+      <c r="E180" t="s">
+        <v>574</v>
+      </c>
+      <c r="F180" t="s">
+        <v>588</v>
+      </c>
+      <c r="G180">
+        <v>3186473339</v>
+      </c>
+      <c r="I180">
+        <v>593171</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181" t="s">
+        <v>383</v>
+      </c>
+      <c r="C181" t="s">
+        <v>401</v>
+      </c>
+      <c r="D181" t="s">
+        <v>558</v>
+      </c>
+      <c r="E181" t="s">
+        <v>574</v>
+      </c>
+      <c r="F181" t="s">
+        <v>588</v>
+      </c>
+      <c r="G181">
+        <v>3206798318</v>
+      </c>
+      <c r="H181" t="s">
+        <v>822</v>
+      </c>
+      <c r="I181">
+        <v>2812103</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" t="s">
+        <v>189</v>
+      </c>
+      <c r="B182" t="s">
+        <v>384</v>
+      </c>
+      <c r="C182" t="s">
+        <v>405</v>
+      </c>
+      <c r="D182" t="s">
+        <v>559</v>
+      </c>
+      <c r="E182" t="s">
+        <v>574</v>
+      </c>
+      <c r="F182" t="s">
+        <v>674</v>
+      </c>
+      <c r="G182">
+        <v>3175795524</v>
+      </c>
+      <c r="H182" t="s">
+        <v>823</v>
+      </c>
+      <c r="I182">
+        <v>650772</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" t="s">
+        <v>190</v>
+      </c>
+      <c r="B183" t="s">
+        <v>385</v>
+      </c>
+      <c r="C183" t="s">
+        <v>400</v>
+      </c>
+      <c r="D183" t="s">
+        <v>560</v>
+      </c>
+      <c r="E183" t="s">
+        <v>574</v>
+      </c>
+      <c r="F183" t="s">
+        <v>588</v>
+      </c>
+      <c r="G183">
+        <v>3116803238</v>
+      </c>
+      <c r="H183" t="s">
+        <v>824</v>
+      </c>
+      <c r="I183">
+        <v>506123</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" t="s">
+        <v>191</v>
+      </c>
+      <c r="B184" t="s">
+        <v>386</v>
+      </c>
+      <c r="C184" t="s">
+        <v>400</v>
+      </c>
+      <c r="D184" t="s">
+        <v>561</v>
+      </c>
+      <c r="E184" t="s">
+        <v>573</v>
+      </c>
+      <c r="F184" t="s">
+        <v>588</v>
+      </c>
+      <c r="G184">
+        <v>3004106594</v>
+      </c>
+      <c r="H184" t="s">
+        <v>825</v>
+      </c>
+      <c r="I184">
+        <v>601842</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" t="s">
+        <v>192</v>
+      </c>
+      <c r="B185" t="s">
+        <v>387</v>
+      </c>
+      <c r="C185" t="s">
+        <v>403</v>
+      </c>
+      <c r="D185" t="s">
+        <v>561</v>
+      </c>
+      <c r="E185" t="s">
+        <v>573</v>
+      </c>
+      <c r="F185" t="s">
+        <v>588</v>
+      </c>
+      <c r="G185">
+        <v>3004106594</v>
+      </c>
+      <c r="H185" t="s">
+        <v>825</v>
+      </c>
+      <c r="I185">
+        <v>663548</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" t="s">
+        <v>193</v>
+      </c>
+      <c r="B186" t="s">
+        <v>388</v>
+      </c>
+      <c r="C186" t="s">
+        <v>403</v>
+      </c>
+      <c r="D186" t="s">
+        <v>562</v>
+      </c>
+      <c r="E186" t="s">
+        <v>573</v>
+      </c>
+      <c r="F186" t="s">
+        <v>588</v>
+      </c>
+      <c r="G186">
+        <v>3128021315</v>
+      </c>
+      <c r="H186" t="s">
+        <v>826</v>
+      </c>
+      <c r="I186">
+        <v>1047586</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" t="s">
+        <v>389</v>
+      </c>
+      <c r="C187" t="s">
+        <v>404</v>
+      </c>
+      <c r="D187" t="s">
+        <v>563</v>
+      </c>
+      <c r="E187" t="s">
+        <v>574</v>
+      </c>
+      <c r="F187" t="s">
+        <v>675</v>
+      </c>
+      <c r="G187">
+        <v>3184795864</v>
+      </c>
+      <c r="H187" t="s">
+        <v>827</v>
+      </c>
+      <c r="I187">
+        <v>467506</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" t="s">
+        <v>195</v>
+      </c>
+      <c r="B188" t="s">
+        <v>390</v>
+      </c>
+      <c r="C188" t="s">
+        <v>407</v>
+      </c>
+      <c r="D188" t="s">
+        <v>564</v>
+      </c>
+      <c r="E188" t="s">
+        <v>574</v>
+      </c>
+      <c r="F188" t="s">
+        <v>676</v>
+      </c>
+      <c r="G188">
+        <v>3052245305</v>
+      </c>
+      <c r="H188" t="s">
+        <v>828</v>
+      </c>
+      <c r="I188">
+        <v>1762458</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" t="s">
+        <v>196</v>
+      </c>
+      <c r="B189" t="s">
+        <v>391</v>
+      </c>
+      <c r="C189" t="s">
+        <v>407</v>
+      </c>
+      <c r="D189" t="s">
+        <v>565</v>
+      </c>
+      <c r="E189" t="s">
+        <v>573</v>
+      </c>
+      <c r="F189" t="s">
+        <v>677</v>
+      </c>
+      <c r="G189">
+        <v>3002799011</v>
+      </c>
+      <c r="H189" t="s">
+        <v>829</v>
+      </c>
+      <c r="I189">
+        <v>3126138</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" t="s">
+        <v>197</v>
+      </c>
+      <c r="B190" t="s">
+        <v>392</v>
+      </c>
+      <c r="C190" t="s">
+        <v>405</v>
+      </c>
+      <c r="D190" t="s">
+        <v>566</v>
+      </c>
+      <c r="E190" t="s">
+        <v>574</v>
+      </c>
+      <c r="F190" t="s">
+        <v>588</v>
+      </c>
+      <c r="G190">
+        <v>3164456857</v>
+      </c>
+      <c r="H190" t="s">
+        <v>830</v>
+      </c>
+      <c r="I190">
+        <v>520288</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" t="s">
+        <v>393</v>
+      </c>
+      <c r="C191" t="s">
+        <v>404</v>
+      </c>
+      <c r="D191" t="s">
+        <v>567</v>
+      </c>
+      <c r="E191" t="s">
+        <v>573</v>
+      </c>
+      <c r="F191" t="s">
+        <v>678</v>
+      </c>
+      <c r="G191">
+        <v>3113582464</v>
+      </c>
+      <c r="H191" t="s">
+        <v>831</v>
+      </c>
+      <c r="I191">
+        <v>477251</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" t="s">
+        <v>199</v>
+      </c>
+      <c r="B192" t="s">
+        <v>394</v>
+      </c>
+      <c r="C192" t="s">
+        <v>402</v>
+      </c>
+      <c r="D192" t="s">
+        <v>568</v>
+      </c>
+      <c r="E192" t="s">
+        <v>578</v>
+      </c>
+      <c r="F192" t="s">
+        <v>679</v>
+      </c>
+      <c r="G192">
+        <v>3104440838</v>
+      </c>
+      <c r="H192" t="s">
+        <v>832</v>
+      </c>
+      <c r="I192">
+        <v>544969</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" t="s">
+        <v>395</v>
+      </c>
+      <c r="C193" t="s">
+        <v>402</v>
+      </c>
+      <c r="D193" t="s">
+        <v>569</v>
+      </c>
+      <c r="E193" t="s">
+        <v>575</v>
+      </c>
+      <c r="F193" t="s">
+        <v>588</v>
+      </c>
+      <c r="G193">
+        <v>3003183744</v>
+      </c>
+      <c r="H193" t="s">
+        <v>833</v>
+      </c>
+      <c r="I193">
+        <v>605299</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" t="s">
+        <v>201</v>
+      </c>
+      <c r="B194" t="s">
+        <v>396</v>
+      </c>
+      <c r="C194" t="s">
+        <v>405</v>
+      </c>
+      <c r="D194" t="s">
+        <v>570</v>
+      </c>
+      <c r="E194" t="s">
+        <v>574</v>
+      </c>
+      <c r="F194" t="s">
+        <v>680</v>
+      </c>
+      <c r="G194">
+        <v>3006059211</v>
+      </c>
+      <c r="H194" t="s">
+        <v>834</v>
+      </c>
+      <c r="I194">
+        <v>577876</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" t="s">
+        <v>397</v>
+      </c>
+      <c r="C195" t="s">
+        <v>399</v>
+      </c>
+      <c r="D195" t="s">
+        <v>571</v>
+      </c>
+      <c r="E195" t="s">
+        <v>574</v>
+      </c>
+      <c r="F195" t="s">
+        <v>588</v>
+      </c>
+      <c r="G195">
         <v>3022250446</v>
       </c>
-      <c r="H79" t="s">
-        <v>340</v>
-      </c>
-      <c r="I79">
-        <v>670805</v>
+      <c r="H195" t="s">
+        <v>835</v>
+      </c>
+      <c r="I195">
+        <v>1343966</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" t="s">
+        <v>203</v>
+      </c>
+      <c r="B196" t="s">
+        <v>398</v>
+      </c>
+      <c r="C196" t="s">
+        <v>404</v>
+      </c>
+      <c r="D196" t="s">
+        <v>572</v>
+      </c>
+      <c r="E196" t="s">
+        <v>581</v>
+      </c>
+      <c r="F196" t="s">
+        <v>681</v>
+      </c>
+      <c r="G196">
+        <v>3127971899</v>
+      </c>
+      <c r="H196" t="s">
+        <v>836</v>
+      </c>
+      <c r="I196">
+        <v>597567</v>
       </c>
     </row>
   </sheetData>
